--- a/Excel2JSON(win-x64)/excel_files/Data.xlsx
+++ b/Excel2JSON(win-x64)/excel_files/Data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28803"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44781798-4072-4BF8-ABD5-22B9F51F0E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13FBCE28-1C13-44FF-98D4-806E3B4B543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foods" sheetId="1" r:id="rId1"/>
@@ -15,9 +15,6 @@
     <sheet name="NPC" sheetId="8" r:id="rId5"/>
     <sheet name="Quest" sheetId="9" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2027,6 +2024,21 @@
     <t>말수 적고 어조가 부드러움</t>
   </si>
   <si>
+    <t>호랑이</t>
+  </si>
+  <si>
+    <t>다수 설화</t>
+  </si>
+  <si>
+    <t>거칠지만 유쾌함</t>
+  </si>
+  <si>
+    <t>육류</t>
+  </si>
+  <si>
+    <t>어눌한 말투와 호탕한 웃음</t>
+  </si>
+  <si>
     <t>도깨비</t>
   </si>
   <si>
@@ -2040,21 +2052,6 @@
   </si>
   <si>
     <t>투박하고 재미있는 말투</t>
-  </si>
-  <si>
-    <t>호랑이</t>
-  </si>
-  <si>
-    <t>다수 설화</t>
-  </si>
-  <si>
-    <t>거칠지만 유쾌함</t>
-  </si>
-  <si>
-    <t>육류</t>
-  </si>
-  <si>
-    <t>어눌한 말투와 호탕한 웃음</t>
   </si>
   <si>
     <t>토끼</t>
@@ -2349,25 +2346,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Gathering_Region"/>
-      <sheetName val="Gathering_Biome"/>
-      <sheetName val="Gathering_Season"/>
-      <sheetName val="Gathering_Chance"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19156,7 +19134,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="8">
-        <v>601</v>
+        <v>800001</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>639</v>
@@ -19177,12 +19155,12 @@
         <v>643</v>
       </c>
       <c r="H4" s="8">
-        <v>701</v>
+        <v>900001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="8">
-        <v>602</v>
+        <v>800002</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>644</v>
@@ -19203,12 +19181,12 @@
         <v>647</v>
       </c>
       <c r="H5" s="8">
-        <v>702</v>
+        <v>900002</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8">
-        <v>603</v>
+        <v>800003</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>648</v>
@@ -19229,12 +19207,12 @@
         <v>652</v>
       </c>
       <c r="H6" s="8">
-        <v>703</v>
+        <v>900003</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8">
-        <v>604</v>
+        <v>800004</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>653</v>
@@ -19255,12 +19233,12 @@
         <v>656</v>
       </c>
       <c r="H7" s="8">
-        <v>704</v>
+        <v>900004</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="8">
-        <v>605</v>
+        <v>800005</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>657</v>
@@ -19281,12 +19259,12 @@
         <v>661</v>
       </c>
       <c r="H8" s="8">
-        <v>705</v>
+        <v>900005</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="8">
-        <v>606</v>
+        <v>800006</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>662</v>
@@ -19301,18 +19279,18 @@
         <v>665</v>
       </c>
       <c r="F9" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>666</v>
       </c>
       <c r="H9" s="8">
-        <v>706</v>
+        <v>900007</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="8">
-        <v>607</v>
+        <v>800007</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>667</v>
@@ -19327,18 +19305,18 @@
         <v>670</v>
       </c>
       <c r="F10" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>671</v>
       </c>
       <c r="H10" s="8">
-        <v>709</v>
+        <v>900006</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="8">
-        <v>608</v>
+        <v>800008</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>672</v>
@@ -19359,12 +19337,12 @@
         <v>676</v>
       </c>
       <c r="H11" s="8">
-        <v>710</v>
+        <v>900008</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="8">
-        <v>609</v>
+        <v>800009</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>677</v>
@@ -19385,12 +19363,12 @@
         <v>680</v>
       </c>
       <c r="H12" s="8">
-        <v>711</v>
+        <v>900009</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="8">
-        <v>610</v>
+        <v>800010</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>681</v>
@@ -19411,7 +19389,7 @@
         <v>685</v>
       </c>
       <c r="H13" s="8">
-        <v>712</v>
+        <v>900010</v>
       </c>
     </row>
   </sheetData>
@@ -19504,16 +19482,16 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3">
-        <v>701</v>
+        <v>900001</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>698</v>
       </c>
       <c r="C4" s="3">
-        <v>601</v>
+        <v>800001</v>
       </c>
       <c r="D4" s="3">
-        <v>104</v>
+        <v>103001</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>699</v>
@@ -19530,16 +19508,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3">
-        <v>702</v>
+        <v>900002</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>701</v>
       </c>
       <c r="C5" s="3">
-        <v>602</v>
+        <v>800002</v>
       </c>
       <c r="D5" s="3">
-        <v>101</v>
+        <v>103004</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>702</v>
@@ -19548,7 +19526,7 @@
         <v>703</v>
       </c>
       <c r="G5" s="3">
-        <v>601</v>
+        <v>800001</v>
       </c>
       <c r="H5" s="3">
         <v>60</v>
@@ -19556,16 +19534,16 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3">
-        <v>703</v>
+        <v>900003</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>704</v>
       </c>
       <c r="C6" s="3">
-        <v>603</v>
+        <v>800003</v>
       </c>
       <c r="D6" s="3">
-        <v>103</v>
+        <v>103002</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>651</v>
@@ -19582,16 +19560,16 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3">
-        <v>704</v>
+        <v>900004</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>706</v>
       </c>
       <c r="C7" s="3">
-        <v>604</v>
+        <v>800004</v>
       </c>
       <c r="D7" s="3">
-        <v>108</v>
+        <v>103003</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>707</v>
@@ -19600,7 +19578,7 @@
         <v>708</v>
       </c>
       <c r="G7" s="3">
-        <v>603</v>
+        <v>800002</v>
       </c>
       <c r="H7" s="3">
         <v>70</v>
@@ -19608,16 +19586,16 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="3">
-        <v>705</v>
+        <v>900005</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>709</v>
       </c>
       <c r="C8" s="3">
-        <v>605</v>
+        <v>800005</v>
       </c>
       <c r="D8" s="3">
-        <v>109</v>
+        <v>103007</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>660</v>
@@ -19634,16 +19612,16 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3">
-        <v>709</v>
+        <v>900006</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>711</v>
       </c>
       <c r="C9" s="3">
-        <v>609</v>
+        <v>800006</v>
       </c>
       <c r="D9" s="3">
-        <v>102</v>
+        <v>103005</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>712</v>
@@ -19652,7 +19630,7 @@
         <v>713</v>
       </c>
       <c r="G9" s="3">
-        <v>605</v>
+        <v>800005</v>
       </c>
       <c r="H9" s="3">
         <v>60</v>
@@ -19660,16 +19638,16 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3">
-        <v>706</v>
+        <v>900007</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>714</v>
       </c>
       <c r="C10" s="3">
-        <v>606</v>
+        <v>800007</v>
       </c>
       <c r="D10" s="3">
-        <v>102</v>
+        <v>103006</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>715</v>
@@ -19678,7 +19656,7 @@
         <v>716</v>
       </c>
       <c r="G10" s="3">
-        <v>605</v>
+        <v>800005</v>
       </c>
       <c r="H10" s="3">
         <v>70</v>
@@ -19686,16 +19664,16 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3">
-        <v>710</v>
+        <v>900008</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>717</v>
       </c>
       <c r="C11" s="3">
-        <v>610</v>
+        <v>800008</v>
       </c>
       <c r="D11" s="3">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>718</v>
@@ -19704,7 +19682,7 @@
         <v>719</v>
       </c>
       <c r="G11" s="3">
-        <v>607</v>
+        <v>800007</v>
       </c>
       <c r="H11" s="3">
         <v>70</v>
@@ -19712,16 +19690,16 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3">
-        <v>711</v>
+        <v>900009</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>720</v>
       </c>
       <c r="C12" s="3">
-        <v>611</v>
+        <v>800009</v>
       </c>
       <c r="D12" s="3">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>721</v>
@@ -19730,7 +19708,7 @@
         <v>722</v>
       </c>
       <c r="G12" s="3">
-        <v>608</v>
+        <v>800008</v>
       </c>
       <c r="H12" s="3">
         <v>60</v>
@@ -19738,16 +19716,16 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="3">
-        <v>712</v>
+        <v>900010</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>723</v>
       </c>
       <c r="C13" s="3">
-        <v>612</v>
+        <v>800010</v>
       </c>
       <c r="D13" s="3">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>724</v>
@@ -19756,7 +19734,7 @@
         <v>725</v>
       </c>
       <c r="G13" s="3">
-        <v>602</v>
+        <v>800010</v>
       </c>
       <c r="H13" s="3">
         <v>60</v>

--- a/Excel2JSON(win-x64)/excel_files/Data.xlsx
+++ b/Excel2JSON(win-x64)/excel_files/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28816"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6AAC89C-00BC-4FFA-B7B2-3808DA23F1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{042C2887-EE4A-4308-B54B-87435F336C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5040" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5243" uniqueCount="981">
   <si>
     <t>key</t>
   </si>
@@ -2406,7 +2406,7 @@
     <t>쌈장</t>
   </si>
   <si>
-    <t>401, 403, 11</t>
+    <t>110401, 110403, 110011</t>
   </si>
   <si>
     <t>조합 재료</t>
@@ -2415,13 +2415,13 @@
     <t>밀가루 반죽</t>
   </si>
   <si>
-    <t>406, 60</t>
+    <t>110406, 110060</t>
   </si>
   <si>
     <t>고구마 맛탕</t>
   </si>
   <si>
-    <t>124, 11</t>
+    <t>110124, 110011</t>
   </si>
   <si>
     <t>조합 요리</t>
@@ -2430,25 +2430,25 @@
     <t>멸치 볶음</t>
   </si>
   <si>
-    <t>147, 11</t>
+    <t>110147, 110011</t>
   </si>
   <si>
     <t>견과류 멸치 볶음</t>
   </si>
   <si>
-    <t>147, 11, 135</t>
+    <t>110147, 110011, 110135</t>
   </si>
   <si>
     <t>버터 감자</t>
   </si>
   <si>
-    <t>114, 407</t>
+    <t>110114, 1100407</t>
   </si>
   <si>
     <t xml:space="preserve">허니 버터 감자 </t>
   </si>
   <si>
-    <t>114, 407, 11</t>
+    <t>110114, 110407, 110011</t>
   </si>
   <si>
     <t>정어리 회</t>
@@ -24001,11 +24001,11 @@
       <c r="B4" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="C4" s="9">
-        <v>100</v>
-      </c>
-      <c r="D4" s="9">
-        <v>1</v>
+      <c r="C4" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>425</v>
       </c>
       <c r="E4" s="9">
         <v>1001</v>
@@ -24021,11 +24021,11 @@
       <c r="B5" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="C5" s="9">
-        <v>101</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1</v>
+      <c r="C5" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>425</v>
       </c>
       <c r="E5" s="9">
         <v>1002</v>
@@ -24041,11 +24041,11 @@
       <c r="B6" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="C6" s="9">
-        <v>102</v>
-      </c>
-      <c r="D6" s="9">
-        <v>2</v>
+      <c r="C6" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>427</v>
       </c>
       <c r="E6" s="9">
         <v>1001</v>
@@ -24061,11 +24061,11 @@
       <c r="B7" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="C7" s="9">
-        <v>103</v>
-      </c>
-      <c r="D7" s="9">
-        <v>2</v>
+      <c r="C7" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>427</v>
       </c>
       <c r="E7" s="9">
         <v>1002</v>
@@ -24081,11 +24081,11 @@
       <c r="B8" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="C8" s="9">
-        <v>104</v>
-      </c>
-      <c r="D8" s="9">
-        <v>3</v>
+      <c r="C8" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>428</v>
       </c>
       <c r="E8" s="9">
         <v>1001</v>
@@ -24101,11 +24101,11 @@
       <c r="B9" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="C9" s="9">
-        <v>105</v>
-      </c>
-      <c r="D9" s="9">
-        <v>3</v>
+      <c r="C9" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>428</v>
       </c>
       <c r="E9" s="9">
         <v>1003</v>
@@ -24121,11 +24121,11 @@
       <c r="B10" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="C10" s="9">
-        <v>106</v>
-      </c>
-      <c r="D10" s="9">
-        <v>4</v>
+      <c r="C10" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>429</v>
       </c>
       <c r="E10" s="9">
         <v>1001</v>
@@ -24141,11 +24141,11 @@
       <c r="B11" s="9" t="s">
         <v>699</v>
       </c>
-      <c r="C11" s="9">
-        <v>107</v>
-      </c>
-      <c r="D11" s="9">
-        <v>7</v>
+      <c r="C11" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>432</v>
       </c>
       <c r="E11" s="9">
         <v>1001</v>
@@ -24161,11 +24161,11 @@
       <c r="B12" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="C12" s="9">
-        <v>108</v>
-      </c>
-      <c r="D12" s="9">
-        <v>7</v>
+      <c r="C12" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>432</v>
       </c>
       <c r="E12" s="9">
         <v>1006</v>
@@ -24181,11 +24181,11 @@
       <c r="B13" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="C13" s="9">
-        <v>109</v>
-      </c>
-      <c r="D13" s="9">
-        <v>7</v>
+      <c r="C13" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>432</v>
       </c>
       <c r="E13" s="9">
         <v>1006</v>
@@ -24201,11 +24201,11 @@
       <c r="B14" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="C14" s="9">
-        <v>110</v>
-      </c>
-      <c r="D14" s="9">
-        <v>8</v>
+      <c r="C14" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>433</v>
       </c>
       <c r="E14" s="9">
         <v>1004</v>
@@ -24221,11 +24221,11 @@
       <c r="B15" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="C15" s="9">
-        <v>111</v>
-      </c>
-      <c r="D15" s="9">
-        <v>8</v>
+      <c r="C15" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>433</v>
       </c>
       <c r="E15" s="9">
         <v>1005</v>
@@ -24241,11 +24241,11 @@
       <c r="B16" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="C16" s="9">
-        <v>112</v>
-      </c>
-      <c r="D16" s="9">
-        <v>8</v>
+      <c r="C16" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>433</v>
       </c>
       <c r="E16" s="9">
         <v>1001</v>
@@ -24261,11 +24261,11 @@
       <c r="B17" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="C17" s="9">
-        <v>113</v>
-      </c>
-      <c r="D17" s="9">
-        <v>9</v>
+      <c r="C17" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>434</v>
       </c>
       <c r="E17" s="9">
         <v>1001</v>
@@ -24281,11 +24281,11 @@
       <c r="B18" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="C18" s="9">
-        <v>114</v>
-      </c>
-      <c r="D18" s="9">
-        <v>9</v>
+      <c r="C18" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>434</v>
       </c>
       <c r="E18" s="9">
         <v>1006</v>
@@ -24301,11 +24301,11 @@
       <c r="B19" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="C19" s="9">
-        <v>115</v>
-      </c>
-      <c r="D19" s="9">
-        <v>9</v>
+      <c r="C19" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>434</v>
       </c>
       <c r="E19" s="9">
         <v>1004</v>
@@ -24321,11 +24321,11 @@
       <c r="B20" s="9" t="s">
         <v>708</v>
       </c>
-      <c r="C20" s="9">
-        <v>116</v>
-      </c>
-      <c r="D20" s="9">
-        <v>9</v>
+      <c r="C20" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>434</v>
       </c>
       <c r="E20" s="9">
         <v>1002</v>
@@ -24341,11 +24341,11 @@
       <c r="B21" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C21" s="9">
-        <v>117</v>
-      </c>
-      <c r="D21" s="9">
-        <v>10</v>
+      <c r="C21" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>435</v>
       </c>
       <c r="E21" s="9">
         <v>1004</v>
@@ -24361,11 +24361,11 @@
       <c r="B22" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="C22" s="9">
-        <v>118</v>
-      </c>
-      <c r="D22" s="9">
-        <v>12</v>
+      <c r="C22" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>437</v>
       </c>
       <c r="E22" s="9">
         <v>1001</v>
@@ -24381,11 +24381,11 @@
       <c r="B23" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="C23" s="9">
-        <v>119</v>
-      </c>
-      <c r="D23" s="9">
-        <v>12</v>
+      <c r="C23" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>437</v>
       </c>
       <c r="E23" s="9">
         <v>1004</v>
@@ -24401,11 +24401,11 @@
       <c r="B24" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C24" s="9">
-        <v>120</v>
-      </c>
-      <c r="D24" s="9">
-        <v>12</v>
+      <c r="C24" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>437</v>
       </c>
       <c r="E24" s="9">
         <v>1003</v>
@@ -24421,11 +24421,11 @@
       <c r="B25" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="C25" s="9">
-        <v>121</v>
-      </c>
-      <c r="D25" s="9">
-        <v>13</v>
+      <c r="C25" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>438</v>
       </c>
       <c r="E25" s="9">
         <v>1001</v>
@@ -24441,11 +24441,11 @@
       <c r="B26" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="C26" s="9">
-        <v>122</v>
-      </c>
-      <c r="D26" s="9">
-        <v>14</v>
+      <c r="C26" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>439</v>
       </c>
       <c r="E26" s="9">
         <v>1003</v>
@@ -24461,11 +24461,11 @@
       <c r="B27" s="9" t="s">
         <v>715</v>
       </c>
-      <c r="C27" s="9">
-        <v>123</v>
-      </c>
-      <c r="D27" s="9">
-        <v>15</v>
+      <c r="C27" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>440</v>
       </c>
       <c r="E27" s="9">
         <v>1001</v>
@@ -24481,11 +24481,11 @@
       <c r="B28" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="C28" s="9">
-        <v>124</v>
-      </c>
-      <c r="D28" s="9">
-        <v>15</v>
+      <c r="C28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>440</v>
       </c>
       <c r="E28" s="9">
         <v>1006</v>
@@ -24501,11 +24501,11 @@
       <c r="B29" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="C29" s="9">
-        <v>125</v>
-      </c>
-      <c r="D29" s="9">
-        <v>15</v>
+      <c r="C29" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>440</v>
       </c>
       <c r="E29" s="9">
         <v>1004</v>
@@ -24521,11 +24521,11 @@
       <c r="B30" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="C30" s="9">
-        <v>126</v>
-      </c>
-      <c r="D30" s="9">
-        <v>15</v>
+      <c r="C30" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>440</v>
       </c>
       <c r="E30" s="9">
         <v>1002</v>
@@ -24541,11 +24541,11 @@
       <c r="B31" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="C31" s="9">
-        <v>127</v>
-      </c>
-      <c r="D31" s="9">
-        <v>17</v>
+      <c r="C31" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>442</v>
       </c>
       <c r="E31" s="9">
         <v>1005</v>
@@ -24561,11 +24561,11 @@
       <c r="B32" s="9" t="s">
         <v>720</v>
       </c>
-      <c r="C32" s="9">
-        <v>128</v>
-      </c>
-      <c r="D32" s="9">
-        <v>18</v>
+      <c r="C32" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>443</v>
       </c>
       <c r="E32" s="9">
         <v>1005</v>
@@ -24581,11 +24581,11 @@
       <c r="B33" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="C33" s="9">
-        <v>129</v>
-      </c>
-      <c r="D33" s="9">
-        <v>18</v>
+      <c r="C33" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>443</v>
       </c>
       <c r="E33" s="9">
         <v>1002</v>
@@ -24601,11 +24601,11 @@
       <c r="B34" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="C34" s="9">
-        <v>130</v>
-      </c>
-      <c r="D34" s="9">
-        <v>19</v>
+      <c r="C34" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>444</v>
       </c>
       <c r="E34" s="9">
         <v>1001</v>
@@ -24621,11 +24621,11 @@
       <c r="B35" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="C35" s="9">
-        <v>131</v>
-      </c>
-      <c r="D35" s="9">
-        <v>19</v>
+      <c r="C35" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>444</v>
       </c>
       <c r="E35" s="9">
         <v>1003</v>
@@ -24641,11 +24641,11 @@
       <c r="B36" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="C36" s="9">
-        <v>132</v>
-      </c>
-      <c r="D36" s="9">
-        <v>20</v>
+      <c r="C36" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>445</v>
       </c>
       <c r="E36" s="9">
         <v>1001</v>
@@ -24661,11 +24661,11 @@
       <c r="B37" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="C37" s="9">
-        <v>133</v>
-      </c>
-      <c r="D37" s="9">
-        <v>20</v>
+      <c r="C37" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>445</v>
       </c>
       <c r="E37" s="9">
         <v>1003</v>
@@ -24681,11 +24681,11 @@
       <c r="B38" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="C38" s="9">
-        <v>134</v>
-      </c>
-      <c r="D38" s="9">
-        <v>21</v>
+      <c r="C38" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="E38" s="9">
         <v>1002</v>
@@ -24701,11 +24701,11 @@
       <c r="B39" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="C39" s="9">
-        <v>135</v>
-      </c>
-      <c r="D39" s="9">
-        <v>21</v>
+      <c r="C39" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="E39" s="9">
         <v>1001</v>
@@ -24721,11 +24721,11 @@
       <c r="B40" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="C40" s="9">
-        <v>136</v>
-      </c>
-      <c r="D40" s="9">
-        <v>22</v>
+      <c r="C40" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>447</v>
       </c>
       <c r="E40" s="9">
         <v>1001</v>
@@ -24741,11 +24741,11 @@
       <c r="B41" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="C41" s="9">
-        <v>137</v>
-      </c>
-      <c r="D41" s="9">
-        <v>23</v>
+      <c r="C41" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>448</v>
       </c>
       <c r="E41" s="9">
         <v>1001</v>
@@ -24761,11 +24761,11 @@
       <c r="B42" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="C42" s="9">
-        <v>138</v>
-      </c>
-      <c r="D42" s="9">
-        <v>24</v>
+      <c r="C42" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>449</v>
       </c>
       <c r="E42" s="9">
         <v>1001</v>
@@ -24781,11 +24781,11 @@
       <c r="B43" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="C43" s="9">
-        <v>139</v>
-      </c>
-      <c r="D43" s="9">
-        <v>24</v>
+      <c r="C43" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>449</v>
       </c>
       <c r="E43" s="9">
         <v>1003</v>
@@ -24801,11 +24801,11 @@
       <c r="B44" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="C44" s="9">
-        <v>140</v>
-      </c>
-      <c r="D44" s="9">
-        <v>27</v>
+      <c r="C44" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>452</v>
       </c>
       <c r="E44" s="9">
         <v>1001</v>
@@ -24821,11 +24821,11 @@
       <c r="B45" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="C45" s="9">
-        <v>141</v>
-      </c>
-      <c r="D45" s="9">
-        <v>27</v>
+      <c r="C45" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>452</v>
       </c>
       <c r="E45" s="9">
         <v>1001</v>
@@ -24841,11 +24841,11 @@
       <c r="B46" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="C46" s="9">
-        <v>142</v>
-      </c>
-      <c r="D46" s="9">
-        <v>28</v>
+      <c r="C46" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>453</v>
       </c>
       <c r="E46" s="9">
         <v>1004</v>
@@ -24861,11 +24861,11 @@
       <c r="B47" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="C47" s="9">
-        <v>143</v>
-      </c>
-      <c r="D47" s="9">
-        <v>32</v>
+      <c r="C47" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>457</v>
       </c>
       <c r="E47" s="9">
         <v>1001</v>
@@ -24881,11 +24881,11 @@
       <c r="B48" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="C48" s="9">
-        <v>144</v>
-      </c>
-      <c r="D48" s="9">
-        <v>32</v>
+      <c r="C48" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>457</v>
       </c>
       <c r="E48" s="9">
         <v>1001</v>
@@ -24901,11 +24901,11 @@
       <c r="B49" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="C49" s="9">
-        <v>145</v>
-      </c>
-      <c r="D49" s="9">
-        <v>32</v>
+      <c r="C49" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>457</v>
       </c>
       <c r="E49" s="9">
         <v>1006</v>
@@ -24921,11 +24921,11 @@
       <c r="B50" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="C50" s="9">
-        <v>146</v>
-      </c>
-      <c r="D50" s="9">
-        <v>33</v>
+      <c r="C50" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>458</v>
       </c>
       <c r="E50" s="9">
         <v>1001</v>
@@ -24941,11 +24941,11 @@
       <c r="B51" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="C51" s="9">
-        <v>147</v>
-      </c>
-      <c r="D51" s="9">
-        <v>33</v>
+      <c r="C51" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>458</v>
       </c>
       <c r="E51" s="9">
         <v>1006</v>
@@ -24961,11 +24961,11 @@
       <c r="B52" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="C52" s="9">
-        <v>148</v>
-      </c>
-      <c r="D52" s="9">
-        <v>34</v>
+      <c r="C52" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>459</v>
       </c>
       <c r="E52" s="9">
         <v>1004</v>
@@ -24981,11 +24981,11 @@
       <c r="B53" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="C53" s="9">
-        <v>149</v>
-      </c>
-      <c r="D53" s="9">
-        <v>35</v>
+      <c r="C53" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>460</v>
       </c>
       <c r="E53" s="9">
         <v>1004</v>
@@ -25001,11 +25001,11 @@
       <c r="B54" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="C54" s="9">
-        <v>150</v>
-      </c>
-      <c r="D54" s="9">
-        <v>36</v>
+      <c r="C54" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>461</v>
       </c>
       <c r="E54" s="9">
         <v>1001</v>
@@ -25021,11 +25021,11 @@
       <c r="B55" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="C55" s="9">
-        <v>151</v>
-      </c>
-      <c r="D55" s="9">
-        <v>36</v>
+      <c r="C55" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>461</v>
       </c>
       <c r="E55" s="9">
         <v>1001</v>
@@ -25041,11 +25041,11 @@
       <c r="B56" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="C56" s="9">
-        <v>152</v>
-      </c>
-      <c r="D56" s="9">
-        <v>36</v>
+      <c r="C56" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>461</v>
       </c>
       <c r="E56" s="9">
         <v>1006</v>
@@ -25061,11 +25061,11 @@
       <c r="B57" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="C57" s="9">
-        <v>153</v>
-      </c>
-      <c r="D57" s="9">
-        <v>37</v>
+      <c r="C57" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>462</v>
       </c>
       <c r="E57" s="9">
         <v>1001</v>
@@ -25081,11 +25081,11 @@
       <c r="B58" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="C58" s="9">
-        <v>154</v>
-      </c>
-      <c r="D58" s="9">
-        <v>39</v>
+      <c r="C58" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>464</v>
       </c>
       <c r="E58" s="9">
         <v>1001</v>
@@ -25101,11 +25101,11 @@
       <c r="B59" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="C59" s="9">
-        <v>155</v>
-      </c>
-      <c r="D59" s="9">
-        <v>39</v>
+      <c r="C59" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>464</v>
       </c>
       <c r="E59" s="9">
         <v>1001</v>
@@ -25121,11 +25121,11 @@
       <c r="B60" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="C60" s="9">
-        <v>156</v>
-      </c>
-      <c r="D60" s="9">
-        <v>40</v>
+      <c r="C60" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>465</v>
       </c>
       <c r="E60" s="9">
         <v>1005</v>
@@ -25141,11 +25141,11 @@
       <c r="B61" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="C61" s="9">
-        <v>157</v>
-      </c>
-      <c r="D61" s="9">
-        <v>41</v>
+      <c r="C61" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>466</v>
       </c>
       <c r="E61" s="9">
         <v>1001</v>
@@ -25161,11 +25161,11 @@
       <c r="B62" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="C62" s="9">
-        <v>158</v>
-      </c>
-      <c r="D62" s="9">
-        <v>42</v>
+      <c r="C62" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>467</v>
       </c>
       <c r="E62" s="9">
         <v>1001</v>
@@ -25181,11 +25181,11 @@
       <c r="B63" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="C63" s="9">
-        <v>159</v>
-      </c>
-      <c r="D63" s="9">
-        <v>42</v>
+      <c r="C63" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>467</v>
       </c>
       <c r="E63" s="9">
         <v>1001</v>
@@ -25201,11 +25201,11 @@
       <c r="B64" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="C64" s="9">
-        <v>160</v>
-      </c>
-      <c r="D64" s="9">
-        <v>42</v>
+      <c r="C64" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>467</v>
       </c>
       <c r="E64" s="9">
         <v>1006</v>
@@ -25221,11 +25221,11 @@
       <c r="B65" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="C65" s="9">
-        <v>161</v>
-      </c>
-      <c r="D65" s="9">
-        <v>44</v>
+      <c r="C65" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>469</v>
       </c>
       <c r="E65" s="9">
         <v>1001</v>
@@ -25241,11 +25241,11 @@
       <c r="B66" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="C66" s="9">
-        <v>162</v>
-      </c>
-      <c r="D66" s="9">
-        <v>44</v>
+      <c r="C66" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>469</v>
       </c>
       <c r="E66" s="9">
         <v>1001</v>
@@ -25261,11 +25261,11 @@
       <c r="B67" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="C67" s="9">
-        <v>163</v>
-      </c>
-      <c r="D67" s="9">
-        <v>44</v>
+      <c r="C67" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>469</v>
       </c>
       <c r="E67" s="9">
         <v>1001</v>
@@ -25281,11 +25281,11 @@
       <c r="B68" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="C68" s="9">
-        <v>164</v>
-      </c>
-      <c r="D68" s="9">
-        <v>44</v>
+      <c r="C68" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>469</v>
       </c>
       <c r="E68" s="9">
         <v>1005</v>
@@ -25301,11 +25301,11 @@
       <c r="B69" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="C69" s="9">
-        <v>165</v>
-      </c>
-      <c r="D69" s="9">
-        <v>44</v>
+      <c r="C69" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>469</v>
       </c>
       <c r="E69" s="9">
         <v>1006</v>
@@ -25321,11 +25321,11 @@
       <c r="B70" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="C70" s="9">
-        <v>166</v>
-      </c>
-      <c r="D70" s="9">
-        <v>45</v>
+      <c r="C70" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>470</v>
       </c>
       <c r="E70" s="9">
         <v>1001</v>
@@ -25341,11 +25341,11 @@
       <c r="B71" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="C71" s="9">
-        <v>167</v>
-      </c>
-      <c r="D71" s="9">
-        <v>45</v>
+      <c r="C71" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>470</v>
       </c>
       <c r="E71" s="9">
         <v>1001</v>
@@ -25361,11 +25361,11 @@
       <c r="B72" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="C72" s="9">
-        <v>168</v>
-      </c>
-      <c r="D72" s="9">
-        <v>45</v>
+      <c r="C72" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>470</v>
       </c>
       <c r="E72" s="9">
         <v>1005</v>
@@ -25381,11 +25381,11 @@
       <c r="B73" s="9" t="s">
         <v>761</v>
       </c>
-      <c r="C73" s="9">
-        <v>169</v>
-      </c>
-      <c r="D73" s="9">
-        <v>46</v>
+      <c r="C73" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>471</v>
       </c>
       <c r="E73" s="9">
         <v>1001</v>
@@ -25401,11 +25401,11 @@
       <c r="B74" s="9" t="s">
         <v>762</v>
       </c>
-      <c r="C74" s="9">
-        <v>170</v>
-      </c>
-      <c r="D74" s="9">
-        <v>46</v>
+      <c r="C74" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>471</v>
       </c>
       <c r="E74" s="9">
         <v>1005</v>
@@ -25421,11 +25421,11 @@
       <c r="B75" s="9" t="s">
         <v>763</v>
       </c>
-      <c r="C75" s="9">
-        <v>171</v>
-      </c>
-      <c r="D75" s="9">
-        <v>46</v>
+      <c r="C75" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>471</v>
       </c>
       <c r="E75" s="9">
         <v>1006</v>
@@ -25441,11 +25441,11 @@
       <c r="B76" s="9" t="s">
         <v>764</v>
       </c>
-      <c r="C76" s="9">
-        <v>172</v>
-      </c>
-      <c r="D76" s="9">
-        <v>47</v>
+      <c r="C76" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>472</v>
       </c>
       <c r="E76" s="9">
         <v>1001</v>
@@ -25461,11 +25461,11 @@
       <c r="B77" s="9" t="s">
         <v>765</v>
       </c>
-      <c r="C77" s="9">
-        <v>173</v>
-      </c>
-      <c r="D77" s="9">
-        <v>47</v>
+      <c r="C77" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>472</v>
       </c>
       <c r="E77" s="9">
         <v>1001</v>
@@ -25481,11 +25481,11 @@
       <c r="B78" s="9" t="s">
         <v>766</v>
       </c>
-      <c r="C78" s="9">
-        <v>174</v>
-      </c>
-      <c r="D78" s="9">
-        <v>47</v>
+      <c r="C78" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>472</v>
       </c>
       <c r="E78" s="9">
         <v>1005</v>
@@ -25501,11 +25501,11 @@
       <c r="B79" s="9" t="s">
         <v>767</v>
       </c>
-      <c r="C79" s="9">
-        <v>175</v>
-      </c>
-      <c r="D79" s="9">
-        <v>47</v>
+      <c r="C79" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>472</v>
       </c>
       <c r="E79" s="9">
         <v>1001</v>
@@ -25521,11 +25521,11 @@
       <c r="B80" s="9" t="s">
         <v>768</v>
       </c>
-      <c r="C80" s="9">
-        <v>176</v>
-      </c>
-      <c r="D80" s="9">
-        <v>48</v>
+      <c r="C80" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>473</v>
       </c>
       <c r="E80" s="9">
         <v>1001</v>
@@ -25541,11 +25541,11 @@
       <c r="B81" s="9" t="s">
         <v>769</v>
       </c>
-      <c r="C81" s="9">
-        <v>177</v>
-      </c>
-      <c r="D81" s="9">
-        <v>48</v>
+      <c r="C81" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>473</v>
       </c>
       <c r="E81" s="9">
         <v>1001</v>
@@ -25561,11 +25561,11 @@
       <c r="B82" s="9" t="s">
         <v>770</v>
       </c>
-      <c r="C82" s="9">
-        <v>178</v>
-      </c>
-      <c r="D82" s="9">
-        <v>48</v>
+      <c r="C82" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>473</v>
       </c>
       <c r="E82" s="9">
         <v>1005</v>
@@ -25581,11 +25581,11 @@
       <c r="B83" s="9" t="s">
         <v>771</v>
       </c>
-      <c r="C83" s="9">
-        <v>179</v>
-      </c>
-      <c r="D83" s="9">
-        <v>50</v>
+      <c r="C83" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>475</v>
       </c>
       <c r="E83" s="9">
         <v>1001</v>
@@ -25601,11 +25601,11 @@
       <c r="B84" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="C84" s="9">
-        <v>180</v>
-      </c>
-      <c r="D84" s="9">
-        <v>50</v>
+      <c r="C84" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>475</v>
       </c>
       <c r="E84" s="9">
         <v>1001</v>
@@ -25621,11 +25621,11 @@
       <c r="B85" s="9" t="s">
         <v>773</v>
       </c>
-      <c r="C85" s="9">
-        <v>181</v>
-      </c>
-      <c r="D85" s="9">
-        <v>50</v>
+      <c r="C85" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>475</v>
       </c>
       <c r="E85" s="9">
         <v>1005</v>
@@ -25641,11 +25641,11 @@
       <c r="B86" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="C86" s="9">
-        <v>182</v>
-      </c>
-      <c r="D86" s="9">
-        <v>50</v>
+      <c r="C86" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>475</v>
       </c>
       <c r="E86" s="9">
         <v>1001</v>
@@ -25661,11 +25661,11 @@
       <c r="B87" s="9" t="s">
         <v>775</v>
       </c>
-      <c r="C87" s="9">
-        <v>183</v>
-      </c>
-      <c r="D87" s="9">
-        <v>52</v>
+      <c r="C87" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>477</v>
       </c>
       <c r="E87" s="9">
         <v>1005</v>
@@ -25681,11 +25681,11 @@
       <c r="B88" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="C88" s="9">
-        <v>184</v>
-      </c>
-      <c r="D88" s="9">
-        <v>52</v>
+      <c r="C88" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>477</v>
       </c>
       <c r="E88" s="9">
         <v>1006</v>
@@ -25701,11 +25701,11 @@
       <c r="B89" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="C89" s="9">
-        <v>185</v>
-      </c>
-      <c r="D89" s="9">
-        <v>53</v>
+      <c r="C89" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>478</v>
       </c>
       <c r="E89" s="9">
         <v>1005</v>
@@ -25721,11 +25721,11 @@
       <c r="B90" s="9" t="s">
         <v>778</v>
       </c>
-      <c r="C90" s="9">
-        <v>186</v>
-      </c>
-      <c r="D90" s="9">
-        <v>53</v>
+      <c r="C90" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>478</v>
       </c>
       <c r="E90" s="9">
         <v>1006</v>
@@ -25741,11 +25741,11 @@
       <c r="B91" s="9" t="s">
         <v>779</v>
       </c>
-      <c r="C91" s="9">
-        <v>187</v>
-      </c>
-      <c r="D91" s="9">
-        <v>54</v>
+      <c r="C91" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="E91" s="9">
         <v>1005</v>
@@ -25761,11 +25761,11 @@
       <c r="B92" s="9" t="s">
         <v>780</v>
       </c>
-      <c r="C92" s="9">
-        <v>188</v>
-      </c>
-      <c r="D92" s="9">
-        <v>56</v>
+      <c r="C92" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>481</v>
       </c>
       <c r="E92" s="9">
         <v>1001</v>
@@ -25781,11 +25781,11 @@
       <c r="B93" s="9" t="s">
         <v>781</v>
       </c>
-      <c r="C93" s="9">
-        <v>189</v>
-      </c>
-      <c r="D93" s="9">
-        <v>56</v>
+      <c r="C93" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>481</v>
       </c>
       <c r="E93" s="9">
         <v>1001</v>
@@ -25801,11 +25801,11 @@
       <c r="B94" s="9" t="s">
         <v>782</v>
       </c>
-      <c r="C94" s="9">
-        <v>190</v>
-      </c>
-      <c r="D94" s="9">
-        <v>57</v>
+      <c r="C94" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>482</v>
       </c>
       <c r="E94" s="9">
         <v>1001</v>
@@ -25821,11 +25821,11 @@
       <c r="B95" s="9" t="s">
         <v>783</v>
       </c>
-      <c r="C95" s="9">
-        <v>191</v>
-      </c>
-      <c r="D95" s="9">
-        <v>57</v>
+      <c r="C95" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>482</v>
       </c>
       <c r="E95" s="9">
         <v>1003</v>
@@ -25841,11 +25841,11 @@
       <c r="B96" s="9" t="s">
         <v>784</v>
       </c>
-      <c r="C96" s="9">
-        <v>192</v>
-      </c>
-      <c r="D96" s="9">
-        <v>58</v>
+      <c r="C96" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>483</v>
       </c>
       <c r="E96" s="9">
         <v>1001</v>
@@ -25861,11 +25861,11 @@
       <c r="B97" s="9" t="s">
         <v>785</v>
       </c>
-      <c r="C97" s="9">
-        <v>193</v>
-      </c>
-      <c r="D97" s="9">
-        <v>58</v>
+      <c r="C97" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>483</v>
       </c>
       <c r="E97" s="9">
         <v>1003</v>
@@ -25881,11 +25881,11 @@
       <c r="B98" s="9" t="s">
         <v>786</v>
       </c>
-      <c r="C98" s="9">
-        <v>194</v>
-      </c>
-      <c r="D98" s="9">
-        <v>405</v>
+      <c r="C98" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>590</v>
       </c>
       <c r="E98" s="9">
         <v>1004</v>
@@ -25901,11 +25901,11 @@
       <c r="B99" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="C99" s="9">
-        <v>195</v>
-      </c>
-      <c r="D99" s="9">
-        <v>404</v>
+      <c r="C99" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>589</v>
       </c>
       <c r="E99" s="9">
         <v>1004</v>
@@ -25921,8 +25921,8 @@
       <c r="B100" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="C100" s="9">
-        <v>194</v>
+      <c r="C100" s="9" t="s">
+        <v>582</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>789</v>
@@ -25941,8 +25941,8 @@
       <c r="B101" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="C101" s="9">
-        <v>196</v>
+      <c r="C101" s="9" t="s">
+        <v>584</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>792</v>
@@ -25961,8 +25961,8 @@
       <c r="B102" s="9" t="s">
         <v>793</v>
       </c>
-      <c r="C102" s="9">
-        <v>501</v>
+      <c r="C102" s="9" t="s">
+        <v>593</v>
       </c>
       <c r="D102" s="9" t="s">
         <v>794</v>
@@ -25981,8 +25981,8 @@
       <c r="B103" s="9" t="s">
         <v>796</v>
       </c>
-      <c r="C103" s="9">
-        <v>502</v>
+      <c r="C103" s="9" t="s">
+        <v>594</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>797</v>
@@ -26001,8 +26001,8 @@
       <c r="B104" s="9" t="s">
         <v>798</v>
       </c>
-      <c r="C104" s="9">
-        <v>503</v>
+      <c r="C104" s="9" t="s">
+        <v>595</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>799</v>
@@ -26021,8 +26021,8 @@
       <c r="B105" s="9" t="s">
         <v>800</v>
       </c>
-      <c r="C105" s="9">
-        <v>504</v>
+      <c r="C105" s="9" t="s">
+        <v>596</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>801</v>
@@ -26041,8 +26041,8 @@
       <c r="B106" s="9" t="s">
         <v>802</v>
       </c>
-      <c r="C106" s="9">
-        <v>505</v>
+      <c r="C106" s="9" t="s">
+        <v>597</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>803</v>
@@ -26061,11 +26061,11 @@
       <c r="B107" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="C107" s="9">
-        <v>506</v>
-      </c>
-      <c r="D107" s="9">
-        <v>144</v>
+      <c r="C107" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>530</v>
       </c>
       <c r="E107" s="9">
         <v>1008</v>
@@ -26081,11 +26081,11 @@
       <c r="B108" s="9" t="s">
         <v>805</v>
       </c>
-      <c r="C108" s="9">
-        <v>507</v>
-      </c>
-      <c r="D108" s="9">
-        <v>145</v>
+      <c r="C108" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>531</v>
       </c>
       <c r="E108" s="9">
         <v>1008</v>

--- a/Excel2JSON(win-x64)/excel_files/Data.xlsx
+++ b/Excel2JSON(win-x64)/excel_files/Data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28914"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82BEEFB2-0F8B-42FF-A01B-33033C25ACCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16B6C8EF-FD2F-49EC-A66D-4F4AFAE401EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="7" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foods" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5188" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5240" uniqueCount="1405">
   <si>
     <t>key</t>
   </si>
@@ -1288,16 +1288,16 @@
     <t>완벽한 조림간장</t>
   </si>
   <si>
-    <t>망가진 고추양념장</t>
+    <t>망가진 고추 양념장</t>
   </si>
   <si>
     <t>spicyChiliSauce</t>
   </si>
   <si>
-    <t>평범한 고추양념장</t>
-  </si>
-  <si>
-    <t>완벽한 고추양념장</t>
+    <t>평범한 고추 양념장</t>
+  </si>
+  <si>
+    <t>완벽한 고추 양념장</t>
   </si>
   <si>
     <t>망가진 튀김반죽</t>
@@ -2320,7 +2320,7 @@
     <t>조림간장</t>
   </si>
   <si>
-    <t>고추양념장</t>
+    <t>고추 양념장</t>
   </si>
   <si>
     <t>튀김반죽</t>
@@ -2572,25 +2572,22 @@
     <t>forest</t>
   </si>
   <si>
-    <t>101036, 101004, 101005, 101038</t>
+    <t>101036, 101004, 101005</t>
   </si>
   <si>
     <t>101006, 101009, 101017</t>
   </si>
   <si>
-    <t>101036, 101038</t>
-  </si>
-  <si>
     <t>101006, 101009</t>
   </si>
   <si>
     <t>gangwon</t>
   </si>
   <si>
-    <t>101036, 101001, 101003, 101038</t>
-  </si>
-  <si>
-    <t>101036, 101001, 101002, 101003, 101038</t>
+    <t>101036, 101001, 101003</t>
+  </si>
+  <si>
+    <t>101036, 101001, 101002, 101003</t>
   </si>
   <si>
     <t>chungcheong</t>
@@ -2623,13 +2620,13 @@
     <t>101034, 101035</t>
   </si>
   <si>
-    <t>101036, 101005, 101038</t>
-  </si>
-  <si>
-    <t>101036, 101002, 101005, 101038</t>
-  </si>
-  <si>
-    <t>101036, 101002, 101038</t>
+    <t>101036, 101005</t>
+  </si>
+  <si>
+    <t>101036, 101002, 101005</t>
+  </si>
+  <si>
+    <t>101036, 101002</t>
   </si>
   <si>
     <t>resultCategory</t>
@@ -2806,10 +2803,10 @@
     <t>110185, 110408, 110005</t>
   </si>
   <si>
-    <t>110109, 110174, 110177</t>
-  </si>
-  <si>
-    <t>110113, 110179, 110175</t>
+    <t>110109, 110405, 110177</t>
+  </si>
+  <si>
+    <t>110113, 110405, 110175</t>
   </si>
   <si>
     <t>110173, 110181, 110104</t>
@@ -3145,13 +3142,28 @@
     <t>conditionFavorability</t>
   </si>
   <si>
+    <t>letterOfferKeyword</t>
+  </si>
+  <si>
+    <t>letterOfferTitle</t>
+  </si>
+  <si>
     <t>letterOffer</t>
   </si>
   <si>
+    <t>letterNotBadSuccessTitle</t>
+  </si>
+  <si>
     <t>letterNotBadSuccess</t>
   </si>
   <si>
-    <t>letterSoSoGoodSuccess</t>
+    <t>letterSuccessTitle</t>
+  </si>
+  <si>
+    <t>letterSuccess</t>
+  </si>
+  <si>
+    <t>letterFailTitle</t>
   </si>
   <si>
     <t>letterFail</t>
@@ -3166,6 +3178,9 @@
     <t>notBadFood</t>
   </si>
   <si>
+    <t>List&lt;string&gt;</t>
+  </si>
+  <si>
     <t>퀘스트 ID (INT)</t>
   </si>
   <si>
@@ -3187,15 +3202,30 @@
     <t>조건 호감도</t>
   </si>
   <si>
+    <t>의뢰편지 키워드</t>
+  </si>
+  <si>
+    <t>의뢰 편지 제목</t>
+  </si>
+  <si>
     <t>의뢰편지 내용</t>
   </si>
   <si>
+    <t>하 성공 편지 제목</t>
+  </si>
+  <si>
     <t>만족도 하 요리를 받았을 때 (호감도만 오르고 보상 X)</t>
   </si>
   <si>
+    <t>중,상 성공 편지 제목</t>
+  </si>
+  <si>
     <t>성공편지 (만족도 중 이상 요리를 받았을 때)</t>
   </si>
   <si>
+    <t>실패 편지 제목</t>
+  </si>
+  <si>
     <t>실패편지</t>
   </si>
   <si>
@@ -3214,20 +3244,30 @@
     <t>따뜻한 국물</t>
   </si>
   <si>
-    <t>보양식 등급 이상 요리 제출</t>
-  </si>
-  <si>
-    <t>제목: “아픈 아이를 위한 따뜻한 한 그릇…”
-저희 집 막내가 며칠째 끙끙 앓고 있어요.
+    <t>죽 요리 제출</t>
+  </si>
+  <si>
+    <t>굴, 육수, 미역</t>
+  </si>
+  <si>
+    <t>아픈 아이를 위한 따뜻한 한 그릇…</t>
+  </si>
+  <si>
+    <t>저희 집 막내가 며칠째 끙끙 앓고 있어요.
 약도 좋지만… 역시 사람 살리는 건 따뜻한 국물 한 그릇 아닐까요?
 살림이 넉넉지 않아 자주 좋은 음식은 못 해주지만,
 오늘만큼은 아이가 속 편히 먹을 수 있는 든든한 보양식을 부탁드립니다.
-뜨끈하고 정성 가득한 국물요리,
-그 마음이 전해지면… 아이도 금세 나아질 거라 믿어요.</t>
-  </si>
-  <si>
-    <t>제목: “마음은 참 고마운데…”
-정성 들이신 건 느껴졌어요.
+혹시 가능하시다면, 굴과 육수로 만든 미역국,
+정성껏 끓여주실 수 있을까요?
+참고로, 육수 같은 조합 재료는 도감에서 확인하실 수 있어요.
+미역국이 아니어도, 그와 비슷한 전복이나 게를 사용한 따뜻하고 부드러운 죽 요리라면 괜찮아요.
+뜨끈하고 정성 가득한 그 한 그릇이, 아이에게 큰 힘이 될 거예요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 마음은 참 고마운데…</t>
+  </si>
+  <si>
+    <t>정성 들이신 건 느껴졌어요.
 아이도 조용히 한 숟갈씩 먹긴 했지요.
 다만… 조금만 더 따뜻했더라면,
 속까지 더 편안해졌을지도 모르겠어요.
@@ -3236,8 +3276,10 @@
 다시 부탁드려도 될까요?</t>
   </si>
   <si>
-    <t>제목: “마음이 따뜻해졌습니다”
-아이가 국물을 한 숟갈, 두 숟갈 조용히 떠먹더니
+    <t>마음이 따뜻해졌습니다</t>
+  </si>
+  <si>
+    <t>아이가 국물을 한 숟갈, 두 숟갈 조용히 떠먹더니
 오랜만에 웃음을 지었습니다.
 큰 기대 없이 부탁드렸는데…
 이렇게까지 정성껏 해주시다니 정말 감사합니다.
@@ -3246,8 +3288,10 @@
 부디 다음에도… 부탁드릴 수 있을까요?</t>
   </si>
   <si>
-    <t>제목: “아이에게 먹이긴 어려울 것 같아요…”
-정성껏 준비해주신 건 알겠어요.
+    <t>아이에게 먹이긴 어려울 것 같아요…</t>
+  </si>
+  <si>
+    <t>정성껏 준비해주신 건 알겠어요.
 하지만… 이건 아이가 먹기엔 조금 무거운 음식 같아요.
 저는… 속이 따뜻해지는 국물 요리를 원했답니다.
 죄송하지만, 이번 건 넘길게요.
@@ -3269,27 +3313,41 @@
     <t>귀한 재료</t>
   </si>
   <si>
-    <t>희귀 등급 이상 요리 제출</t>
-  </si>
-  <si>
-    <t>제목: “내 입은 아무 음식이나 안 받아”
-이 집 요리사 수준은 어떤가 좀 보자.
-나처럼 품격 있는 사람은 아무거나 못 먹거든?
-흔한 재료로 만든 투박한 음식? 그런 건 짐승 밥이지.
-나는 말이야, 귀하고 특별한 식재료가 들어간 요리만 먹는다고.
-보기에도 고급스럽고, 입에 넣자마자 감탄이 나올
-그런 수준의 음식을 기대할 테니, 실망시키지 말도록 해.</t>
-  </si>
-  <si>
-    <t>제목: “이걸… 나보고 먹으라고?”
-뭐, 굶는 것보단 낫겠지.
+    <t>고급 재료 사용 요리 제출</t>
+  </si>
+  <si>
+    <t>전복, 대게, 간장</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 내 입은 아무 음식이나 안 받아</t>
+  </si>
+  <si>
+    <t>이 집 요리사의 수준이 어느 정도인지… 좀 보자.
+나처럼 품격 있는 사람은 아무 음식이나 입에 못 대거든.
+흔한 재료로 만든 투박한 음식? 그건 짐승이나 먹는 거지.
+나는 전복이나 대게 같은 귀한 재료가 들어간,
+고급 회 요리만 먹는단 말이야.
+보기에도 화려하고, 입에 넣자마자 감탄이 나오는—
+그런 완벽한 요리를 기대하고 있을 테니, 실망시키지 마.
+물론, 간장에 콕 찍어 먹을 수 있는 회 요리여야겠지.
+기본이 안 되어 있으면 바로 실격이니까!
+뭐, 회 요리가 아니더라도 그 정도 격에 어울리는 조선 인삼을 이용한 고급 요리라면…
+한 번쯤은 봐줄 수도 있겠지.</t>
+  </si>
+  <si>
+    <t>이걸… 나보고 먹으라고?</t>
+  </si>
+  <si>
+    <t>뭐, 굶는 것보단 낫겠지.
 그래도 이 정도 수준으론 내 입맛을 맞추기엔 한참 멀었어.
 흠… 아주 실망까진 아니니까
 다음엔 좀 더 제대로 만들어보는 게 어때</t>
   </si>
   <si>
-    <t>제목: “그래, 이 정도면…”
-흠, 그럭저럭 먹을 만했군.
+    <t xml:space="preserve"> 그래, 이 정도면…</t>
+  </si>
+  <si>
+    <t>흠, 그럭저럭 먹을 만했군.
 솔직히 말해, 기대는 안 했거든.
 그런데 뭐랄까…
 입 안에서 감칠맛이 제법 괜찮게 감돌더군.
@@ -3298,8 +3356,10 @@
 특별히, 너한텐 줘도 괜찮을 것 같군.</t>
   </si>
   <si>
-    <t>제목: “내가 이런 걸 먹을 사람으로 보여?”
-허…
+    <t>내가 이런 걸 먹을 사람으로 보여?</t>
+  </si>
+  <si>
+    <t>허…
 이게 귀한 재료가 들어간 거라고 말하긴 좀 민망하군.
 내 입맛은 까다롭다고 말하지 않았던가?
 다시 말하지만,
@@ -3321,27 +3381,38 @@
     <t>국물 요리 제출</t>
   </si>
   <si>
-    <t>제목: “그 시절의 따뜻함을 다시 한 번…”
-요즘 들어 부쩍 몸도 마음도 지치네요.
-별다른 이유도 없이 눈물이 날 때가 있고…
-그런 날엔 어릴 적 어머니께서 만들어주시던 진한 요리가 생각나요.
-따뜻한 요리 한 숟갈에 마음까지 데워지던 그 시절처럼,
-속으로 스며들 듯 조용히 위로해주는 한 그릇,
-지금 제게 꼭 필요한 온기예요.
-혹시… 가능하다면,
-그 따뜻함을 담아 다시 만들어주실 수 있을까요?</t>
-  </si>
-  <si>
-    <t>제목: “괜찮았어요… 조금 아쉬웠지만”
-분명 정성은 느껴졌어요.
+    <t>감자, 두부, 된장국물 베이스</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 그 시절의 따뜻함을 다시 한 번…</t>
+  </si>
+  <si>
+    <t>요즘 들어 부쩍 몸도 마음도 지치네요.
+별다른 이유 없이 눈물이 날 때도 있고요…
+그런 날엔 어릴 적 어머니께서 끓여주시던 된장찌개가 생각나요.
+따뜻한 국물 한 숟갈에 마음까지 데워지던 그 시절처럼,
+속으로 스며들 듯 조용히 위로해주는 한 그릇이 지금의 저에겐 꼭 필요해요.
+감자와 두부가 들어간 된장찌개,
+그 따뜻함을 담아 다시 만들어주실 수 있을까요?
+참고로, 찌개에 들어갈 된장국물 베이스는 조합 재료 도감에서 확인할 수 있어요.
+그와 비슷한 따뜻한 콩나물과 김치를 이용한 국물 요리도 괜찮아요.
+중요한 건… 정성과 온기니까요.</t>
+  </si>
+  <si>
+    <t>괜찮았어요… 조금 아쉬웠지만</t>
+  </si>
+  <si>
+    <t>분명 정성은 느껴졌어요.
 그런데 제 마음까지는… 아직 닿지 않은 걸까요?
 따뜻하긴 했지만,
 어릴 적 어머니의 그 온기까지는 닿지 않았어요.
 다음엔 조금 더… 진한 국물, 기대해도 될까요?</t>
   </si>
   <si>
-    <t>제목: “진심이 전해졌어요”
-마음이 따뜻해졌어요.
+    <t>진심이 전해졌어요</t>
+  </si>
+  <si>
+    <t>마음이 따뜻해졌어요.
 오랜만에, 잊고 지낸 맛을 느낄 수 있었습니다.
 이렇게 진심이 담긴 요리를 만나게 해주셔서 정말 감사해요.
 예전에 어머니께서 정성껏 빚으신 간장이 있어요.
@@ -3350,8 +3421,10 @@
 부디 다음에도… 그 마음 그대로 전해주시길 바라요.</t>
   </si>
   <si>
-    <t>제목: “고마워요… 하지만 지금은 조금 다를 것 같아요”
-이 요리도 맛있어 보이긴 해요.
+    <t xml:space="preserve"> 고마워요… 하지만 지금은 조금 다를 것 같아요</t>
+  </si>
+  <si>
+    <t>이 요리도 맛있어 보이긴 해요.
 그런데 지금 제게 필요한 건…
 진하게 우러난 따뜻한 국물이었거든요.
 괜찮으시다면,
@@ -3376,18 +3449,28 @@
     <t>3재료 이상 조합 요리</t>
   </si>
   <si>
-    <t>제목: “이왕이면 제대로 좀 해봐”
-어휴, 요즘 집안 음식들이 다 거기서 거기야.
-똑같은 된장국, 고만고만한 반찬들… 질린다고.
+    <t>두부, 밀가루, 조림간장</t>
+  </si>
+  <si>
+    <t>이왕이면 제대로 좀 해봐</t>
+  </si>
+  <si>
+    <t>어휴, 요즘 집안 음식들이 다 거기서 거기야.
+똑같은 된장국에 고만고만한 반찬들… 솔직히 질렸어.
 조금은 특별한 요리, 그거 못 해?
-손이 많이 가도 맛만 있다면 용서해줄게.
-아주 평범한 요리는 솔직히 실망스러울 거고,
-그나마 정성은 들였구나 싶은 요리는 인정해줄 수도 있지.
-내 기준은 까다로우니까, 실망시키지 마!</t>
-  </si>
-  <si>
-    <t>제목: “…이걸 요리라고 한 거야?”
-어휴, 정성은 알겠는데…
+손이 좀 많이 가더라도, 맛만 있으면 용서해줄 테니까.
+평범한 건 싫어.
+두부랑 밀가루, 조림간장을 정성껏 조합해 만든 ‘두부 스테이크’ 정도는 돼야
+“그래, 이 정도면 정성 들였구나” 하고 봐줄 수 있지.
+내 기준은 꽤 까다롭거든. 실망시키지 마!
+뭐, 이처럼 재료 3가지를 정성껏 조합해서 만든 요리라면
+꼭 두부 스테이크가 아니더라도… 한 번쯤은 봐줄 수도 있어. 감자를 반죽해서 튀긴거라던지...</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> …이걸 요리라고 한 거야?</t>
+  </si>
+  <si>
+    <t>어휴, 정성은 알겠는데…
 너무 성의 없어 보이는 건 나만 그렇게 느낀 거야?
 뭐, 그럭저럭 입에 넣을 순 있었지만.
 다음엔 내가 말한 대로,
@@ -3395,16 +3478,20 @@
 이번 건 솔직히 아~주 아쉬웠어.</t>
   </si>
   <si>
-    <t>제목: “음, 이 정도면… 봐줄 만하네”
-뭐, 아주 마음에 들었다곤 안 했지만.
+    <t>음, 이 정도면… 봐줄 만하네</t>
+  </si>
+  <si>
+    <t>뭐, 아주 마음에 들었다곤 안 했지만.
 생각보다 제법 괜찮았달까?
 너 같은 사람이 이런 요리를 해냈다는 게… 의외였달까.
 고추장이 좀 남았는데 말야,
 이 정도면 보상으로 줄 만하지 않겠어?</t>
   </si>
   <si>
-    <t>제목: “이게 내 입에 들어갈 거라고 생각했어?”
-음… 간은 싱겁고, 조리법도 너무 단순하고…
+    <t>이게 내 입에 들어갈 거라고 생각했어?</t>
+  </si>
+  <si>
+    <t>음… 간은 싱겁고, 조리법도 너무 단순하고…
 대충 만든 티가 팍팍 나거든?
 나, 그런 거 입에도 안 대니까 알아둬.
 정~말 제대로 된 요리로 다시 와.
@@ -3426,34 +3513,49 @@
     <t>디저트류 요리 제출</t>
   </si>
   <si>
-    <t>제목: “달콤한 것이… 그리운 날이에요”
-문득,
+    <t>식수, 밤, 꿀</t>
+  </si>
+  <si>
+    <t>달콤한 것이… 그리운 날이에요</t>
+  </si>
+  <si>
+    <t>문득,
 하늘빛처럼 맑고 부드러운 맛이 그리워졌어요.
 지나간 기억이 스쳐가던 어느 날,
-조용히 입 안에 퍼지는 달콤함이 위로가 되었던 순간이 떠올랐죠.
+조용히 입 안에 퍼지던 달콤한 한 조각이
+마음을 위로해주던 순간이 떠올랐죠.
 복잡하지 않아도 괜찮아요.
-마음을 천천히 감싸주는 부드러운 맛,
-그 한 조각이 필요해요.</t>
-  </si>
-  <si>
-    <t>제목: “향긋하긴 했지만…”
-부드럽고 달콤한 향은 있었어요.
+밤에 식수와 꿀을 조려 만든 ‘밤조림’,
+그 부드럽고 따스한 맛이 지금의 저를 감싸주었으면 해요.
+혹시 밤조림이 어렵다면,
+마음을 천천히 감싸주는 듯한 주스나 디저트 같은 요리도 괜찮아요.
+중요한 건… 그 속에 담긴 따뜻한 마음이니까요.</t>
+  </si>
+  <si>
+    <t>향긋하긴 했지만…</t>
+  </si>
+  <si>
+    <t>부드럽고 달콤한 향은 있었어요.
 다만… 바람처럼 스쳐가는 맛이었달까요.
 오래 머물지 못했어요.
 다음엔,
 조금 더 깊고, 오래 기억에 남는 맛을 기다릴게요.</t>
   </si>
   <si>
-    <t>제목: “맑은 바람 같은 맛이었어요”
-그 요리를 입에 넣는 순간,
+    <t>맑은 바람 같은 맛이었어요</t>
+  </si>
+  <si>
+    <t>그 요리를 입에 넣는 순간,
 마치 하늘 아래 조용히 떠다니는 기분이었답니다.
 바람결처럼 맑고 부드러웠어요.
 저 아래 마을에서 얻은 소면 한 줌,
 다음 요리를 위해 가져가셔도 좋아요.</t>
   </si>
   <si>
-    <t>제목: “이건… 너무 무거워요”
-맛이 없진 않았어요.
+    <t>이건… 너무 무거워요</t>
+  </si>
+  <si>
+    <t>맛이 없진 않았어요.
 하지만 제가 원한 건… 달콤하고 부드러운 디저트였어요.
 오늘의 음식은 너무 기름지고,
 제겐 조금 버거운 맛이었답니다.
@@ -3478,25 +3580,40 @@
     <t>육류 포함 요리</t>
   </si>
   <si>
-    <t>제목: “크~ 고기 냄새 나는 날이 좋아!”
-내가 말이지… 풀만 먹고는 하루도 못 버텨!
+    <t>파, 고추 양념장, 고기</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 크~ 고기 냄새 나는 날이 좋아!</t>
+  </si>
+  <si>
+    <t>내가 말이지… 풀만 먹고는 하루도 못 버텨!
 기운 펄펄 나는 고기 요리, 그게 있어야 숨 좀 쉬겠다고!
-뭐… 요란한 거 말고,
-한입 딱 베어물면 쫙쫙 씹히는 그런 육즙 가득한 요리면 돼.
+뭐 요란할 필요는 없지.
+한입 딱 베어 물면 육즙 쫙쫙~ 씹는 맛 확실한
+그런 든든한 한 접시면 충분해.
+파와 고추 양념장, 푸짐한 고기를 넣고
+얼큰하게 볶아낸 고추장 제육볶음,
 으하하! 생각만 해도 군침이 도는구먼!
-배 든든하게 채워줄 야성적인 한 상, 기대할게!</t>
-  </si>
-  <si>
-    <t>제목: “으응… 뭔가 아쉬운데?”
-입에 넣자마자 뭔가…
+배 든든하게 채워줄 야성적인 한 상, 기대할게!
+아, 고추 양념장은 요리 도감에서 확인할 수 있으니 참고하라고!
+뭐, 제육볶음이 아니더라도 고기를 제대로 쓴 요리라면 다 좋지!
+내 입만 만족시켜준다면야, 인정이다! 껄껄!</t>
+  </si>
+  <si>
+    <t>으응… 뭔가 아쉬운데?</t>
+  </si>
+  <si>
+    <t>입에 넣자마자 뭔가…
 “어?” 했어. 고기 같은데, 고기 같은 게 아닌 느낌?
 배는 찼는데 마음은 좀 허하네~
 다음엔 확실하게!
 기름 좔좔~ 육즙 팡팡! 부탁 좀 해볼게~ 으허허!</t>
   </si>
   <si>
-    <t>제목: “으허허! 배 빵빵하다!”
-크~ 이게 바로 밥도둑이지 뭐냐!
+    <t xml:space="preserve"> 으허허! 배 빵빵하다!</t>
+  </si>
+  <si>
+    <t>크~ 이게 바로 밥도둑이지 뭐냐!
 고기 냄새가 코를 때리는 그 순간,
 나, 벌써 두 그릇째 퍼먹고 있었다니까!
 너한테 기름 한 병 줄게!
@@ -3504,8 +3621,10 @@
 다음엔 더 화끈한 고기 요리 기대할게! 으하하!</t>
   </si>
   <si>
-    <t>제목: “고기는… 없었잖아?”
-음… 맛은 나쁘지 않았어.
+    <t xml:space="preserve"> 고기는… 없었잖아?</t>
+  </si>
+  <si>
+    <t>음… 맛은 나쁘지 않았어.
 근데 말이야…
 나, 풀만 먹으면 배가 안 불러!!
 고기 들어간 거 달라니까~
@@ -3531,16 +3650,30 @@
     <t>풍미 가득한 요리</t>
   </si>
   <si>
-    <t>제목: “이 맛이야! 입에서 향이 가득차는 맛!”
-으아~ 요즘 먹는 게 너무 밍밍해!
-입 안에서 꽉차는 것 같은 풍미 가득한 맛, 그거 없어?
-평범한 건 사절이야. 도깨비 입맛은 좀 독특하거든?
-먹자마자 풍미가 가득한 향긋한 맛!
-너만 믿는다~ 얼른 만들어줘, 껄껄껄!</t>
-  </si>
-  <si>
-    <t>제목: “음… 이건 좀 심심한데?”
-킁킁… 어라?
+    <t>쑥, 두부, 된장국물 베이스</t>
+  </si>
+  <si>
+    <t>이 맛이야! 입에서 향이 가득차는 맛!</t>
+  </si>
+  <si>
+    <t>으아~ 요즘 먹는 게 너무 밍밍해!
+입 안에서 확! 퍼지는 풍미 가득한 맛… 그거 없어?
+평범한 건 사절! 도깨비 입맛은 좀 특별하거든?
+먹자마자 향긋하고 진한 맛이 훅! 하고 올라오는,
+그런 요리 아니면 실망할지도 몰라~ 껄껄껄!
+쑥과 두부, 그리고 된장국물 베이스로 만든 쑥 된장국,
+너라면 만들 수 있겠지? 너만 믿는다~! 얼른 뚝딱 해줘!
+아, 된장국물 베이스는 도감에서 확인할 수 있으니까
+까먹지 말고 꼭 참고하라고~!
+뭐, 쑥 된장국이 아니더라도 향이 강하게 확~ 느껴지는 요리라면
+도깨비 입맛에도 딱 맞을 테니 기대하고 있을게~!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">음… 이건 좀 심심한데?
+</t>
+  </si>
+  <si>
+    <t>킁킁… 어라?
 뭐지, 냄새가 안 나잖아?!
 나는 입안 가득 풍미가 퍼지는 그런 걸 기대했거든.
 오늘 건 그냥…아쉽다랄까...
@@ -3548,16 +3681,20 @@
 펑! 하고 터지는 향, 꼭 부탁해~ 알았지? 껄껄!</t>
   </si>
   <si>
-    <t>제목: “으하하! 이 맛이지~”
-이야~ 제대로 정신이 번쩍 들었어!
+    <t>으하하! 이 맛이지~</t>
+  </si>
+  <si>
+    <t>이야~ 제대로 정신이 번쩍 들었어!
 너, 꽤 하는구만?
 기분 좋아졌으니까 이 참기름 한 병 줄게!
 나도 아껴둔 건데… 너한텐 줘도 괜찮을 것 같아~
 다음엔 더 재미있는 맛 만들어줘!</t>
   </si>
   <si>
-    <t>제목: “이건 너무 얌전하잖아~”
-킁킁…
+    <t>이건 너무 얌전하잖아~</t>
+  </si>
+  <si>
+    <t>킁킁…
 에잇! 이건 향도 안 나고, 밍숭맹숭해!
 다음엔 내 입안에 펑!하고 가득차는 향으로,
 꼭 부탁할게. 이번 건 재미 없었어!</t>
@@ -3581,25 +3718,40 @@
     <t>채소만 사용된 요리</t>
   </si>
   <si>
-    <t>제목: “느릿느릿한 건 못 참아!”
-에휴, 무거운 음식은 딱 질색이야.
+    <t>콩나물, 간장 양념장, 참기름</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 느릿느릿한 건 못 참아!</t>
+  </si>
+  <si>
+    <t>에휴, 무거운 음식은 딱 질색이야.
 먹고 바로 뛰어야 하거든!
 채소 위주의 가볍고 산뜻한 요리,
-입 안에서 아삭아삭~ 씹히는 게 좋아!
+입 안에서 아삭아삭~ 씹히는 게 최고야!
 너무 기름지면 발이 안 떨어지니까,
-몸도 마음도 가볍게 해줄 음식, 부탁해!</t>
-  </si>
-  <si>
-    <t>제목: “음~ 가볍긴 한데… 
-맛은 있었어!
+몸도 마음도 가볍게 해줄 음식, 부탁할게!
+콩나물에 간장 양념장이랑 참기름을 넣고 조물조물 무친 콩나물 무침,
+딱 그런 느낌이지!
+아참, 간장 양념장 조합은 도감에서 확인할 수 있으니까
+까먹지 말고 꼭 챙겨봐!
+그리고 말인데, 이런 느낌의 아삭아삭한 채소 요리라면
+다른 메뉴도 얼마든지 환영이야! 기다리고 있을게~!</t>
+  </si>
+  <si>
+    <t>음~ 가볍긴 한데…</t>
+  </si>
+  <si>
+    <t>맛은 있었어!
 근데 뭔가 산뜻하지 않고 덜 아삭한 느낌?
 뛰긴 뛰었는데 몸이 좀 무겁더라고~!
 다음엔… 채소도 채소 나름이지!
 나 좀 감동시켜줘봐, 응?</t>
   </si>
   <si>
-    <t xml:space="preserve">제목: “오~ 가볍고 상쾌했어!”
-이 정도면 내 발이 붕붕 떠다니겠는걸?
+    <t xml:space="preserve"> 오~ 가볍고 상쾌했어!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 정도면 내 발이 붕붕 떠다니겠는걸?
 너무 무겁지도 않고,
 딱 내 스타일로 산뜻하게 빠졌어!
 혹시 모르지~ 다음엔 채소 댄스 파티 열어달라고 부탁할지도?
@@ -3607,12 +3759,13 @@
 꼭~ 맛있게 써줘야 해~? 약속! </t>
   </si>
   <si>
-    <t xml:space="preserve">제목: “이거 먹고 뛸 수 있을까…?”
-흠… 좀 무겁고 둔한 맛인데?
+    <t>이거 먹고 뛸 수 있을까…?</t>
+  </si>
+  <si>
+    <t>흠… 좀 무겁고 둔한 맛인데?
 내 발이 무거워질 것 같은 기분이야!
 다음엔 산뜻하고 아삭한 채소 요리로 부탁해줘~
-나, 느릿한 거 딱 질색이거든!
-</t>
+나, 느릿한 거 딱 질색이거든!</t>
   </si>
   <si>
     <t>104021, 104024, 104030</t>
@@ -3630,23 +3783,37 @@
     <t>X</t>
   </si>
   <si>
-    <t>제목: “서두를 필요는 없습니다…”
-좋은 음식은… 시간이 걸리기 마련이지요.
+    <t>배, 꿀</t>
+  </si>
+  <si>
+    <t>서두를 필요는 없습니다…</t>
+  </si>
+  <si>
+    <t>좋은 음식은… 시간이 걸리기 마련이지요.
 서두르지 말고, 천천히…
 속까지 스며드는 깊은 맛, 저는 그런 음식을 좋아합니다.
-그 느긋한 정취를 한 숟갈 가득 느끼고 싶군요.</t>
-  </si>
-  <si>
-    <t>제목: “조금 급했네요…”
-마음이 바쁘셨던 걸까요?
+그 느긋한 정취를 한 숟갈 가득 느끼고 싶군요.
+토막난 배와 배즙, 그리고 꿀을 넣고 천천히 끓여낸 ‘배숙’,
+바로 그런, 시간과 정성이 담긴 요리를 부탁드립니다.
+물론, 배숙이 아니더라도 천천히 정성 들여 만드는 국수 요리라면
+기꺼이 기다릴 수 있습니다.
+좋은 음식은 언제나, 기다림의 가치를 증명하니까요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 조금 급했네요…</t>
+  </si>
+  <si>
+    <t>마음이 바쁘셨던 걸까요?
 국물 맛이 조금 얕고… 아직 익지 않은 재료도 있었어요.
 저는 천천히, 오래 끓인 맛을 좋아해서요.
-다음엔… 시간과 마음을 더 담은 국물,
+다음엔… 시간과 마음을 더 담은 요리,
 기대해보겠습니다.</t>
   </si>
   <si>
-    <t>제목: “천천히, 그리고 깊게”
-맛이란…
+    <t xml:space="preserve"> 천천히, 그리고 깊게</t>
+  </si>
+  <si>
+    <t>맛이란…
 한입 베어 물자마자 알 수 있는 게 아니지요.
 오늘의 요리는 말입니다,
 먹을수록 조용히, 그리고 묵직하게 다가왔습니다.
@@ -3655,8 +3822,10 @@
 이 정성에 잘 어울리겠지요.</t>
   </si>
   <si>
-    <t>제목: “시간이 들지 않은 음식이군요…”
-급히 만든 음식 같네요.
+    <t>시간이 들지 않은 음식이군요…</t>
+  </si>
+  <si>
+    <t>급히 만든 음식 같네요.
 맛이… 아직 겉돌고 있었습니다.
 저는 오래 끓인 국물처럼,
 속까지 우러난 맛을 좋아합니다.
@@ -3681,26 +3850,40 @@
     <t>전통 종류의 요리</t>
   </si>
   <si>
-    <t>제목: “지나침보다 절제가 으뜸이라”
-요사이 음식이란 것이 지나치게 요란하니,
+    <t>문어, 육수, 무</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 지나침보다 절제가 으뜸이라</t>
+  </si>
+  <si>
+    <t>요사이 음식이란 것이 지나치게 요란하니,
 미각을 자극함은 있으되, 감동을 주진 못하는 법이오.
 나는 그대에게 정통 조선의 방식으로 빚어진,
 단순하나 깊고, 절제되었으나 정성스러운 음식을 청하오.
 허투루 만든 요리는 사양하겠소.
+문어와 육수, 그리고 무를 넣어 끓여낸 ‘문어 연포탕’,
+그 시대의 혼과 정성이 담긴 음식이라면 기꺼이 맛보겠소.
+참고로, 육수는 요리 도감에서 확인할 수 있으니 잊지 마시오.
+물론, 문어 연포탕이 아니더라도 조선의 정신이 느껴지는
+탕이나 국수 요리라면 마다하지 않겠소.
 오직, 그 시대의 정신이 담긴 요리만이
 진정한 맛이라 이를 수 있을 것이외다.</t>
   </si>
   <si>
-    <t>제목: “절제와 빈약함은 다르오”
-간결함과 허전함은, 닮은 듯 다르지요.
+    <t xml:space="preserve"> 절제와 빈약함은 다르오</t>
+  </si>
+  <si>
+    <t>간결함과 허전함은, 닮은 듯 다르지요.
 오늘 요리는 후자에 가까웠소.
 무언가 한 줌 더 보탰더라면… 하는 아쉬움이 남았소이다.
 그럼에도 정성은 느껴졌으니,
 다음엔 더욱 고심한 조선의 맛을 부탁드리오.</t>
   </si>
   <si>
-    <t>제목: “절제 속 깊이”
-넘치지 않았고,
+    <t xml:space="preserve"> 절제 속 깊이</t>
+  </si>
+  <si>
+    <t>넘치지 않았고,
 부족하지도 않았소.
 그 요리에는 조선의 정신,
 즉 절제된 정성과 깊은 풍미가 깃들어 있었소.
@@ -3709,8 +3892,10 @@
 부디, 이 또한 다음 요리에 품위 있게 사용해 주시길 바라오.</t>
   </si>
   <si>
-    <t>제목: “조선의 맛과는 거리가 있군요”
-오늘 요리는,
+    <t>조선의 맛과는 거리가 있군요</t>
+  </si>
+  <si>
+    <t>오늘 요리는,
 형식만 갖췄을 뿐 정신은 담기지 않았습니다.
 조선의 맛이란,
 절제된 깊이와 정성이 깃든 구조이니,
@@ -3795,9 +3980,6 @@
     <t>국물에 넣으면 시원함 2배. 단단하지만 부드러운 채소. 무 없인 국도 울고 간다.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>기운이 뻗치고도 남는 귀한 약초. 산삼이 부러워하는 양반 인삼.</t>
   </si>
   <si>
@@ -3951,9 +4133,6 @@
     <t>ingredientsName</t>
   </si>
   <si>
-    <t>List&lt;string&gt;</t>
-  </si>
-  <si>
     <t>음식군ID</t>
   </si>
   <si>
@@ -4011,7 +4190,7 @@
     <t>보이지 않지만 모든 맛의 뼈대. 멸치, 마늘, 물이 만든 숨겨진 조력자.</t>
   </si>
   <si>
-    <t>고추양념장, 된장, 식수</t>
+    <t>고추 양념장, 된장, 식수</t>
   </si>
   <si>
     <t>바다의 맛을 농축한 진한 국물의 정수. 어떠한 재료도 기꺼이 몸을 담근다.</t>
@@ -4055,7 +4234,7 @@
 몸을 깨우는 구이 한 점, 건강한 불맛의 정수.</t>
   </si>
   <si>
-    <t>썰린 두부, 고추양념장</t>
+    <t>썰린 두부, 고추 양념장</t>
   </si>
   <si>
     <t>두툼한 두부에 양념이 쏙쏙!
@@ -4151,7 +4330,7 @@
 든든하면서도 깔끔한 한 끼.</t>
   </si>
   <si>
-    <t>파채, 고추양념장, 삶은 고기</t>
+    <t>파채, 고추 양념장, 삶은 고기</t>
   </si>
   <si>
     <t>매콤달콤 고추장 양념이 밥을 부른다!
@@ -4295,7 +4474,7 @@
 골라 먹는 재미도 쏠쏠하다.</t>
   </si>
   <si>
-    <t>썰린 두부, 밀가루 반죽, 조림간장</t>
+    <t>썰린 두부, 밀가루, 조림간장</t>
   </si>
   <si>
     <t>담백한 두부를 고기처럼 구워낸 웰빙 요리.
@@ -4303,7 +4482,7 @@
 다이어터에게도 인기만점.</t>
   </si>
   <si>
-    <t>으깬 감자, 튀김반죽, 뜨거운 식용유</t>
+    <t>으깬 감자, 밀가루, 뜨거운 식용유</t>
   </si>
   <si>
     <t>부드러운 감자 속에 바삭한 튀김옷.
@@ -15310,6 +15489,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4777B2FE-C94E-4C26-BD4C-C0D8BBFEF080}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -15319,16 +15501,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1225</v>
+        <v>1284</v>
       </c>
       <c r="D1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E1" t="s">
-        <v>1226</v>
+        <v>1285</v>
       </c>
       <c r="F1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15345,7 +15527,7 @@
         <v>824</v>
       </c>
       <c r="E2" t="s">
-        <v>1227</v>
+        <v>1045</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -15353,22 +15535,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1228</v>
+        <v>1286</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1229</v>
+        <v>1287</v>
       </c>
       <c r="D3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E3" t="s">
-        <v>1230</v>
+        <v>1288</v>
       </c>
       <c r="F3" t="s">
-        <v>1159</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15382,13 +15564,13 @@
         <v>392</v>
       </c>
       <c r="D4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E4" t="s">
-        <v>1231</v>
+        <v>1289</v>
       </c>
       <c r="F4" t="s">
-        <v>1232</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15402,13 +15584,13 @@
         <v>400</v>
       </c>
       <c r="D5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E5" t="s">
-        <v>1233</v>
+        <v>1291</v>
       </c>
       <c r="F5" t="s">
-        <v>1234</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15422,13 +15604,13 @@
         <v>408</v>
       </c>
       <c r="D6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E6" t="s">
-        <v>1235</v>
+        <v>1293</v>
       </c>
       <c r="F6" t="s">
-        <v>1236</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15442,13 +15624,13 @@
         <v>412</v>
       </c>
       <c r="D7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E7" t="s">
-        <v>1237</v>
+        <v>1295</v>
       </c>
       <c r="F7" t="s">
-        <v>1238</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15462,13 +15644,13 @@
         <v>416</v>
       </c>
       <c r="D8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E8" t="s">
-        <v>1239</v>
+        <v>1297</v>
       </c>
       <c r="F8" t="s">
-        <v>1240</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15482,13 +15664,13 @@
         <v>420</v>
       </c>
       <c r="D9" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E9" t="s">
-        <v>1241</v>
+        <v>1299</v>
       </c>
       <c r="F9" t="s">
-        <v>1242</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15502,13 +15684,13 @@
         <v>424</v>
       </c>
       <c r="D10" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E10" t="s">
-        <v>1243</v>
+        <v>1301</v>
       </c>
       <c r="F10" t="s">
-        <v>1244</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15522,13 +15704,13 @@
         <v>428</v>
       </c>
       <c r="D11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E11" t="s">
-        <v>1245</v>
+        <v>1303</v>
       </c>
       <c r="F11" t="s">
-        <v>1246</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15542,13 +15724,13 @@
         <v>432</v>
       </c>
       <c r="D12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E12" t="s">
-        <v>1247</v>
+        <v>1305</v>
       </c>
       <c r="F12" t="s">
-        <v>1248</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15562,13 +15744,13 @@
         <v>436</v>
       </c>
       <c r="D13" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E13" t="s">
-        <v>1249</v>
+        <v>1307</v>
       </c>
       <c r="F13" t="s">
-        <v>1250</v>
+        <v>1308</v>
       </c>
     </row>
   </sheetData>
@@ -15589,16 +15771,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1225</v>
+        <v>1284</v>
       </c>
       <c r="D1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E1" t="s">
-        <v>1226</v>
+        <v>1285</v>
       </c>
       <c r="F1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15615,7 +15797,7 @@
         <v>824</v>
       </c>
       <c r="E2" t="s">
-        <v>1227</v>
+        <v>1045</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -15623,22 +15805,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1228</v>
+        <v>1286</v>
       </c>
       <c r="B3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C3" t="s">
-        <v>1229</v>
+        <v>1287</v>
       </c>
       <c r="D3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E3" t="s">
-        <v>1230</v>
+        <v>1288</v>
       </c>
       <c r="F3" t="s">
-        <v>1159</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15652,13 +15834,13 @@
         <v>471</v>
       </c>
       <c r="D4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E4" t="s">
-        <v>1251</v>
+        <v>1309</v>
       </c>
       <c r="F4" t="s">
-        <v>1252</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15672,13 +15854,13 @@
         <v>475</v>
       </c>
       <c r="D5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E5" t="s">
-        <v>1253</v>
+        <v>1311</v>
       </c>
       <c r="F5" t="s">
-        <v>1254</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15692,13 +15874,13 @@
         <v>479</v>
       </c>
       <c r="D6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E6" t="s">
-        <v>1255</v>
+        <v>1313</v>
       </c>
       <c r="F6" t="s">
-        <v>1256</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15712,13 +15894,13 @@
         <v>483</v>
       </c>
       <c r="D7" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E7" t="s">
-        <v>1257</v>
+        <v>1315</v>
       </c>
       <c r="F7" t="s">
-        <v>1258</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15732,13 +15914,13 @@
         <v>487</v>
       </c>
       <c r="D8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E8" t="s">
-        <v>1259</v>
+        <v>1317</v>
       </c>
       <c r="F8" t="s">
-        <v>1260</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15746,19 +15928,19 @@
         <v>110506</v>
       </c>
       <c r="B9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C9" t="s">
         <v>491</v>
       </c>
       <c r="D9" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E9" t="s">
-        <v>1261</v>
+        <v>1319</v>
       </c>
       <c r="F9" t="s">
-        <v>1262</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15772,13 +15954,13 @@
         <v>495</v>
       </c>
       <c r="D10" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E10" t="s">
-        <v>1263</v>
+        <v>1321</v>
       </c>
       <c r="F10" t="s">
-        <v>1264</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15792,13 +15974,13 @@
         <v>499</v>
       </c>
       <c r="D11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E11" t="s">
-        <v>1265</v>
+        <v>1323</v>
       </c>
       <c r="F11" t="s">
-        <v>1266</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15812,13 +15994,13 @@
         <v>503</v>
       </c>
       <c r="D12" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E12" t="s">
-        <v>1267</v>
+        <v>1325</v>
       </c>
       <c r="F12" t="s">
-        <v>1268</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15832,13 +16014,13 @@
         <v>507</v>
       </c>
       <c r="D13" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E13" t="s">
-        <v>1269</v>
+        <v>1327</v>
       </c>
       <c r="F13" t="s">
-        <v>1270</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15852,13 +16034,13 @@
         <v>511</v>
       </c>
       <c r="D14" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E14" t="s">
-        <v>1271</v>
+        <v>1329</v>
       </c>
       <c r="F14" t="s">
-        <v>1272</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15872,13 +16054,13 @@
         <v>515</v>
       </c>
       <c r="D15" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E15" t="s">
-        <v>1273</v>
+        <v>1331</v>
       </c>
       <c r="F15" t="s">
-        <v>1274</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15892,13 +16074,13 @@
         <v>519</v>
       </c>
       <c r="D16" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E16" t="s">
-        <v>1275</v>
+        <v>1333</v>
       </c>
       <c r="F16" t="s">
-        <v>1276</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -15912,13 +16094,13 @@
         <v>523</v>
       </c>
       <c r="D17" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E17" t="s">
-        <v>1277</v>
+        <v>1335</v>
       </c>
       <c r="F17" t="s">
-        <v>1278</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15932,13 +16114,13 @@
         <v>527</v>
       </c>
       <c r="D18" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E18" t="s">
-        <v>1279</v>
+        <v>1337</v>
       </c>
       <c r="F18" t="s">
-        <v>1280</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -15952,13 +16134,13 @@
         <v>531</v>
       </c>
       <c r="D19" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E19" t="s">
-        <v>1281</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="s">
-        <v>1282</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -15972,13 +16154,13 @@
         <v>535</v>
       </c>
       <c r="D20" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E20" t="s">
-        <v>1283</v>
+        <v>1341</v>
       </c>
       <c r="F20" t="s">
-        <v>1284</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -15992,13 +16174,13 @@
         <v>539</v>
       </c>
       <c r="D21" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E21" t="s">
-        <v>1285</v>
+        <v>1343</v>
       </c>
       <c r="F21" t="s">
-        <v>1286</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -16012,13 +16194,13 @@
         <v>543</v>
       </c>
       <c r="D22" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E22" t="s">
-        <v>1287</v>
+        <v>1345</v>
       </c>
       <c r="F22" t="s">
-        <v>1288</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -16032,13 +16214,13 @@
         <v>547</v>
       </c>
       <c r="D23" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E23" t="s">
-        <v>1289</v>
+        <v>1347</v>
       </c>
       <c r="F23" t="s">
-        <v>1290</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -16052,13 +16234,13 @@
         <v>551</v>
       </c>
       <c r="D24" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E24" t="s">
-        <v>1291</v>
+        <v>1349</v>
       </c>
       <c r="F24" t="s">
-        <v>1292</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -16072,13 +16254,13 @@
         <v>555</v>
       </c>
       <c r="D25" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E25" t="s">
-        <v>1293</v>
+        <v>1351</v>
       </c>
       <c r="F25" t="s">
-        <v>1294</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -16092,13 +16274,13 @@
         <v>559</v>
       </c>
       <c r="D26" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E26" t="s">
-        <v>1295</v>
+        <v>1353</v>
       </c>
       <c r="F26" t="s">
-        <v>1296</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -16112,13 +16294,13 @@
         <v>563</v>
       </c>
       <c r="D27" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E27" t="s">
-        <v>1297</v>
+        <v>1355</v>
       </c>
       <c r="F27" t="s">
-        <v>1298</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -16126,19 +16308,19 @@
         <v>110525</v>
       </c>
       <c r="B28" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C28" t="s">
         <v>567</v>
       </c>
       <c r="D28" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E28" t="s">
-        <v>1299</v>
+        <v>1357</v>
       </c>
       <c r="F28" t="s">
-        <v>1300</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -16152,13 +16334,13 @@
         <v>571</v>
       </c>
       <c r="D29" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E29" t="s">
-        <v>1301</v>
+        <v>1359</v>
       </c>
       <c r="F29" t="s">
-        <v>1302</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -16172,13 +16354,13 @@
         <v>575</v>
       </c>
       <c r="D30" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E30" t="s">
-        <v>1303</v>
+        <v>1361</v>
       </c>
       <c r="F30" t="s">
-        <v>1304</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -16192,13 +16374,13 @@
         <v>579</v>
       </c>
       <c r="D31" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E31" t="s">
-        <v>1305</v>
+        <v>1363</v>
       </c>
       <c r="F31" t="s">
-        <v>1306</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -16212,13 +16394,13 @@
         <v>583</v>
       </c>
       <c r="D32" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E32" t="s">
-        <v>1307</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="s">
-        <v>1308</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -16232,13 +16414,13 @@
         <v>587</v>
       </c>
       <c r="D33" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E33" t="s">
-        <v>1309</v>
+        <v>1367</v>
       </c>
       <c r="F33" t="s">
-        <v>1310</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -16252,13 +16434,13 @@
         <v>591</v>
       </c>
       <c r="D34" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E34" t="s">
-        <v>1311</v>
+        <v>1369</v>
       </c>
       <c r="F34" t="s">
-        <v>1312</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -16272,13 +16454,13 @@
         <v>595</v>
       </c>
       <c r="D35" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E35" t="s">
-        <v>1313</v>
+        <v>1371</v>
       </c>
       <c r="F35" t="s">
-        <v>1314</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -16292,13 +16474,13 @@
         <v>599</v>
       </c>
       <c r="D36" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E36" t="s">
-        <v>1315</v>
+        <v>1373</v>
       </c>
       <c r="F36" t="s">
-        <v>1316</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -16312,13 +16494,13 @@
         <v>603</v>
       </c>
       <c r="D37" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E37" t="s">
-        <v>1317</v>
+        <v>1375</v>
       </c>
       <c r="F37" t="s">
-        <v>1318</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -16332,13 +16514,13 @@
         <v>607</v>
       </c>
       <c r="D38" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E38" t="s">
-        <v>1319</v>
+        <v>1377</v>
       </c>
       <c r="F38" t="s">
-        <v>1320</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -16352,13 +16534,13 @@
         <v>611</v>
       </c>
       <c r="D39" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E39" t="s">
-        <v>1321</v>
+        <v>1379</v>
       </c>
       <c r="F39" t="s">
-        <v>1322</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -16372,13 +16554,13 @@
         <v>615</v>
       </c>
       <c r="D40" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E40" t="s">
-        <v>1323</v>
+        <v>1381</v>
       </c>
       <c r="F40" t="s">
-        <v>1324</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -16392,13 +16574,13 @@
         <v>619</v>
       </c>
       <c r="D41" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E41" t="s">
-        <v>1325</v>
+        <v>1383</v>
       </c>
       <c r="F41" t="s">
-        <v>1326</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -16412,13 +16594,13 @@
         <v>623</v>
       </c>
       <c r="D42" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E42" t="s">
-        <v>1327</v>
+        <v>1385</v>
       </c>
       <c r="F42" t="s">
-        <v>1328</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -16432,13 +16614,13 @@
         <v>627</v>
       </c>
       <c r="D43" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E43" t="s">
-        <v>1329</v>
+        <v>1387</v>
       </c>
       <c r="F43" t="s">
-        <v>1330</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -16452,13 +16634,13 @@
         <v>631</v>
       </c>
       <c r="D44" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E44" t="s">
-        <v>1331</v>
+        <v>1389</v>
       </c>
       <c r="F44" t="s">
-        <v>1332</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -16472,13 +16654,13 @@
         <v>635</v>
       </c>
       <c r="D45" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E45" t="s">
-        <v>1333</v>
+        <v>1391</v>
       </c>
       <c r="F45" t="s">
-        <v>1334</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -16492,13 +16674,13 @@
         <v>639</v>
       </c>
       <c r="D46" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E46" t="s">
-        <v>1335</v>
+        <v>1393</v>
       </c>
       <c r="F46" t="s">
-        <v>1336</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -16512,13 +16694,13 @@
         <v>643</v>
       </c>
       <c r="D47" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E47" t="s">
-        <v>1337</v>
+        <v>1395</v>
       </c>
       <c r="F47" t="s">
-        <v>1338</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -16532,13 +16714,13 @@
         <v>647</v>
       </c>
       <c r="D48" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E48" t="s">
-        <v>1339</v>
+        <v>1397</v>
       </c>
       <c r="F48" t="s">
-        <v>1340</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -16552,13 +16734,13 @@
         <v>651</v>
       </c>
       <c r="D49" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E49" t="s">
-        <v>1341</v>
+        <v>1399</v>
       </c>
       <c r="F49" t="s">
-        <v>1342</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -16572,13 +16754,13 @@
         <v>655</v>
       </c>
       <c r="D50" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E50" t="s">
-        <v>1343</v>
+        <v>1401</v>
       </c>
       <c r="F50" t="s">
-        <v>1344</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -16592,13 +16774,13 @@
         <v>659</v>
       </c>
       <c r="D51" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E51" t="s">
-        <v>1345</v>
+        <v>1403</v>
       </c>
       <c r="F51" t="s">
-        <v>1346</v>
+        <v>1404</v>
       </c>
     </row>
   </sheetData>
@@ -18181,7 +18363,7 @@
         <v>101</v>
       </c>
       <c r="J49">
-        <v>601008</v>
+        <v>601009</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -23118,8 +23300,8 @@
       <c r="E31" t="s">
         <v>836</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>845</v>
+      <c r="F31" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -23173,7 +23355,7 @@
         <v>835</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -23192,8 +23374,8 @@
       <c r="E35" t="s">
         <v>836</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>845</v>
+      <c r="F35" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -23201,7 +23383,7 @@
         <v>200033</v>
       </c>
       <c r="B36" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C36" t="s">
         <v>831</v>
@@ -23218,7 +23400,7 @@
         <v>200034</v>
       </c>
       <c r="B37" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C37" t="s">
         <v>831</v>
@@ -23235,7 +23417,7 @@
         <v>200035</v>
       </c>
       <c r="B38" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C38" t="s">
         <v>831</v>
@@ -23255,7 +23437,7 @@
         <v>200036</v>
       </c>
       <c r="B39" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C39" t="s">
         <v>831</v>
@@ -23275,7 +23457,7 @@
         <v>200037</v>
       </c>
       <c r="B40" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C40" t="s">
         <v>831</v>
@@ -23292,7 +23474,7 @@
         <v>200038</v>
       </c>
       <c r="B41" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C41" t="s">
         <v>831</v>
@@ -23309,7 +23491,7 @@
         <v>200039</v>
       </c>
       <c r="B42" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C42" t="s">
         <v>831</v>
@@ -23326,7 +23508,7 @@
         <v>200040</v>
       </c>
       <c r="B43" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C43" t="s">
         <v>831</v>
@@ -23346,7 +23528,7 @@
         <v>200041</v>
       </c>
       <c r="B44" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C44" t="s">
         <v>831</v>
@@ -23363,7 +23545,7 @@
         <v>200042</v>
       </c>
       <c r="B45" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C45" t="s">
         <v>831</v>
@@ -23380,7 +23562,7 @@
         <v>200043</v>
       </c>
       <c r="B46" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C46" t="s">
         <v>831</v>
@@ -23400,7 +23582,7 @@
         <v>200044</v>
       </c>
       <c r="B47" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C47" t="s">
         <v>831</v>
@@ -23420,7 +23602,7 @@
         <v>200045</v>
       </c>
       <c r="B48" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C48" t="s">
         <v>831</v>
@@ -23440,7 +23622,7 @@
         <v>200046</v>
       </c>
       <c r="B49" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C49" t="s">
         <v>831</v>
@@ -23457,7 +23639,7 @@
         <v>200047</v>
       </c>
       <c r="B50" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C50" t="s">
         <v>831</v>
@@ -23477,7 +23659,7 @@
         <v>200048</v>
       </c>
       <c r="B51" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C51" t="s">
         <v>831</v>
@@ -23494,7 +23676,7 @@
         <v>200049</v>
       </c>
       <c r="B52" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C52" t="s">
         <v>842</v>
@@ -23511,7 +23693,7 @@
         <v>200050</v>
       </c>
       <c r="B53" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C53" t="s">
         <v>842</v>
@@ -23528,7 +23710,7 @@
         <v>200051</v>
       </c>
       <c r="B54" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C54" t="s">
         <v>842</v>
@@ -23545,7 +23727,7 @@
         <v>200052</v>
       </c>
       <c r="B55" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C55" t="s">
         <v>842</v>
@@ -23557,7 +23739,7 @@
         <v>836</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -23565,7 +23747,7 @@
         <v>200053</v>
       </c>
       <c r="B56" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C56" t="s">
         <v>842</v>
@@ -23582,7 +23764,7 @@
         <v>200054</v>
       </c>
       <c r="B57" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C57" t="s">
         <v>842</v>
@@ -23602,7 +23784,7 @@
         <v>200055</v>
       </c>
       <c r="B58" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C58" t="s">
         <v>842</v>
@@ -23619,7 +23801,7 @@
         <v>200056</v>
       </c>
       <c r="B59" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C59" t="s">
         <v>842</v>
@@ -23631,7 +23813,7 @@
         <v>836</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -23639,7 +23821,7 @@
         <v>200057</v>
       </c>
       <c r="B60" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C60" t="s">
         <v>842</v>
@@ -23659,7 +23841,7 @@
         <v>200058</v>
       </c>
       <c r="B61" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C61" t="s">
         <v>842</v>
@@ -23679,7 +23861,7 @@
         <v>200059</v>
       </c>
       <c r="B62" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C62" t="s">
         <v>842</v>
@@ -23699,7 +23881,7 @@
         <v>200060</v>
       </c>
       <c r="B63" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C63" t="s">
         <v>842</v>
@@ -23711,7 +23893,7 @@
         <v>836</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -23719,7 +23901,7 @@
         <v>200061</v>
       </c>
       <c r="B64" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C64" t="s">
         <v>842</v>
@@ -23736,7 +23918,7 @@
         <v>200062</v>
       </c>
       <c r="B65" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C65" t="s">
         <v>842</v>
@@ -23753,7 +23935,7 @@
         <v>200063</v>
       </c>
       <c r="B66" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C66" t="s">
         <v>842</v>
@@ -23773,7 +23955,7 @@
         <v>200064</v>
       </c>
       <c r="B67" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C67" t="s">
         <v>842</v>
@@ -23784,8 +23966,8 @@
       <c r="E67" t="s">
         <v>836</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>845</v>
+      <c r="F67" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -23793,7 +23975,7 @@
         <v>200065</v>
       </c>
       <c r="B68" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C68" t="s">
         <v>831</v>
@@ -23810,7 +23992,7 @@
         <v>200066</v>
       </c>
       <c r="B69" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C69" t="s">
         <v>831</v>
@@ -23827,7 +24009,7 @@
         <v>200067</v>
       </c>
       <c r="B70" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C70" t="s">
         <v>831</v>
@@ -23847,7 +24029,7 @@
         <v>200068</v>
       </c>
       <c r="B71" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C71" t="s">
         <v>831</v>
@@ -23867,7 +24049,7 @@
         <v>200069</v>
       </c>
       <c r="B72" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C72" t="s">
         <v>831</v>
@@ -23887,7 +24069,7 @@
         <v>200070</v>
       </c>
       <c r="B73" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C73" t="s">
         <v>831</v>
@@ -23904,7 +24086,7 @@
         <v>200071</v>
       </c>
       <c r="B74" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C74" t="s">
         <v>831</v>
@@ -23924,7 +24106,7 @@
         <v>200072</v>
       </c>
       <c r="B75" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C75" t="s">
         <v>831</v>
@@ -23944,7 +24126,7 @@
         <v>200073</v>
       </c>
       <c r="B76" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C76" t="s">
         <v>831</v>
@@ -23961,7 +24143,7 @@
         <v>200074</v>
       </c>
       <c r="B77" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C77" t="s">
         <v>831</v>
@@ -23978,7 +24160,7 @@
         <v>200075</v>
       </c>
       <c r="B78" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C78" t="s">
         <v>831</v>
@@ -23998,7 +24180,7 @@
         <v>200076</v>
       </c>
       <c r="B79" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C79" t="s">
         <v>831</v>
@@ -24018,7 +24200,7 @@
         <v>200077</v>
       </c>
       <c r="B80" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C80" t="s">
         <v>831</v>
@@ -24035,7 +24217,7 @@
         <v>200078</v>
       </c>
       <c r="B81" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C81" t="s">
         <v>831</v>
@@ -24052,7 +24234,7 @@
         <v>200079</v>
       </c>
       <c r="B82" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C82" t="s">
         <v>831</v>
@@ -24072,7 +24254,7 @@
         <v>200080</v>
       </c>
       <c r="B83" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C83" t="s">
         <v>831</v>
@@ -24089,7 +24271,7 @@
         <v>200081</v>
       </c>
       <c r="B84" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C84" t="s">
         <v>842</v>
@@ -24106,7 +24288,7 @@
         <v>200082</v>
       </c>
       <c r="B85" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C85" t="s">
         <v>842</v>
@@ -24123,7 +24305,7 @@
         <v>200083</v>
       </c>
       <c r="B86" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C86" t="s">
         <v>842</v>
@@ -24143,7 +24325,7 @@
         <v>200084</v>
       </c>
       <c r="B87" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C87" t="s">
         <v>842</v>
@@ -24154,8 +24336,8 @@
       <c r="E87" t="s">
         <v>836</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>845</v>
+      <c r="F87" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -24163,7 +24345,7 @@
         <v>200085</v>
       </c>
       <c r="B88" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C88" t="s">
         <v>842</v>
@@ -24180,7 +24362,7 @@
         <v>200086</v>
       </c>
       <c r="B89" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C89" t="s">
         <v>842</v>
@@ -24197,7 +24379,7 @@
         <v>200087</v>
       </c>
       <c r="B90" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C90" t="s">
         <v>842</v>
@@ -24217,7 +24399,7 @@
         <v>200088</v>
       </c>
       <c r="B91" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C91" t="s">
         <v>842</v>
@@ -24228,8 +24410,8 @@
       <c r="E91" t="s">
         <v>836</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>845</v>
+      <c r="F91" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -24237,7 +24419,7 @@
         <v>200089</v>
       </c>
       <c r="B92" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C92" t="s">
         <v>842</v>
@@ -24254,7 +24436,7 @@
         <v>200090</v>
       </c>
       <c r="B93" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C93" t="s">
         <v>842</v>
@@ -24274,7 +24456,7 @@
         <v>200091</v>
       </c>
       <c r="B94" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C94" t="s">
         <v>842</v>
@@ -24286,7 +24468,7 @@
         <v>835</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -24294,7 +24476,7 @@
         <v>200092</v>
       </c>
       <c r="B95" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C95" t="s">
         <v>842</v>
@@ -24305,8 +24487,8 @@
       <c r="E95" t="s">
         <v>836</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>845</v>
+      <c r="F95" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -24314,7 +24496,7 @@
         <v>200093</v>
       </c>
       <c r="B96" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C96" t="s">
         <v>842</v>
@@ -24331,7 +24513,7 @@
         <v>200094</v>
       </c>
       <c r="B97" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C97" t="s">
         <v>842</v>
@@ -24351,7 +24533,7 @@
         <v>200095</v>
       </c>
       <c r="B98" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C98" t="s">
         <v>842</v>
@@ -24363,7 +24545,7 @@
         <v>835</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -24371,7 +24553,7 @@
         <v>200096</v>
       </c>
       <c r="B99" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C99" t="s">
         <v>842</v>
@@ -24382,8 +24564,8 @@
       <c r="E99" t="s">
         <v>836</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>845</v>
+      <c r="F99" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -24391,7 +24573,7 @@
         <v>200097</v>
       </c>
       <c r="B100" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C100" t="s">
         <v>831</v>
@@ -24408,7 +24590,7 @@
         <v>200098</v>
       </c>
       <c r="B101" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C101" t="s">
         <v>831</v>
@@ -24428,7 +24610,7 @@
         <v>200099</v>
       </c>
       <c r="B102" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C102" t="s">
         <v>831</v>
@@ -24445,7 +24627,7 @@
         <v>200100</v>
       </c>
       <c r="B103" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C103" t="s">
         <v>831</v>
@@ -24465,7 +24647,7 @@
         <v>200101</v>
       </c>
       <c r="B104" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C104" t="s">
         <v>831</v>
@@ -24482,7 +24664,7 @@
         <v>200102</v>
       </c>
       <c r="B105" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C105" t="s">
         <v>831</v>
@@ -24502,7 +24684,7 @@
         <v>200103</v>
       </c>
       <c r="B106" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C106" t="s">
         <v>831</v>
@@ -24519,7 +24701,7 @@
         <v>200104</v>
       </c>
       <c r="B107" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C107" t="s">
         <v>831</v>
@@ -24539,7 +24721,7 @@
         <v>200105</v>
       </c>
       <c r="B108" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C108" t="s">
         <v>831</v>
@@ -24556,7 +24738,7 @@
         <v>200106</v>
       </c>
       <c r="B109" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C109" t="s">
         <v>831</v>
@@ -24573,7 +24755,7 @@
         <v>200107</v>
       </c>
       <c r="B110" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C110" t="s">
         <v>831</v>
@@ -24593,7 +24775,7 @@
         <v>200108</v>
       </c>
       <c r="B111" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C111" t="s">
         <v>831</v>
@@ -24613,7 +24795,7 @@
         <v>200109</v>
       </c>
       <c r="B112" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C112" t="s">
         <v>831</v>
@@ -24630,7 +24812,7 @@
         <v>200110</v>
       </c>
       <c r="B113" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C113" t="s">
         <v>831</v>
@@ -24647,7 +24829,7 @@
         <v>200111</v>
       </c>
       <c r="B114" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C114" t="s">
         <v>831</v>
@@ -24667,7 +24849,7 @@
         <v>200112</v>
       </c>
       <c r="B115" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C115" t="s">
         <v>831</v>
@@ -24684,7 +24866,7 @@
         <v>200113</v>
       </c>
       <c r="B116" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C116" t="s">
         <v>842</v>
@@ -24701,7 +24883,7 @@
         <v>200114</v>
       </c>
       <c r="B117" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C117" t="s">
         <v>842</v>
@@ -24713,7 +24895,7 @@
         <v>834</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -24721,7 +24903,7 @@
         <v>200115</v>
       </c>
       <c r="B118" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C118" t="s">
         <v>842</v>
@@ -24741,7 +24923,7 @@
         <v>200116</v>
       </c>
       <c r="B119" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C119" t="s">
         <v>842</v>
@@ -24752,8 +24934,8 @@
       <c r="E119" t="s">
         <v>836</v>
       </c>
-      <c r="F119" s="1" t="s">
-        <v>845</v>
+      <c r="F119" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -24761,7 +24943,7 @@
         <v>200117</v>
       </c>
       <c r="B120" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C120" t="s">
         <v>842</v>
@@ -24778,7 +24960,7 @@
         <v>200118</v>
       </c>
       <c r="B121" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C121" t="s">
         <v>842</v>
@@ -24790,7 +24972,7 @@
         <v>834</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -24798,7 +24980,7 @@
         <v>200119</v>
       </c>
       <c r="B122" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C122" t="s">
         <v>842</v>
@@ -24815,7 +24997,7 @@
         <v>200120</v>
       </c>
       <c r="B123" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C123" t="s">
         <v>842</v>
@@ -24826,8 +25008,8 @@
       <c r="E123" t="s">
         <v>836</v>
       </c>
-      <c r="F123" s="1" t="s">
-        <v>845</v>
+      <c r="F123" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -24835,7 +25017,7 @@
         <v>200121</v>
       </c>
       <c r="B124" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C124" t="s">
         <v>842</v>
@@ -24852,7 +25034,7 @@
         <v>200122</v>
       </c>
       <c r="B125" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C125" t="s">
         <v>842</v>
@@ -24872,7 +25054,7 @@
         <v>200123</v>
       </c>
       <c r="B126" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C126" t="s">
         <v>842</v>
@@ -24884,7 +25066,7 @@
         <v>835</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -24892,7 +25074,7 @@
         <v>200124</v>
       </c>
       <c r="B127" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C127" t="s">
         <v>842</v>
@@ -24903,8 +25085,8 @@
       <c r="E127" t="s">
         <v>836</v>
       </c>
-      <c r="F127" s="1" t="s">
-        <v>845</v>
+      <c r="F127" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -24912,7 +25094,7 @@
         <v>200125</v>
       </c>
       <c r="B128" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C128" t="s">
         <v>842</v>
@@ -24929,7 +25111,7 @@
         <v>200126</v>
       </c>
       <c r="B129" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C129" t="s">
         <v>842</v>
@@ -24949,7 +25131,7 @@
         <v>200127</v>
       </c>
       <c r="B130" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C130" t="s">
         <v>842</v>
@@ -24969,7 +25151,7 @@
         <v>200128</v>
       </c>
       <c r="B131" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C131" t="s">
         <v>842</v>
@@ -24980,8 +25162,8 @@
       <c r="E131" t="s">
         <v>836</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>845</v>
+      <c r="F131" s="1">
+        <v>101036</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -24989,7 +25171,7 @@
         <v>200129</v>
       </c>
       <c r="B132" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C132" t="s">
         <v>831</v>
@@ -25001,7 +25183,7 @@
         <v>833</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -25009,7 +25191,7 @@
         <v>200130</v>
       </c>
       <c r="B133" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C133" t="s">
         <v>831</v>
@@ -25026,7 +25208,7 @@
         <v>200131</v>
       </c>
       <c r="B134" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C134" t="s">
         <v>831</v>
@@ -25043,7 +25225,7 @@
         <v>200132</v>
       </c>
       <c r="B135" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C135" t="s">
         <v>831</v>
@@ -25063,7 +25245,7 @@
         <v>200133</v>
       </c>
       <c r="B136" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C136" t="s">
         <v>831</v>
@@ -25075,7 +25257,7 @@
         <v>833</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -25083,7 +25265,7 @@
         <v>200134</v>
       </c>
       <c r="B137" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C137" t="s">
         <v>831</v>
@@ -25100,7 +25282,7 @@
         <v>200135</v>
       </c>
       <c r="B138" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C138" t="s">
         <v>831</v>
@@ -25117,7 +25299,7 @@
         <v>200136</v>
       </c>
       <c r="B139" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C139" t="s">
         <v>831</v>
@@ -25137,7 +25319,7 @@
         <v>200137</v>
       </c>
       <c r="B140" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C140" t="s">
         <v>831</v>
@@ -25157,7 +25339,7 @@
         <v>200138</v>
       </c>
       <c r="B141" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C141" t="s">
         <v>831</v>
@@ -25174,7 +25356,7 @@
         <v>200139</v>
       </c>
       <c r="B142" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C142" t="s">
         <v>831</v>
@@ -25191,7 +25373,7 @@
         <v>200140</v>
       </c>
       <c r="B143" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C143" t="s">
         <v>831</v>
@@ -25211,7 +25393,7 @@
         <v>200141</v>
       </c>
       <c r="B144" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C144" t="s">
         <v>831</v>
@@ -25223,7 +25405,7 @@
         <v>833</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -25231,7 +25413,7 @@
         <v>200142</v>
       </c>
       <c r="B145" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C145" t="s">
         <v>831</v>
@@ -25248,7 +25430,7 @@
         <v>200143</v>
       </c>
       <c r="B146" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C146" t="s">
         <v>831</v>
@@ -25265,7 +25447,7 @@
         <v>200144</v>
       </c>
       <c r="B147" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C147" t="s">
         <v>831</v>
@@ -25282,7 +25464,7 @@
         <v>200145</v>
       </c>
       <c r="B148" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C148" t="s">
         <v>842</v>
@@ -25299,7 +25481,7 @@
         <v>200146</v>
       </c>
       <c r="B149" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C149" t="s">
         <v>842</v>
@@ -25316,7 +25498,7 @@
         <v>200147</v>
       </c>
       <c r="B150" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C150" t="s">
         <v>842</v>
@@ -25333,7 +25515,7 @@
         <v>200148</v>
       </c>
       <c r="B151" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C151" t="s">
         <v>842</v>
@@ -25345,7 +25527,7 @@
         <v>836</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -25353,7 +25535,7 @@
         <v>200149</v>
       </c>
       <c r="B152" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C152" t="s">
         <v>842</v>
@@ -25370,7 +25552,7 @@
         <v>200150</v>
       </c>
       <c r="B153" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C153" t="s">
         <v>842</v>
@@ -25390,7 +25572,7 @@
         <v>200151</v>
       </c>
       <c r="B154" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C154" t="s">
         <v>842</v>
@@ -25407,7 +25589,7 @@
         <v>200152</v>
       </c>
       <c r="B155" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C155" t="s">
         <v>842</v>
@@ -25419,7 +25601,7 @@
         <v>836</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -25427,7 +25609,7 @@
         <v>200153</v>
       </c>
       <c r="B156" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C156" t="s">
         <v>842</v>
@@ -25444,7 +25626,7 @@
         <v>200154</v>
       </c>
       <c r="B157" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C157" t="s">
         <v>842</v>
@@ -25464,7 +25646,7 @@
         <v>200155</v>
       </c>
       <c r="B158" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C158" t="s">
         <v>842</v>
@@ -25484,7 +25666,7 @@
         <v>200156</v>
       </c>
       <c r="B159" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C159" t="s">
         <v>842</v>
@@ -25496,7 +25678,7 @@
         <v>836</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -25504,7 +25686,7 @@
         <v>200157</v>
       </c>
       <c r="B160" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C160" t="s">
         <v>842</v>
@@ -25521,7 +25703,7 @@
         <v>200158</v>
       </c>
       <c r="B161" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C161" t="s">
         <v>842</v>
@@ -25538,7 +25720,7 @@
         <v>200159</v>
       </c>
       <c r="B162" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C162" t="s">
         <v>842</v>
@@ -25558,7 +25740,7 @@
         <v>200160</v>
       </c>
       <c r="B163" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C163" t="s">
         <v>842</v>
@@ -25569,8 +25751,8 @@
       <c r="E163" t="s">
         <v>836</v>
       </c>
-      <c r="F163" s="1" t="s">
-        <v>845</v>
+      <c r="F163" s="1">
+        <v>101036</v>
       </c>
     </row>
   </sheetData>
@@ -25583,7 +25765,9 @@
   <dimension ref="A1:F137"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="10.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="22.25" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
@@ -25596,13 +25780,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>863</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>864</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>865</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>669</v>
@@ -25630,22 +25814,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>866</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>867</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>869</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>870</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -25653,7 +25837,7 @@
         <v>601001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C4" s="9">
         <v>110100</v>
@@ -25816,7 +26000,7 @@
         <v>689</v>
       </c>
       <c r="C12" s="9">
-        <v>110108</v>
+        <v>102043</v>
       </c>
       <c r="D12" s="9">
         <v>110006</v>
@@ -26813,7 +26997,7 @@
         <v>601059</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C62" s="9">
         <v>110158</v>
@@ -26853,7 +27037,7 @@
         <v>601061</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C64" s="9">
         <v>110160</v>
@@ -27179,7 +27363,7 @@
         <v>110172</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E80" s="9">
         <v>1007</v>
@@ -27199,7 +27383,7 @@
         <v>110174</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E81" s="9">
         <v>1007</v>
@@ -27219,7 +27403,7 @@
         <v>110176</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E82" s="9">
         <v>1007</v>
@@ -27239,7 +27423,7 @@
         <v>110177</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E83" s="9">
         <v>1007</v>
@@ -27259,7 +27443,7 @@
         <v>110178</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E84" s="9">
         <v>1007</v>
@@ -27279,7 +27463,7 @@
         <v>110179</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E85" s="9">
         <v>1007</v>
@@ -27299,7 +27483,7 @@
         <v>110180</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E86" s="9">
         <v>1007</v>
@@ -27319,7 +27503,7 @@
         <v>110181</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E87" s="9">
         <v>1007</v>
@@ -27339,7 +27523,7 @@
         <v>110182</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E88" s="9">
         <v>1007</v>
@@ -27359,7 +27543,7 @@
         <v>110183</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E89" s="9">
         <v>1007</v>
@@ -27379,7 +27563,7 @@
         <v>110501</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E90" s="9">
         <v>1008</v>
@@ -27399,7 +27583,7 @@
         <v>110502</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E91" s="9">
         <v>1008</v>
@@ -27419,7 +27603,7 @@
         <v>110503</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E92" s="9">
         <v>1008</v>
@@ -27439,7 +27623,7 @@
         <v>110504</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E93" s="9">
         <v>1008</v>
@@ -27459,7 +27643,7 @@
         <v>110505</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E94" s="9">
         <v>1008</v>
@@ -27473,13 +27657,13 @@
         <v>603006</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C95" s="9">
         <v>110506</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E95" s="9">
         <v>1008</v>
@@ -27499,7 +27683,7 @@
         <v>110507</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E96" s="9">
         <v>1008</v>
@@ -27519,7 +27703,7 @@
         <v>110508</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E97" s="9">
         <v>1008</v>
@@ -27539,7 +27723,7 @@
         <v>110509</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E98" s="9">
         <v>1008</v>
@@ -27559,7 +27743,7 @@
         <v>110510</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E99" s="9">
         <v>1008</v>
@@ -27579,7 +27763,7 @@
         <v>110511</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E100" s="9">
         <v>1008</v>
@@ -27599,7 +27783,7 @@
         <v>110512</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E101" s="9">
         <v>1008</v>
@@ -27619,7 +27803,7 @@
         <v>110513</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E102" s="9">
         <v>1008</v>
@@ -27639,7 +27823,7 @@
         <v>110514</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E103" s="9">
         <v>1008</v>
@@ -27659,7 +27843,7 @@
         <v>110515</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E104" s="9">
         <v>1008</v>
@@ -27679,7 +27863,7 @@
         <v>110516</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E105" s="9">
         <v>1008</v>
@@ -27699,7 +27883,7 @@
         <v>110517</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E106" s="9">
         <v>1008</v>
@@ -27719,7 +27903,7 @@
         <v>110518</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E107" s="9">
         <v>1008</v>
@@ -27739,7 +27923,7 @@
         <v>110519</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E108" s="9">
         <v>1008</v>
@@ -27759,7 +27943,7 @@
         <v>110520</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E109" s="1">
         <v>1008</v>
@@ -27779,7 +27963,7 @@
         <v>110521</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E110" s="1">
         <v>1008</v>
@@ -27799,7 +27983,7 @@
         <v>110522</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E111" s="1">
         <v>1008</v>
@@ -27819,7 +28003,7 @@
         <v>110523</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E112" s="1">
         <v>1008</v>
@@ -27839,7 +28023,7 @@
         <v>110524</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E113" s="1">
         <v>1008</v>
@@ -27853,13 +28037,13 @@
         <v>603025</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C114" s="1">
         <v>110525</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E114" s="1">
         <v>1008</v>
@@ -27879,7 +28063,7 @@
         <v>110526</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E115" s="1">
         <v>1008</v>
@@ -27899,7 +28083,7 @@
         <v>110527</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E116" s="1">
         <v>1008</v>
@@ -27919,7 +28103,7 @@
         <v>110528</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E117" s="1">
         <v>1008</v>
@@ -27939,7 +28123,7 @@
         <v>110529</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E118" s="1">
         <v>1008</v>
@@ -27959,7 +28143,7 @@
         <v>110530</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E119" s="1">
         <v>1008</v>
@@ -27979,7 +28163,7 @@
         <v>110531</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E120" s="1">
         <v>1008</v>
@@ -27999,7 +28183,7 @@
         <v>110532</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E121" s="1">
         <v>1008</v>
@@ -28019,7 +28203,7 @@
         <v>110533</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E122" s="1">
         <v>1008</v>
@@ -28039,7 +28223,7 @@
         <v>110534</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E123" s="1">
         <v>1008</v>
@@ -28059,7 +28243,7 @@
         <v>110535</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E124" s="1">
         <v>1008</v>
@@ -28079,7 +28263,7 @@
         <v>110536</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E125" s="1">
         <v>1008</v>
@@ -28099,7 +28283,7 @@
         <v>110537</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E126" s="1">
         <v>1008</v>
@@ -28119,7 +28303,7 @@
         <v>110538</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E127" s="1">
         <v>1008</v>
@@ -28139,7 +28323,7 @@
         <v>110539</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E128" s="1">
         <v>1008</v>
@@ -28159,7 +28343,7 @@
         <v>110540</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E129" s="1">
         <v>1008</v>
@@ -28179,7 +28363,7 @@
         <v>110541</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E130" s="1">
         <v>1008</v>
@@ -28199,7 +28383,7 @@
         <v>110542</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E131" s="1">
         <v>1008</v>
@@ -28219,7 +28403,7 @@
         <v>110543</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E132" s="1">
         <v>1008</v>
@@ -28239,7 +28423,7 @@
         <v>110544</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E133" s="1">
         <v>1008</v>
@@ -28259,7 +28443,7 @@
         <v>110545</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E134" s="1">
         <v>1008</v>
@@ -28279,7 +28463,7 @@
         <v>110546</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E135" s="1">
         <v>1008</v>
@@ -28299,7 +28483,7 @@
         <v>110547</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E136" s="1">
         <v>1008</v>
@@ -28319,7 +28503,7 @@
         <v>110548</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E137" s="1">
         <v>1008</v>
@@ -28351,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -28362,18 +28546,18 @@
         <v>8</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>937</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
         <v>938</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -28381,10 +28565,10 @@
         <v>1001</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>940</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -28392,10 +28576,10 @@
         <v>1002</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>941</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>942</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -28403,10 +28587,10 @@
         <v>1003</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>944</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -28414,10 +28598,10 @@
         <v>1004</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>946</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -28425,10 +28609,10 @@
         <v>1005</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -28436,10 +28620,10 @@
         <v>1006</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>949</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -28447,10 +28631,10 @@
         <v>1007</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>951</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -28458,7 +28642,7 @@
         <v>1008</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>470</v>
@@ -28485,25 +28669,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="10" t="s">
         <v>956</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -28523,7 +28707,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>8</v>
@@ -28537,31 +28721,31 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>962</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
         <v>963</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>964</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>965</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>966</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>967</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>968</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -28569,28 +28753,28 @@
         <v>800001</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>970</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>971</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>972</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>973</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>974</v>
       </c>
       <c r="F4" s="10">
         <v>30</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H4" s="10">
         <v>900001</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -28598,28 +28782,28 @@
         <v>800002</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>976</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>971</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>977</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>972</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>978</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>979</v>
       </c>
       <c r="F5" s="10">
         <v>10</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H5" s="10">
         <v>900002</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -28627,28 +28811,28 @@
         <v>800003</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>982</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>983</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>984</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>985</v>
       </c>
       <c r="F6" s="10">
         <v>40</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H6" s="10">
         <v>900003</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -28656,28 +28840,28 @@
         <v>800004</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>987</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>982</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>988</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>983</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>989</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>990</v>
       </c>
       <c r="F7" s="10">
         <v>20</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H7" s="10">
         <v>900004</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -28685,28 +28869,28 @@
         <v>800005</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>992</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>993</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>994</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>995</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>996</v>
       </c>
       <c r="F8" s="10">
         <v>40</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H8" s="10">
         <v>900005</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -28714,28 +28898,28 @@
         <v>800006</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>998</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>999</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>1000</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>1001</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>1002</v>
       </c>
       <c r="F9" s="10">
         <v>20</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H9" s="10">
         <v>900007</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -28743,28 +28927,28 @@
         <v>800007</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>1005</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>1006</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>1007</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>1008</v>
       </c>
       <c r="F10" s="10">
         <v>35</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H10" s="10">
         <v>900006</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -28772,28 +28956,28 @@
         <v>800008</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>1011</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>1012</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="10" t="s">
         <v>1013</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>1014</v>
       </c>
       <c r="F11" s="10">
         <v>35</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H11" s="10">
         <v>900008</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -28801,28 +28985,28 @@
         <v>800009</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>1017</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>1018</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>1019</v>
       </c>
       <c r="F12" s="10">
         <v>25</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H12" s="10">
         <v>900009</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -28830,28 +29014,28 @@
         <v>800010</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>1022</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>1023</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>1024</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>1025</v>
       </c>
       <c r="F13" s="10">
         <v>30</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H13" s="10">
         <v>900010</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
@@ -28861,7 +29045,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A4D0D2-A015-4A45-937C-5C1E151626F6}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.875" style="1" bestFit="1" customWidth="1"/>
@@ -28873,14 +29057,17 @@
     <col min="7" max="7" width="10.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="14" max="14" width="23.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:20" ht="15" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -28888,46 +29075,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>1029</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>1030</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>1032</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="11" t="s">
         <v>1033</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>1034</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>1035</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>1036</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>1037</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>1038</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>1040</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="Q1" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
@@ -28950,10 +29152,10 @@
         <v>7</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>8</v>
+        <v>1045</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>8</v>
@@ -28965,68 +29167,98 @@
         <v>8</v>
       </c>
       <c r="M2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="S2" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:20" ht="15" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>1059</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1">
       <c r="A4" s="8">
         <v>900001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="C4" s="8">
         <v>800001</v>
@@ -29035,10 +29267,10 @@
         <v>103003</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>1057</v>
+        <v>1067</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
@@ -29047,33 +29279,48 @@
         <v>0</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1059</v>
+        <v>1069</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>1061</v>
+        <v>1071</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>1062</v>
+        <v>1072</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>1074</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1">
       <c r="A5" s="8">
         <v>900002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1065</v>
+        <v>1080</v>
       </c>
       <c r="C5" s="8">
         <v>800002</v>
@@ -29082,10 +29329,10 @@
         <v>103007</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1067</v>
+        <v>1082</v>
       </c>
       <c r="G5" s="8">
         <v>800001</v>
@@ -29094,33 +29341,48 @@
         <v>50</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1068</v>
+        <v>1083</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>1070</v>
+        <v>1085</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1071</v>
+        <v>1086</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1073</v>
+        <v>1088</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>1089</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1">
       <c r="A6" s="8">
         <v>900003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1075</v>
+        <v>1095</v>
       </c>
       <c r="C6" s="8">
         <v>800003</v>
@@ -29129,10 +29391,10 @@
         <v>103002</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>1076</v>
+        <v>1096</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -29141,33 +29403,48 @@
         <v>0</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>1077</v>
+        <v>1097</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1078</v>
+        <v>1098</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1079</v>
+        <v>1099</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>1080</v>
+        <v>1100</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>1081</v>
+        <v>1101</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>1082</v>
+        <v>1102</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>1103</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1">
       <c r="A7" s="8">
         <v>900004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1084</v>
+        <v>1109</v>
       </c>
       <c r="C7" s="8">
         <v>800004</v>
@@ -29176,10 +29453,10 @@
         <v>103001</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1085</v>
+        <v>1110</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="G7" s="8">
         <v>800003</v>
@@ -29188,33 +29465,48 @@
         <v>60</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>1088</v>
+        <v>1113</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>1089</v>
+        <v>1114</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>1090</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>1091</v>
+        <v>1115</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>1116</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>1092</v>
+        <v>1117</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="33">
+        <v>1118</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1">
       <c r="A8" s="8">
         <v>900005</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1094</v>
+        <v>1124</v>
       </c>
       <c r="C8" s="8">
         <v>800005</v>
@@ -29223,10 +29515,10 @@
         <v>103006</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="G8" s="8">
         <v>800002</v>
@@ -29235,33 +29527,48 @@
         <v>50</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>1096</v>
+        <v>1126</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>1097</v>
+        <v>1127</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>1098</v>
+        <v>1128</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1099</v>
+        <v>1129</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>1101</v>
+        <v>1131</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>1132</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1">
       <c r="A9" s="8">
         <v>900006</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1103</v>
+        <v>1138</v>
       </c>
       <c r="C9" s="8">
         <v>800006</v>
@@ -29270,10 +29577,10 @@
         <v>103004</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1104</v>
+        <v>1139</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>1105</v>
+        <v>1140</v>
       </c>
       <c r="G9" s="8">
         <v>800005</v>
@@ -29282,33 +29589,48 @@
         <v>60</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>1106</v>
+        <v>1141</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>1107</v>
+        <v>1142</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>1108</v>
+        <v>1143</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1109</v>
+        <v>1144</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>1110</v>
+        <v>1145</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>1111</v>
+        <v>1146</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>1147</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1">
       <c r="A10" s="8">
         <v>900007</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1113</v>
+        <v>1153</v>
       </c>
       <c r="C10" s="8">
         <v>800007</v>
@@ -29317,10 +29639,10 @@
         <v>103009</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1114</v>
+        <v>1154</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1115</v>
+        <v>1155</v>
       </c>
       <c r="G10" s="8">
         <v>800005</v>
@@ -29329,33 +29651,48 @@
         <v>70</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>1116</v>
+        <v>1156</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>1117</v>
+        <v>1157</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>1118</v>
+        <v>1158</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1119</v>
+        <v>1159</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>1121</v>
+        <v>1161</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>1162</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15" customHeight="1">
       <c r="A11" s="8">
         <v>900008</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1123</v>
+        <v>1168</v>
       </c>
       <c r="C11" s="8">
         <v>800008</v>
@@ -29364,10 +29701,10 @@
         <v>103005</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1124</v>
+        <v>1169</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1125</v>
+        <v>1170</v>
       </c>
       <c r="G11" s="8">
         <v>800007</v>
@@ -29376,33 +29713,48 @@
         <v>50</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>1126</v>
+        <v>1171</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>1127</v>
+        <v>1172</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>1128</v>
+        <v>1173</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>1129</v>
+        <v>1174</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>1130</v>
+        <v>1175</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>1131</v>
+        <v>1176</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>1177</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1">
       <c r="A12" s="8">
         <v>900009</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1133</v>
+        <v>1183</v>
       </c>
       <c r="C12" s="8">
         <v>800009</v>
@@ -29411,10 +29763,10 @@
         <v>103010</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1134</v>
+        <v>1184</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>1134</v>
+        <v>1184</v>
       </c>
       <c r="G12" s="8">
         <v>800008</v>
@@ -29423,33 +29775,48 @@
         <v>50</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>1135</v>
+        <v>1185</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>1136</v>
+        <v>1186</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>1137</v>
+        <v>1187</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>1138</v>
+        <v>1188</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>1139</v>
+        <v>1189</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>1140</v>
+        <v>1190</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>1191</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15" customHeight="1">
       <c r="A13" s="8">
         <v>900010</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1142</v>
+        <v>1197</v>
       </c>
       <c r="C13" s="8">
         <v>800010</v>
@@ -29458,10 +29825,10 @@
         <v>103008</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1143</v>
+        <v>1198</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>1144</v>
+        <v>1199</v>
       </c>
       <c r="G13" s="8">
         <v>800001</v>
@@ -29470,25 +29837,40 @@
         <v>60</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>1145</v>
+        <v>1200</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>1146</v>
+        <v>1201</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>1147</v>
+        <v>1202</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>1148</v>
+        <v>1203</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>1149</v>
+        <v>1204</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>1150</v>
+        <v>1205</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>1151</v>
+        <v>1206</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -29498,7 +29880,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0316AC22-6E76-4466-9040-E33C4C116F68}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="23.625" bestFit="1" customWidth="1"/>
@@ -29506,7 +29888,7 @@
     <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -29517,19 +29899,19 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>1152</v>
+        <v>1212</v>
       </c>
       <c r="E1" t="s">
-        <v>1153</v>
+        <v>1213</v>
       </c>
       <c r="F1" t="s">
-        <v>1154</v>
+        <v>1214</v>
       </c>
       <c r="G1" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -29540,27 +29922,27 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>1155</v>
+        <v>1215</v>
       </c>
       <c r="E2" t="s">
         <v>821</v>
       </c>
       <c r="F2" t="s">
-        <v>1156</v>
+        <v>1216</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>1157</v>
+        <v>1217</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1158</v>
+        <v>1218</v>
       </c>
       <c r="D3" t="s">
         <v>825</v>
@@ -29572,10 +29954,10 @@
         <v>827</v>
       </c>
       <c r="G3" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>110001</v>
       </c>
@@ -29586,19 +29968,19 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E4" t="s">
         <v>842</v>
       </c>
       <c r="F4" t="s">
-        <v>1160</v>
+        <v>1220</v>
       </c>
       <c r="G4" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>110002</v>
       </c>
@@ -29609,19 +29991,19 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E5" t="s">
         <v>842</v>
       </c>
       <c r="F5" t="s">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="G5" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>110003</v>
       </c>
@@ -29632,19 +30014,19 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E6" t="s">
         <v>842</v>
       </c>
       <c r="F6" t="s">
-        <v>1160</v>
+        <v>1220</v>
       </c>
       <c r="G6" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>110004</v>
       </c>
@@ -29661,13 +30043,13 @@
         <v>842</v>
       </c>
       <c r="F7" t="s">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="G7" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>110005</v>
       </c>
@@ -29678,19 +30060,19 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>1167</v>
+        <v>1227</v>
       </c>
       <c r="E8" t="s">
         <v>842</v>
       </c>
       <c r="F8" t="s">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="G8" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>110006</v>
       </c>
@@ -29707,13 +30089,13 @@
         <v>842</v>
       </c>
       <c r="F9" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G9" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>110007</v>
       </c>
@@ -29724,19 +30106,19 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E10" t="s">
         <v>842</v>
       </c>
       <c r="F10" t="s">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="G10" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>110008</v>
       </c>
@@ -29747,19 +30129,19 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E11" t="s">
         <v>842</v>
       </c>
       <c r="F11" t="s">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="G11" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>110009</v>
       </c>
@@ -29770,22 +30152,19 @@
         <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>1173</v>
+        <v>1233</v>
       </c>
       <c r="E12" t="s">
         <v>842</v>
       </c>
       <c r="F12" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G12" t="s">
-        <v>1174</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>110010</v>
       </c>
@@ -29796,7 +30175,7 @@
         <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E13" t="s">
         <v>842</v>
@@ -29805,10 +30184,10 @@
         <v>839</v>
       </c>
       <c r="G13" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>110011</v>
       </c>
@@ -29819,19 +30198,19 @@
         <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E14" t="s">
         <v>842</v>
       </c>
       <c r="F14" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G14" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>110012</v>
       </c>
@@ -29842,7 +30221,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E15" t="s">
         <v>842</v>
@@ -29851,10 +30230,10 @@
         <v>832</v>
       </c>
       <c r="G15" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>110013</v>
       </c>
@@ -29865,16 +30244,16 @@
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>1179</v>
+        <v>1238</v>
       </c>
       <c r="E16" t="s">
         <v>842</v>
       </c>
       <c r="F16" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G16" t="s">
-        <v>1180</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -29888,16 +30267,16 @@
         <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E17" t="s">
         <v>842</v>
       </c>
       <c r="F17" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G17" t="s">
-        <v>1181</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -29911,7 +30290,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>1182</v>
+        <v>1241</v>
       </c>
       <c r="E18" t="s">
         <v>842</v>
@@ -29920,7 +30299,7 @@
         <v>839</v>
       </c>
       <c r="G18" t="s">
-        <v>1183</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -29934,16 +30313,16 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E19" t="s">
         <v>842</v>
       </c>
       <c r="F19" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G19" t="s">
-        <v>1184</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -29966,7 +30345,7 @@
         <v>839</v>
       </c>
       <c r="G20" t="s">
-        <v>1185</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -29980,16 +30359,16 @@
         <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>1179</v>
+        <v>1238</v>
       </c>
       <c r="E21" t="s">
         <v>842</v>
       </c>
       <c r="F21" t="s">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="G21" t="s">
-        <v>1186</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -30003,16 +30382,16 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>1187</v>
+        <v>1246</v>
       </c>
       <c r="E22" t="s">
         <v>831</v>
       </c>
       <c r="F22" t="s">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="G22" t="s">
-        <v>1188</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -30026,16 +30405,16 @@
         <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>1187</v>
+        <v>1246</v>
       </c>
       <c r="E23" t="s">
         <v>831</v>
       </c>
       <c r="F23" t="s">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="G23" t="s">
-        <v>1189</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -30055,10 +30434,10 @@
         <v>831</v>
       </c>
       <c r="F24" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G24" t="s">
-        <v>1190</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -30072,16 +30451,16 @@
         <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E25" t="s">
         <v>831</v>
       </c>
       <c r="F25" t="s">
-        <v>1191</v>
+        <v>1250</v>
       </c>
       <c r="G25" t="s">
-        <v>1192</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -30101,10 +30480,10 @@
         <v>831</v>
       </c>
       <c r="F26" t="s">
-        <v>1191</v>
+        <v>1250</v>
       </c>
       <c r="G26" t="s">
-        <v>1193</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -30118,16 +30497,16 @@
         <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E27" t="s">
         <v>831</v>
       </c>
       <c r="F27" t="s">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="G27" t="s">
-        <v>1194</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -30141,16 +30520,16 @@
         <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E28" t="s">
         <v>831</v>
       </c>
       <c r="F28" t="s">
-        <v>1191</v>
+        <v>1250</v>
       </c>
       <c r="G28" t="s">
-        <v>1195</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -30164,16 +30543,16 @@
         <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E29" t="s">
         <v>831</v>
       </c>
       <c r="F29" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G29" t="s">
-        <v>1196</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -30187,7 +30566,7 @@
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E30" t="s">
         <v>831</v>
@@ -30196,7 +30575,7 @@
         <v>832</v>
       </c>
       <c r="G30" t="s">
-        <v>1197</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -30210,7 +30589,7 @@
         <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E31" t="s">
         <v>831</v>
@@ -30219,7 +30598,7 @@
         <v>837</v>
       </c>
       <c r="G31" t="s">
-        <v>1198</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -30233,7 +30612,7 @@
         <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>1199</v>
+        <v>1258</v>
       </c>
       <c r="E32" t="s">
         <v>831</v>
@@ -30242,7 +30621,7 @@
         <v>837</v>
       </c>
       <c r="G32" t="s">
-        <v>1200</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -30265,7 +30644,7 @@
         <v>839</v>
       </c>
       <c r="G33" t="s">
-        <v>1201</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -30279,7 +30658,7 @@
         <v>83</v>
       </c>
       <c r="D34" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E34" t="s">
         <v>831</v>
@@ -30288,7 +30667,7 @@
         <v>839</v>
       </c>
       <c r="G34" t="s">
-        <v>1202</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -30302,7 +30681,7 @@
         <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E35" t="s">
         <v>831</v>
@@ -30311,7 +30690,7 @@
         <v>841</v>
       </c>
       <c r="G35" t="s">
-        <v>1203</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -30325,16 +30704,16 @@
         <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E36" t="s">
         <v>831</v>
       </c>
       <c r="F36" t="s">
-        <v>1162</v>
+        <v>1222</v>
       </c>
       <c r="G36" t="s">
-        <v>1204</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -30348,16 +30727,16 @@
         <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E37" t="s">
         <v>831</v>
       </c>
       <c r="F37" t="s">
-        <v>1169</v>
+        <v>1229</v>
       </c>
       <c r="G37" t="s">
-        <v>1205</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -30371,16 +30750,16 @@
         <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E38" t="s">
         <v>831</v>
       </c>
       <c r="F38" t="s">
-        <v>1191</v>
+        <v>1250</v>
       </c>
       <c r="G38" t="s">
-        <v>1206</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -30394,16 +30773,16 @@
         <v>93</v>
       </c>
       <c r="D39" t="s">
-        <v>1187</v>
+        <v>1246</v>
       </c>
       <c r="E39" t="s">
         <v>842</v>
       </c>
       <c r="F39" t="s">
-        <v>1207</v>
+        <v>1266</v>
       </c>
       <c r="G39" t="s">
-        <v>1208</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -30417,16 +30796,16 @@
         <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>1187</v>
+        <v>1246</v>
       </c>
       <c r="E40" t="s">
         <v>842</v>
       </c>
       <c r="F40" t="s">
-        <v>1207</v>
+        <v>1266</v>
       </c>
       <c r="G40" t="s">
-        <v>1209</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -30440,16 +30819,16 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>1187</v>
+        <v>1246</v>
       </c>
       <c r="E41" t="s">
         <v>842</v>
       </c>
       <c r="F41" t="s">
-        <v>1207</v>
+        <v>1266</v>
       </c>
       <c r="G41" t="s">
-        <v>1210</v>
+        <v>1269</v>
       </c>
     </row>
   </sheetData>
@@ -30473,13 +30852,13 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>1211</v>
+        <v>1270</v>
       </c>
       <c r="E1" t="s">
-        <v>1212</v>
+        <v>1271</v>
       </c>
       <c r="F1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -30504,22 +30883,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1157</v>
+        <v>1217</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1158</v>
+        <v>1218</v>
       </c>
       <c r="D3" t="s">
-        <v>1213</v>
+        <v>1272</v>
       </c>
       <c r="E3" t="s">
-        <v>1214</v>
+        <v>1273</v>
       </c>
       <c r="F3" t="s">
-        <v>1159</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -30536,10 +30915,10 @@
         <v>800004</v>
       </c>
       <c r="E4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F4" t="s">
-        <v>1215</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -30556,10 +30935,10 @@
         <v>800003</v>
       </c>
       <c r="E5" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F5" t="s">
-        <v>1216</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -30576,10 +30955,10 @@
         <v>800001</v>
       </c>
       <c r="E6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F6" t="s">
-        <v>1217</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -30596,10 +30975,10 @@
         <v>800006</v>
       </c>
       <c r="E7" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F7" t="s">
-        <v>1218</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -30616,10 +30995,10 @@
         <v>800008</v>
       </c>
       <c r="E8" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F8" t="s">
-        <v>1219</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -30636,10 +31015,10 @@
         <v>800005</v>
       </c>
       <c r="E9" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F9" t="s">
-        <v>1220</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -30656,10 +31035,10 @@
         <v>800002</v>
       </c>
       <c r="E10" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F10" t="s">
-        <v>1221</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -30676,10 +31055,10 @@
         <v>800010</v>
       </c>
       <c r="E11" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F11" t="s">
-        <v>1222</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -30696,10 +31075,10 @@
         <v>800007</v>
       </c>
       <c r="E12" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F12" t="s">
-        <v>1223</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -30716,10 +31095,10 @@
         <v>800009</v>
       </c>
       <c r="E13" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F13" t="s">
-        <v>1224</v>
+        <v>1283</v>
       </c>
     </row>
   </sheetData>

--- a/Excel2JSON(win-x64)/excel_files/Data.xlsx
+++ b/Excel2JSON(win-x64)/excel_files/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28919"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAE9F78D-1F55-4DE1-A360-6A4EE2C311C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{252F667A-DDC5-4EAC-91B8-827CF82B4EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5241" uniqueCount="1407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5254" uniqueCount="1417">
   <si>
     <t>key</t>
   </si>
@@ -2956,6 +2956,9 @@
     <t>물건 받을 시 멘트</t>
   </si>
   <si>
+    <t>영어이름</t>
+  </si>
+  <si>
     <t>흥부</t>
   </si>
   <si>
@@ -2974,6 +2977,9 @@
     <t>이런 귀한 음식을 제게 주시다니… 고맙습니다.</t>
   </si>
   <si>
+    <t>heungbu</t>
+  </si>
+  <si>
     <t>놀부</t>
   </si>
   <si>
@@ -2989,6 +2995,9 @@
     <t>후… 뭐, 내 입에는 그럭저럭 맞는군</t>
   </si>
   <si>
+    <t>nolbu</t>
+  </si>
+  <si>
     <t>콩쥐</t>
   </si>
   <si>
@@ -3007,6 +3016,9 @@
     <t>정말 정성껏 만들어주셨군요. 향만으로도 마음이 편해져요. 감사합니다.</t>
   </si>
   <si>
+    <t>kongjwi</t>
+  </si>
+  <si>
     <t>팥쥐</t>
   </si>
   <si>
@@ -3022,6 +3034,9 @@
     <t>…뭐, 먹을 순 있겠네.</t>
   </si>
   <si>
+    <t>patjwi</t>
+  </si>
+  <si>
     <t>선녀</t>
   </si>
   <si>
@@ -3040,6 +3055,9 @@
     <t>달콤한 향… 오랜만에 이런 맛을 느껴봅니다. 고마워요.</t>
   </si>
   <si>
+    <t>fairy</t>
+  </si>
+  <si>
     <t>호랑이</t>
   </si>
   <si>
@@ -3058,6 +3076,9 @@
     <t>크하하! 사람들 몰래 혼자 다 먹어야겠어~</t>
   </si>
   <si>
+    <t>tiger</t>
+  </si>
+  <si>
     <t>도깨비</t>
   </si>
   <si>
@@ -3076,6 +3097,9 @@
     <t xml:space="preserve">우왁! 혀가 막 춤춘다 춤춰~! </t>
   </si>
   <si>
+    <t>goblin</t>
+  </si>
+  <si>
     <t>토끼</t>
   </si>
   <si>
@@ -3094,6 +3118,9 @@
     <t>오! 이건 예상 밖인데?  맛있게 잘 먹을게!</t>
   </si>
   <si>
+    <t>rabbit</t>
+  </si>
+  <si>
     <t>거북이</t>
   </si>
   <si>
@@ -3109,6 +3136,9 @@
     <t>음… 오래 기다린 보람이 있습니다.</t>
   </si>
   <si>
+    <t>turtle</t>
+  </si>
+  <si>
     <t>허생</t>
   </si>
   <si>
@@ -3125,6 +3155,9 @@
   </si>
   <si>
     <t>향이 아주 마음에 드는군요. 잘 먹겠습니다.</t>
+  </si>
+  <si>
+    <t>heosaeng</t>
   </si>
   <si>
     <t>givingNPC</t>
@@ -3937,9 +3970,6 @@
   </si>
   <si>
     <t>음식군id</t>
-  </si>
-  <si>
-    <t>영어이름</t>
   </si>
   <si>
     <t>설명</t>
@@ -15514,16 +15544,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="D1" t="s">
         <v>864</v>
       </c>
       <c r="E1" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="F1" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15540,7 +15570,7 @@
         <v>824</v>
       </c>
       <c r="E2" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -15548,22 +15578,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="D3" t="s">
         <v>869</v>
       </c>
       <c r="E3" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
       <c r="F3" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15580,10 +15610,10 @@
         <v>875</v>
       </c>
       <c r="E4" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="F4" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15600,10 +15630,10 @@
         <v>876</v>
       </c>
       <c r="E5" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="F5" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15620,10 +15650,10 @@
         <v>877</v>
       </c>
       <c r="E6" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
       <c r="F6" t="s">
-        <v>1295</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15640,10 +15670,10 @@
         <v>878</v>
       </c>
       <c r="E7" t="s">
-        <v>1296</v>
+        <v>1306</v>
       </c>
       <c r="F7" t="s">
-        <v>1297</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15660,10 +15690,10 @@
         <v>879</v>
       </c>
       <c r="E8" t="s">
-        <v>1298</v>
+        <v>1308</v>
       </c>
       <c r="F8" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15680,10 +15710,10 @@
         <v>880</v>
       </c>
       <c r="E9" t="s">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="F9" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15700,10 +15730,10 @@
         <v>881</v>
       </c>
       <c r="E10" t="s">
-        <v>1302</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="s">
-        <v>1303</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15720,10 +15750,10 @@
         <v>882</v>
       </c>
       <c r="E11" t="s">
-        <v>1304</v>
+        <v>1314</v>
       </c>
       <c r="F11" t="s">
-        <v>1305</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15740,10 +15770,10 @@
         <v>883</v>
       </c>
       <c r="E12" t="s">
-        <v>1306</v>
+        <v>1316</v>
       </c>
       <c r="F12" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15760,10 +15790,10 @@
         <v>884</v>
       </c>
       <c r="E13" t="s">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="F13" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
     </row>
   </sheetData>
@@ -15784,16 +15814,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="D1" t="s">
         <v>864</v>
       </c>
       <c r="E1" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="F1" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15810,7 +15840,7 @@
         <v>824</v>
       </c>
       <c r="E2" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -15818,22 +15848,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
       <c r="B3" t="s">
         <v>867</v>
       </c>
       <c r="C3" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="D3" t="s">
         <v>869</v>
       </c>
       <c r="E3" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
       <c r="F3" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15850,10 +15880,10 @@
         <v>885</v>
       </c>
       <c r="E4" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="F4" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15870,10 +15900,10 @@
         <v>886</v>
       </c>
       <c r="E5" t="s">
-        <v>1312</v>
+        <v>1322</v>
       </c>
       <c r="F5" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15890,10 +15920,10 @@
         <v>887</v>
       </c>
       <c r="E6" t="s">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="F6" t="s">
-        <v>1315</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15910,10 +15940,10 @@
         <v>888</v>
       </c>
       <c r="E7" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="F7" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15930,10 +15960,10 @@
         <v>889</v>
       </c>
       <c r="E8" t="s">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="F8" t="s">
-        <v>1319</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15947,13 +15977,13 @@
         <v>491</v>
       </c>
       <c r="D9" t="s">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="E9" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="F9" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15970,10 +16000,10 @@
         <v>892</v>
       </c>
       <c r="E10" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
       <c r="F10" t="s">
-        <v>1324</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15990,10 +16020,10 @@
         <v>893</v>
       </c>
       <c r="E11" t="s">
-        <v>1325</v>
+        <v>1335</v>
       </c>
       <c r="F11" t="s">
-        <v>1326</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -16010,10 +16040,10 @@
         <v>894</v>
       </c>
       <c r="E12" t="s">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="F12" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -16030,10 +16060,10 @@
         <v>895</v>
       </c>
       <c r="E13" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="s">
-        <v>1330</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -16050,10 +16080,10 @@
         <v>896</v>
       </c>
       <c r="E14" t="s">
-        <v>1331</v>
+        <v>1341</v>
       </c>
       <c r="F14" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -16070,10 +16100,10 @@
         <v>897</v>
       </c>
       <c r="E15" t="s">
-        <v>1333</v>
+        <v>1343</v>
       </c>
       <c r="F15" t="s">
-        <v>1334</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -16090,10 +16120,10 @@
         <v>898</v>
       </c>
       <c r="E16" t="s">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="F16" t="s">
-        <v>1336</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -16110,10 +16140,10 @@
         <v>899</v>
       </c>
       <c r="E17" t="s">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="F17" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -16130,10 +16160,10 @@
         <v>900</v>
       </c>
       <c r="E18" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="F18" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -16150,10 +16180,10 @@
         <v>901</v>
       </c>
       <c r="E19" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
       <c r="F19" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -16170,10 +16200,10 @@
         <v>902</v>
       </c>
       <c r="E20" t="s">
-        <v>1343</v>
+        <v>1353</v>
       </c>
       <c r="F20" t="s">
-        <v>1344</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -16190,10 +16220,10 @@
         <v>903</v>
       </c>
       <c r="E21" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="F21" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -16210,10 +16240,10 @@
         <v>904</v>
       </c>
       <c r="E22" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="F22" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -16230,10 +16260,10 @@
         <v>905</v>
       </c>
       <c r="E23" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
       <c r="F23" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -16250,10 +16280,10 @@
         <v>906</v>
       </c>
       <c r="E24" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="F24" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -16270,10 +16300,10 @@
         <v>907</v>
       </c>
       <c r="E25" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="F25" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -16290,10 +16320,10 @@
         <v>908</v>
       </c>
       <c r="E26" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="F26" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -16310,10 +16340,10 @@
         <v>909</v>
       </c>
       <c r="E27" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="F27" t="s">
-        <v>1358</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -16330,10 +16360,10 @@
         <v>911</v>
       </c>
       <c r="E28" t="s">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="F28" t="s">
-        <v>1360</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -16350,10 +16380,10 @@
         <v>912</v>
       </c>
       <c r="E29" t="s">
-        <v>1361</v>
+        <v>1371</v>
       </c>
       <c r="F29" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -16370,10 +16400,10 @@
         <v>913</v>
       </c>
       <c r="E30" t="s">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="F30" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -16390,10 +16420,10 @@
         <v>914</v>
       </c>
       <c r="E31" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
       <c r="F31" t="s">
-        <v>1366</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -16410,10 +16440,10 @@
         <v>915</v>
       </c>
       <c r="E32" t="s">
-        <v>1367</v>
+        <v>1377</v>
       </c>
       <c r="F32" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -16430,10 +16460,10 @@
         <v>916</v>
       </c>
       <c r="E33" t="s">
-        <v>1369</v>
+        <v>1379</v>
       </c>
       <c r="F33" t="s">
-        <v>1370</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -16450,10 +16480,10 @@
         <v>917</v>
       </c>
       <c r="E34" t="s">
-        <v>1371</v>
+        <v>1381</v>
       </c>
       <c r="F34" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -16470,10 +16500,10 @@
         <v>918</v>
       </c>
       <c r="E35" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="F35" t="s">
-        <v>1374</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -16490,10 +16520,10 @@
         <v>919</v>
       </c>
       <c r="E36" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="F36" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -16510,10 +16540,10 @@
         <v>920</v>
       </c>
       <c r="E37" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="F37" t="s">
-        <v>1378</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -16530,10 +16560,10 @@
         <v>921</v>
       </c>
       <c r="E38" t="s">
-        <v>1379</v>
+        <v>1389</v>
       </c>
       <c r="F38" t="s">
-        <v>1380</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -16550,10 +16580,10 @@
         <v>922</v>
       </c>
       <c r="E39" t="s">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="F39" t="s">
-        <v>1382</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -16570,10 +16600,10 @@
         <v>923</v>
       </c>
       <c r="E40" t="s">
-        <v>1383</v>
+        <v>1393</v>
       </c>
       <c r="F40" t="s">
-        <v>1384</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -16590,10 +16620,10 @@
         <v>924</v>
       </c>
       <c r="E41" t="s">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="F41" t="s">
-        <v>1386</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -16610,10 +16640,10 @@
         <v>925</v>
       </c>
       <c r="E42" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="F42" t="s">
-        <v>1388</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -16630,10 +16660,10 @@
         <v>926</v>
       </c>
       <c r="E43" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="F43" t="s">
-        <v>1390</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -16650,10 +16680,10 @@
         <v>927</v>
       </c>
       <c r="E44" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="F44" t="s">
-        <v>1392</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -16670,10 +16700,10 @@
         <v>928</v>
       </c>
       <c r="E45" t="s">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="F45" t="s">
-        <v>1394</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -16690,10 +16720,10 @@
         <v>929</v>
       </c>
       <c r="E46" t="s">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="F46" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -16710,10 +16740,10 @@
         <v>930</v>
       </c>
       <c r="E47" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="F47" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -16730,10 +16760,10 @@
         <v>931</v>
       </c>
       <c r="E48" t="s">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="F48" t="s">
-        <v>1400</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -16750,10 +16780,10 @@
         <v>932</v>
       </c>
       <c r="E49" t="s">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="F49" t="s">
-        <v>1402</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -16770,10 +16800,10 @@
         <v>933</v>
       </c>
       <c r="E50" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="F50" t="s">
-        <v>1404</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -16790,10 +16820,10 @@
         <v>934</v>
       </c>
       <c r="E51" t="s">
-        <v>1405</v>
+        <v>1415</v>
       </c>
       <c r="F51" t="s">
-        <v>1406</v>
+        <v>1416</v>
       </c>
     </row>
   </sheetData>
@@ -28674,13 +28704,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC27A9BC-43A3-4506-B48F-3BBE5EEBD1E7}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -28708,8 +28738,11 @@
       <c r="I1" s="1" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
@@ -28737,8 +28770,11 @@
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
         <v>962</v>
       </c>
@@ -28766,295 +28802,328 @@
       <c r="I3" s="1" t="s">
         <v>970</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="1" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="10">
         <v>800001</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F4" s="10">
         <v>30</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H4" s="10">
         <v>900001</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>977</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="10">
         <v>800002</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F5" s="10">
         <v>10</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="H5" s="10">
         <v>900002</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>983</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="10">
         <v>800003</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F6" s="10">
         <v>40</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="H6" s="10">
         <v>900003</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>990</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="10">
         <v>800004</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="F7" s="10">
         <v>20</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="H7" s="10">
         <v>900004</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>996</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="10">
         <v>800005</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="F8" s="10">
         <v>40</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="H8" s="10">
         <v>900005</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>1003</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="10">
         <v>800006</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F9" s="10">
         <v>20</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="H9" s="10">
         <v>900007</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>1010</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="10">
         <v>800007</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="F10" s="10">
         <v>35</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="H10" s="10">
         <v>900006</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>1017</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="10">
         <v>800008</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="F11" s="10">
         <v>35</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="H11" s="10">
         <v>900008</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>1024</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="10">
         <v>800009</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1017</v>
+        <v>1026</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1019</v>
+        <v>1028</v>
       </c>
       <c r="F12" s="10">
         <v>25</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>1020</v>
+        <v>1029</v>
       </c>
       <c r="H12" s="10">
         <v>900009</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>1030</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="10">
         <v>800010</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="F13" s="10">
         <v>30</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="H13" s="10">
         <v>900010</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>1027</v>
+        <v>1037</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
@@ -29094,58 +29163,58 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1029</v>
+        <v>1040</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>1036</v>
+        <v>1047</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>1037</v>
+        <v>1048</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1041</v>
+        <v>1052</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1045</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1">
@@ -29174,7 +29243,7 @@
         <v>961</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>8</v>
@@ -29212,64 +29281,64 @@
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1048</v>
+        <v>1059</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>962</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>1055</v>
+        <v>1066</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1056</v>
+        <v>1067</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1059</v>
+        <v>1070</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>1062</v>
+        <v>1073</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1">
@@ -29277,7 +29346,7 @@
         <v>900001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="C4" s="8">
         <v>800001</v>
@@ -29286,10 +29355,10 @@
         <v>103003</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
@@ -29298,40 +29367,40 @@
         <v>0</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1075</v>
+        <v>1086</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1076</v>
+        <v>1087</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>1077</v>
+        <v>1088</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>1078</v>
+        <v>1089</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1">
@@ -29339,7 +29408,7 @@
         <v>900002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1081</v>
+        <v>1092</v>
       </c>
       <c r="C5" s="8">
         <v>800002</v>
@@ -29348,10 +29417,10 @@
         <v>103007</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="G5" s="8">
         <v>800001</v>
@@ -29360,40 +29429,40 @@
         <v>10</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1085</v>
+        <v>1096</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>1088</v>
+        <v>1099</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>1095</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1">
@@ -29401,7 +29470,7 @@
         <v>900003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="C6" s="8">
         <v>800003</v>
@@ -29410,10 +29479,10 @@
         <v>103002</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -29422,40 +29491,40 @@
         <v>0</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>1104</v>
+        <v>1115</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>1106</v>
+        <v>1117</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15" customHeight="1">
@@ -29463,7 +29532,7 @@
         <v>900004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1110</v>
+        <v>1121</v>
       </c>
       <c r="C7" s="8">
         <v>800004</v>
@@ -29472,10 +29541,10 @@
         <v>103001</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="G7" s="8">
         <v>800003</v>
@@ -29484,40 +29553,40 @@
         <v>20</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>1113</v>
+        <v>1124</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>1114</v>
+        <v>1125</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>1115</v>
+        <v>1126</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>1116</v>
+        <v>1127</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>1117</v>
+        <v>1128</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>1118</v>
+        <v>1129</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>1123</v>
+        <v>1134</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>1124</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15" customHeight="1">
@@ -29525,7 +29594,7 @@
         <v>900005</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="C8" s="8">
         <v>800005</v>
@@ -29534,10 +29603,10 @@
         <v>103006</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>1126</v>
+        <v>1137</v>
       </c>
       <c r="G8" s="8">
         <v>800002</v>
@@ -29546,40 +29615,40 @@
         <v>10</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>1129</v>
+        <v>1140</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>1132</v>
+        <v>1143</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>1138</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1">
@@ -29587,7 +29656,7 @@
         <v>900006</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="C9" s="8">
         <v>800006</v>
@@ -29596,10 +29665,10 @@
         <v>103004</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="G9" s="8">
         <v>800005</v>
@@ -29608,40 +29677,40 @@
         <v>20</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>1146</v>
+        <v>1157</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>1147</v>
+        <v>1158</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1148</v>
+        <v>1159</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1">
@@ -29649,7 +29718,7 @@
         <v>900007</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="C10" s="8">
         <v>800007</v>
@@ -29658,10 +29727,10 @@
         <v>103009</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1155</v>
+        <v>1166</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1156</v>
+        <v>1167</v>
       </c>
       <c r="G10" s="8">
         <v>800005</v>
@@ -29670,40 +29739,40 @@
         <v>30</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>1157</v>
+        <v>1168</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>1158</v>
+        <v>1169</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>1159</v>
+        <v>1170</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>1161</v>
+        <v>1172</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>1163</v>
+        <v>1174</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>1164</v>
+        <v>1175</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>1166</v>
+        <v>1177</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>1167</v>
+        <v>1178</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>1168</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1">
@@ -29711,7 +29780,7 @@
         <v>900008</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1169</v>
+        <v>1180</v>
       </c>
       <c r="C11" s="8">
         <v>800008</v>
@@ -29720,10 +29789,10 @@
         <v>103005</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1171</v>
+        <v>1182</v>
       </c>
       <c r="G11" s="8">
         <v>800007</v>
@@ -29732,40 +29801,40 @@
         <v>10</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>1172</v>
+        <v>1183</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>1173</v>
+        <v>1184</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>1174</v>
+        <v>1185</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>1175</v>
+        <v>1186</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>1176</v>
+        <v>1187</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>1177</v>
+        <v>1188</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1178</v>
+        <v>1189</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>1180</v>
+        <v>1191</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>1181</v>
+        <v>1192</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>1182</v>
+        <v>1193</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>1183</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1">
@@ -29773,7 +29842,7 @@
         <v>900009</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1184</v>
+        <v>1195</v>
       </c>
       <c r="C12" s="8">
         <v>800009</v>
@@ -29782,10 +29851,10 @@
         <v>103010</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1185</v>
+        <v>1196</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>1185</v>
+        <v>1196</v>
       </c>
       <c r="G12" s="8">
         <v>800008</v>
@@ -29794,40 +29863,40 @@
         <v>10</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>1186</v>
+        <v>1197</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>1187</v>
+        <v>1198</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>1188</v>
+        <v>1199</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>1189</v>
+        <v>1200</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>1190</v>
+        <v>1201</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>1191</v>
+        <v>1202</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>1192</v>
+        <v>1203</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>1193</v>
+        <v>1204</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>1194</v>
+        <v>1205</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>1195</v>
+        <v>1206</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>1196</v>
+        <v>1207</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>1197</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1">
@@ -29835,7 +29904,7 @@
         <v>900010</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1198</v>
+        <v>1209</v>
       </c>
       <c r="C13" s="8">
         <v>800010</v>
@@ -29844,10 +29913,10 @@
         <v>103008</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1199</v>
+        <v>1210</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>1200</v>
+        <v>1211</v>
       </c>
       <c r="G13" s="8">
         <v>800001</v>
@@ -29856,40 +29925,40 @@
         <v>20</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>1201</v>
+        <v>1212</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>1202</v>
+        <v>1213</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>1203</v>
+        <v>1214</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>1204</v>
+        <v>1215</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>1205</v>
+        <v>1216</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>1206</v>
+        <v>1217</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>1207</v>
+        <v>1218</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>1208</v>
+        <v>1219</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>1209</v>
+        <v>1220</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>1210</v>
+        <v>1221</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>1211</v>
+        <v>1222</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>1212</v>
+        <v>1223</v>
       </c>
     </row>
   </sheetData>
@@ -29918,16 +29987,16 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>1213</v>
+        <v>1224</v>
       </c>
       <c r="E1" t="s">
-        <v>1214</v>
+        <v>1225</v>
       </c>
       <c r="F1" t="s">
-        <v>1215</v>
+        <v>1226</v>
       </c>
       <c r="G1" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -29941,13 +30010,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>1216</v>
+        <v>1227</v>
       </c>
       <c r="E2" t="s">
         <v>821</v>
       </c>
       <c r="F2" t="s">
-        <v>1217</v>
+        <v>1228</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -29955,13 +30024,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1219</v>
+        <v>971</v>
       </c>
       <c r="D3" t="s">
         <v>825</v>
@@ -29973,7 +30042,7 @@
         <v>827</v>
       </c>
       <c r="G3" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -29993,10 +30062,10 @@
         <v>842</v>
       </c>
       <c r="F4" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="G4" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -30016,10 +30085,10 @@
         <v>842</v>
       </c>
       <c r="F5" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="G5" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -30039,10 +30108,10 @@
         <v>842</v>
       </c>
       <c r="F6" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="G6" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -30062,10 +30131,10 @@
         <v>842</v>
       </c>
       <c r="F7" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="G7" t="s">
-        <v>1227</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -30079,16 +30148,16 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="E8" t="s">
         <v>842</v>
       </c>
       <c r="F8" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="G8" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -30108,10 +30177,10 @@
         <v>842</v>
       </c>
       <c r="F9" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G9" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -30131,10 +30200,10 @@
         <v>842</v>
       </c>
       <c r="F10" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="G10" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -30154,10 +30223,10 @@
         <v>842</v>
       </c>
       <c r="F11" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="G11" t="s">
-        <v>1233</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -30171,16 +30240,16 @@
         <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="E12" t="s">
         <v>842</v>
       </c>
       <c r="F12" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G12" t="s">
-        <v>1235</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -30203,7 +30272,7 @@
         <v>839</v>
       </c>
       <c r="G13" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -30223,10 +30292,10 @@
         <v>842</v>
       </c>
       <c r="F14" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G14" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -30249,7 +30318,7 @@
         <v>832</v>
       </c>
       <c r="G15" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -30263,16 +30332,16 @@
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
       <c r="E16" t="s">
         <v>842</v>
       </c>
       <c r="F16" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G16" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -30292,10 +30361,10 @@
         <v>842</v>
       </c>
       <c r="F17" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G17" t="s">
-        <v>1241</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -30309,7 +30378,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
       <c r="E18" t="s">
         <v>842</v>
@@ -30318,7 +30387,7 @@
         <v>839</v>
       </c>
       <c r="G18" t="s">
-        <v>1243</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -30338,10 +30407,10 @@
         <v>842</v>
       </c>
       <c r="F19" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G19" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -30364,7 +30433,7 @@
         <v>839</v>
       </c>
       <c r="G20" t="s">
-        <v>1245</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -30378,16 +30447,16 @@
         <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
       <c r="E21" t="s">
         <v>842</v>
       </c>
       <c r="F21" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="G21" t="s">
-        <v>1246</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -30401,16 +30470,16 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="E22" t="s">
         <v>831</v>
       </c>
       <c r="F22" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="G22" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -30424,16 +30493,16 @@
         <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="E23" t="s">
         <v>831</v>
       </c>
       <c r="F23" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="G23" t="s">
-        <v>1249</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -30453,10 +30522,10 @@
         <v>831</v>
       </c>
       <c r="F24" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G24" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -30476,10 +30545,10 @@
         <v>831</v>
       </c>
       <c r="F25" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="G25" t="s">
-        <v>1252</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -30499,10 +30568,10 @@
         <v>831</v>
       </c>
       <c r="F26" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="G26" t="s">
-        <v>1253</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -30522,10 +30591,10 @@
         <v>831</v>
       </c>
       <c r="F27" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="G27" t="s">
-        <v>1254</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -30545,10 +30614,10 @@
         <v>831</v>
       </c>
       <c r="F28" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="G28" t="s">
-        <v>1255</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -30568,10 +30637,10 @@
         <v>831</v>
       </c>
       <c r="F29" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G29" t="s">
-        <v>1256</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -30594,7 +30663,7 @@
         <v>832</v>
       </c>
       <c r="G30" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -30617,7 +30686,7 @@
         <v>837</v>
       </c>
       <c r="G31" t="s">
-        <v>1258</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -30631,7 +30700,7 @@
         <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>1259</v>
+        <v>1269</v>
       </c>
       <c r="E32" t="s">
         <v>831</v>
@@ -30640,7 +30709,7 @@
         <v>837</v>
       </c>
       <c r="G32" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -30663,7 +30732,7 @@
         <v>839</v>
       </c>
       <c r="G33" t="s">
-        <v>1261</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -30686,7 +30755,7 @@
         <v>839</v>
       </c>
       <c r="G34" t="s">
-        <v>1262</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -30709,7 +30778,7 @@
         <v>841</v>
       </c>
       <c r="G35" t="s">
-        <v>1263</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -30729,10 +30798,10 @@
         <v>831</v>
       </c>
       <c r="F36" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="G36" t="s">
-        <v>1264</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -30752,10 +30821,10 @@
         <v>831</v>
       </c>
       <c r="F37" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G37" t="s">
-        <v>1265</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -30775,10 +30844,10 @@
         <v>831</v>
       </c>
       <c r="F38" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="G38" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -30792,16 +30861,16 @@
         <v>93</v>
       </c>
       <c r="D39" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="E39" t="s">
         <v>842</v>
       </c>
       <c r="F39" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="G39" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -30815,16 +30884,16 @@
         <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="E40" t="s">
         <v>842</v>
       </c>
       <c r="F40" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="G40" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -30838,16 +30907,16 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="E41" t="s">
         <v>842</v>
       </c>
       <c r="F41" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="G41" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
     </row>
   </sheetData>
@@ -30871,13 +30940,13 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="E1" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="F1" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -30902,22 +30971,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1219</v>
+        <v>971</v>
       </c>
       <c r="D3" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
       <c r="E3" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="F3" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -30934,10 +31003,10 @@
         <v>800004</v>
       </c>
       <c r="E4" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="F4" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -30954,10 +31023,10 @@
         <v>800003</v>
       </c>
       <c r="E5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="F5" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -30974,10 +31043,10 @@
         <v>800001</v>
       </c>
       <c r="E6" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F6" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -30994,10 +31063,10 @@
         <v>800006</v>
       </c>
       <c r="E7" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="F7" t="s">
-        <v>1278</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -31014,10 +31083,10 @@
         <v>800008</v>
       </c>
       <c r="E8" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="F8" t="s">
-        <v>1279</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -31034,10 +31103,10 @@
         <v>800005</v>
       </c>
       <c r="E9" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="F9" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -31054,10 +31123,10 @@
         <v>800002</v>
       </c>
       <c r="E10" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="F10" t="s">
-        <v>1281</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -31074,10 +31143,10 @@
         <v>800010</v>
       </c>
       <c r="E11" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="F11" t="s">
-        <v>1282</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -31094,10 +31163,10 @@
         <v>800007</v>
       </c>
       <c r="E12" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="F12" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -31114,10 +31183,10 @@
         <v>800009</v>
       </c>
       <c r="E13" t="s">
-        <v>1017</v>
+        <v>1026</v>
       </c>
       <c r="F13" t="s">
-        <v>1284</v>
+        <v>1294</v>
       </c>
     </row>
   </sheetData>

--- a/Excel2JSON(win-x64)/excel_files/Data.xlsx
+++ b/Excel2JSON(win-x64)/excel_files/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28919"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{252F667A-DDC5-4EAC-91B8-827CF82B4EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8851F10D-FA62-449A-99C6-49BED73FBD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5254" uniqueCount="1417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5263" uniqueCount="1419">
   <si>
     <t>key</t>
   </si>
@@ -2554,12 +2554,12 @@
     <t>high</t>
   </si>
   <si>
+    <t>101019, 101020</t>
+  </si>
+  <si>
     <t>summer</t>
   </si>
   <si>
-    <t>101019, 101020</t>
-  </si>
-  <si>
     <t>fall</t>
   </si>
   <si>
@@ -2590,13 +2590,19 @@
     <t>101036, 101001, 101002, 101003</t>
   </si>
   <si>
+    <t>101036, 101001</t>
+  </si>
+  <si>
     <t>chungcheong</t>
   </si>
   <si>
-    <t>101015, 101009, 101011</t>
-  </si>
-  <si>
-    <t>101009, 101011</t>
+    <t>101025, 101033</t>
+  </si>
+  <si>
+    <t>101007, 101015, 101009, 101011</t>
+  </si>
+  <si>
+    <t>101007, 101009, 101011</t>
   </si>
   <si>
     <t>jeolla</t>
@@ -3975,18 +3981,21 @@
     <t>설명</t>
   </si>
   <si>
+    <t>spring, summer, fall, winter</t>
+  </si>
+  <si>
+    <t>생으로는 코가 찡하지만, 익히면 놀랍게도 호랑이도 좋아할 맛! 100일간 먹으면 사람이 된다던 그 전설… 혹시 당신도?</t>
+  </si>
+  <si>
+    <t>summer, fall</t>
+  </si>
+  <si>
+    <t>보기만 해도 맵다! 매운맛 요리에 빠질 수 없는 자극 담당. 도깨비 뿔도 매워서 도망간다 카더라.</t>
+  </si>
+  <si>
     <t>spring, summer, fall</t>
   </si>
   <si>
-    <t>생으로는 코가 찡하지만, 익히면 놀랍게도 호랑이도 좋아할 맛! 100일간 먹으면 사람이 된다던 그 전설… 혹시 당신도?</t>
-  </si>
-  <si>
-    <t>summer, fall</t>
-  </si>
-  <si>
-    <t>보기만 해도 맵다! 매운맛 요리에 빠질 수 없는 자극 담당. 도깨비 뿔도 매워서 도망간다 카더라.</t>
-  </si>
-  <si>
     <t>달콤하고 아삭한 식감. 당근이지~라는 말이 여기서 나왔다는 믿거나 말거나 전설.</t>
   </si>
   <si>
@@ -4002,21 +4011,21 @@
     <t>고기와 함께라면 천하무적! 산신령도 삼겹살엔 상추쌈을 곁들이신다는 말이 있다.</t>
   </si>
   <si>
+    <t>콩으로 변신 준비 완료. 된장, 간장, 두부까지 조선 요리의 비밀병기.</t>
+  </si>
+  <si>
+    <t>든든한 탄수화물. 익히면 포근, 볶으면 아삭. 감자 없인 겨울을 못 난다 카더라.</t>
+  </si>
+  <si>
+    <t>달달함의 정점! 곰도 반할 맛이라던 그 꿀. 옛날 옛적, 나무꿀단지를 통째로 들고 튀던 도깨비가 있었다 카더라…</t>
+  </si>
+  <si>
+    <t>gyeonggi, chungcheong</t>
+  </si>
+  <si>
     <t>fall, winter</t>
   </si>
   <si>
-    <t>콩으로 변신 준비 완료. 된장, 간장, 두부까지 조선 요리의 비밀병기.</t>
-  </si>
-  <si>
-    <t>든든한 탄수화물. 익히면 포근, 볶으면 아삭. 감자 없인 겨울을 못 난다 카더라.</t>
-  </si>
-  <si>
-    <t>달달함의 정점! 곰도 반할 맛이라던 그 꿀. 옛날 옛적, 나무꿀단지를 통째로 들고 튀던 도깨비가 있었다 카더라…</t>
-  </si>
-  <si>
-    <t>gyeonggi, chungcheong</t>
-  </si>
-  <si>
     <t>국물에 넣으면 시원함 2배. 단단하지만 부드러운 채소. 무 없인 국도 울고 간다.</t>
   </si>
   <si>
@@ -4111,9 +4120,6 @@
   </si>
   <si>
     <t>겨울이 제철인 귀한 생선. 칼바람 부는 날엔 방어 한 점이 약보다 낫다지.</t>
-  </si>
-  <si>
-    <t>spring, summer, fall, winter</t>
   </si>
   <si>
     <t>모든 요리의 시작. 깨끗한 물이 맛을 좌우한다.</t>
@@ -15544,16 +15550,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D1" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E1" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="F1" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15570,7 +15576,7 @@
         <v>824</v>
       </c>
       <c r="E2" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -15578,22 +15584,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E3" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="F3" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15607,13 +15613,13 @@
         <v>392</v>
       </c>
       <c r="D4" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E4" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="F4" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15627,13 +15633,13 @@
         <v>400</v>
       </c>
       <c r="D5" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E5" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="F5" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15647,13 +15653,13 @@
         <v>408</v>
       </c>
       <c r="D6" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E6" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="F6" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15667,13 +15673,13 @@
         <v>412</v>
       </c>
       <c r="D7" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E7" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="F7" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15687,13 +15693,13 @@
         <v>416</v>
       </c>
       <c r="D8" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E8" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="F8" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15707,13 +15713,13 @@
         <v>420</v>
       </c>
       <c r="D9" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E9" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15727,13 +15733,13 @@
         <v>424</v>
       </c>
       <c r="D10" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E10" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="F10" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15747,13 +15753,13 @@
         <v>428</v>
       </c>
       <c r="D11" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="E11" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="F11" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15767,13 +15773,13 @@
         <v>432</v>
       </c>
       <c r="D12" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="E12" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="F12" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15787,13 +15793,13 @@
         <v>436</v>
       </c>
       <c r="D13" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="E13" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="F13" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
     </row>
   </sheetData>
@@ -15814,16 +15820,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D1" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E1" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="F1" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15840,7 +15846,7 @@
         <v>824</v>
       </c>
       <c r="E2" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -15848,22 +15854,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C3" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E3" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="F3" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15877,13 +15883,13 @@
         <v>471</v>
       </c>
       <c r="D4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E4" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="F4" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15897,13 +15903,13 @@
         <v>475</v>
       </c>
       <c r="D5" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E5" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="F5" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15917,13 +15923,13 @@
         <v>479</v>
       </c>
       <c r="D6" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E6" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="F6" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15937,13 +15943,13 @@
         <v>483</v>
       </c>
       <c r="D7" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E7" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="F7" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15957,13 +15963,13 @@
         <v>487</v>
       </c>
       <c r="D8" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="E8" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="F8" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15971,19 +15977,19 @@
         <v>110506</v>
       </c>
       <c r="B9" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C9" t="s">
         <v>491</v>
       </c>
       <c r="D9" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="E9" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="F9" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15997,13 +16003,13 @@
         <v>495</v>
       </c>
       <c r="D10" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E10" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="F10" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -16017,13 +16023,13 @@
         <v>499</v>
       </c>
       <c r="D11" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E11" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="F11" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -16037,13 +16043,13 @@
         <v>503</v>
       </c>
       <c r="D12" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="E12" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -16057,13 +16063,13 @@
         <v>507</v>
       </c>
       <c r="D13" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E13" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="F13" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -16077,13 +16083,13 @@
         <v>511</v>
       </c>
       <c r="D14" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="E14" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="F14" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -16097,13 +16103,13 @@
         <v>515</v>
       </c>
       <c r="D15" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E15" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="F15" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -16117,13 +16123,13 @@
         <v>519</v>
       </c>
       <c r="D16" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E16" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="F16" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -16137,13 +16143,13 @@
         <v>523</v>
       </c>
       <c r="D17" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E17" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="F17" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -16157,13 +16163,13 @@
         <v>527</v>
       </c>
       <c r="D18" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E18" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="F18" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -16177,13 +16183,13 @@
         <v>531</v>
       </c>
       <c r="D19" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="E19" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="F19" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -16197,13 +16203,13 @@
         <v>535</v>
       </c>
       <c r="D20" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="E20" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="F20" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -16217,13 +16223,13 @@
         <v>539</v>
       </c>
       <c r="D21" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E21" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="F21" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -16237,13 +16243,13 @@
         <v>543</v>
       </c>
       <c r="D22" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="E22" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="F22" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -16257,13 +16263,13 @@
         <v>547</v>
       </c>
       <c r="D23" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="E23" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F23" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -16277,13 +16283,13 @@
         <v>551</v>
       </c>
       <c r="D24" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E24" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="F24" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -16297,13 +16303,13 @@
         <v>555</v>
       </c>
       <c r="D25" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="E25" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -16317,13 +16323,13 @@
         <v>559</v>
       </c>
       <c r="D26" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E26" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F26" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -16337,13 +16343,13 @@
         <v>563</v>
       </c>
       <c r="D27" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="E27" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="F27" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -16351,19 +16357,19 @@
         <v>110525</v>
       </c>
       <c r="B28" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C28" t="s">
         <v>567</v>
       </c>
       <c r="D28" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="E28" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="F28" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -16377,13 +16383,13 @@
         <v>571</v>
       </c>
       <c r="D29" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="E29" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="F29" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -16397,13 +16403,13 @@
         <v>575</v>
       </c>
       <c r="D30" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E30" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="F30" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -16417,13 +16423,13 @@
         <v>579</v>
       </c>
       <c r="D31" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E31" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="F31" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -16437,13 +16443,13 @@
         <v>583</v>
       </c>
       <c r="D32" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="E32" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="F32" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -16457,13 +16463,13 @@
         <v>587</v>
       </c>
       <c r="D33" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E33" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="F33" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -16477,13 +16483,13 @@
         <v>591</v>
       </c>
       <c r="D34" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="E34" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="F34" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -16497,13 +16503,13 @@
         <v>595</v>
       </c>
       <c r="D35" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E35" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F35" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -16517,13 +16523,13 @@
         <v>599</v>
       </c>
       <c r="D36" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="E36" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="F36" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -16537,13 +16543,13 @@
         <v>603</v>
       </c>
       <c r="D37" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="E37" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="F37" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -16557,13 +16563,13 @@
         <v>607</v>
       </c>
       <c r="D38" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E38" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="F38" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -16577,13 +16583,13 @@
         <v>611</v>
       </c>
       <c r="D39" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E39" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F39" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -16597,13 +16603,13 @@
         <v>615</v>
       </c>
       <c r="D40" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="E40" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F40" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -16617,13 +16623,13 @@
         <v>619</v>
       </c>
       <c r="D41" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="E41" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="F41" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -16637,13 +16643,13 @@
         <v>623</v>
       </c>
       <c r="D42" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E42" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="F42" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -16657,13 +16663,13 @@
         <v>627</v>
       </c>
       <c r="D43" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="E43" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="F43" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -16677,13 +16683,13 @@
         <v>631</v>
       </c>
       <c r="D44" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E44" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F44" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -16697,13 +16703,13 @@
         <v>635</v>
       </c>
       <c r="D45" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="E45" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="F45" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -16717,13 +16723,13 @@
         <v>639</v>
       </c>
       <c r="D46" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="E46" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="F46" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -16737,13 +16743,13 @@
         <v>643</v>
       </c>
       <c r="D47" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E47" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="F47" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -16757,13 +16763,13 @@
         <v>647</v>
       </c>
       <c r="D48" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="E48" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="F48" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -16777,13 +16783,13 @@
         <v>651</v>
       </c>
       <c r="D49" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="E49" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="F49" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -16797,13 +16803,13 @@
         <v>655</v>
       </c>
       <c r="D50" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E50" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="F50" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -16817,13 +16823,13 @@
         <v>659</v>
       </c>
       <c r="D51" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E51" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="F51" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -22908,8 +22914,8 @@
       <c r="E7" t="s">
         <v>836</v>
       </c>
-      <c r="F7" s="1">
-        <v>101020</v>
+      <c r="F7" s="1" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -22923,7 +22929,7 @@
         <v>831</v>
       </c>
       <c r="D8" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E8" t="s">
         <v>833</v>
@@ -22940,7 +22946,7 @@
         <v>831</v>
       </c>
       <c r="D9" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E9" t="s">
         <v>834</v>
@@ -22957,7 +22963,7 @@
         <v>831</v>
       </c>
       <c r="D10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E10" t="s">
         <v>835</v>
@@ -22974,13 +22980,13 @@
         <v>831</v>
       </c>
       <c r="D11" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E11" t="s">
         <v>836</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -23127,8 +23133,8 @@
       <c r="E19" t="s">
         <v>836</v>
       </c>
-      <c r="F19" s="1">
-        <v>101021</v>
+      <c r="F19" s="1" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -23181,6 +23187,9 @@
       <c r="E22" t="s">
         <v>835</v>
       </c>
+      <c r="F22" s="1">
+        <v>101006</v>
+      </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
@@ -23213,7 +23222,7 @@
         <v>842</v>
       </c>
       <c r="D24" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E24" t="s">
         <v>833</v>
@@ -23230,7 +23239,7 @@
         <v>842</v>
       </c>
       <c r="D25" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E25" t="s">
         <v>834</v>
@@ -23247,10 +23256,13 @@
         <v>842</v>
       </c>
       <c r="D26" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E26" t="s">
         <v>835</v>
+      </c>
+      <c r="F26" s="1">
+        <v>101006</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -23264,7 +23276,7 @@
         <v>842</v>
       </c>
       <c r="D27" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E27" t="s">
         <v>836</v>
@@ -23491,8 +23503,8 @@
       <c r="E39" t="s">
         <v>836</v>
       </c>
-      <c r="F39" s="1">
-        <v>101020</v>
+      <c r="F39" s="1" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -23506,7 +23518,7 @@
         <v>831</v>
       </c>
       <c r="D40" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E40" t="s">
         <v>833</v>
@@ -23523,7 +23535,7 @@
         <v>831</v>
       </c>
       <c r="D41" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E41" t="s">
         <v>834</v>
@@ -23540,7 +23552,7 @@
         <v>831</v>
       </c>
       <c r="D42" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E42" t="s">
         <v>835</v>
@@ -23557,13 +23569,13 @@
         <v>831</v>
       </c>
       <c r="D43" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E43" t="s">
         <v>836</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -23713,6 +23725,9 @@
       <c r="E51" t="s">
         <v>836</v>
       </c>
+      <c r="F51" s="1">
+        <v>101019</v>
+      </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
@@ -23796,7 +23811,7 @@
         <v>842</v>
       </c>
       <c r="D56" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E56" t="s">
         <v>833</v>
@@ -23813,7 +23828,7 @@
         <v>842</v>
       </c>
       <c r="D57" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E57" t="s">
         <v>834</v>
@@ -23833,7 +23848,7 @@
         <v>842</v>
       </c>
       <c r="D58" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E58" t="s">
         <v>835</v>
@@ -23850,7 +23865,7 @@
         <v>842</v>
       </c>
       <c r="D59" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E59" t="s">
         <v>836</v>
@@ -24009,8 +24024,8 @@
       <c r="E67" t="s">
         <v>836</v>
       </c>
-      <c r="F67" s="1">
-        <v>101036</v>
+      <c r="F67" s="1" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -24018,7 +24033,7 @@
         <v>200065</v>
       </c>
       <c r="B68" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C68" t="s">
         <v>831</v>
@@ -24035,7 +24050,7 @@
         <v>200066</v>
       </c>
       <c r="B69" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C69" t="s">
         <v>831</v>
@@ -24052,7 +24067,7 @@
         <v>200067</v>
       </c>
       <c r="B70" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C70" t="s">
         <v>831</v>
@@ -24072,7 +24087,7 @@
         <v>200068</v>
       </c>
       <c r="B71" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C71" t="s">
         <v>831</v>
@@ -24083,8 +24098,8 @@
       <c r="E71" t="s">
         <v>836</v>
       </c>
-      <c r="F71" s="1">
-        <v>101020</v>
+      <c r="F71" s="1" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -24092,13 +24107,13 @@
         <v>200069</v>
       </c>
       <c r="B72" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C72" t="s">
         <v>831</v>
       </c>
       <c r="D72" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E72" t="s">
         <v>833</v>
@@ -24112,13 +24127,13 @@
         <v>200070</v>
       </c>
       <c r="B73" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C73" t="s">
         <v>831</v>
       </c>
       <c r="D73" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E73" t="s">
         <v>834</v>
@@ -24129,19 +24144,19 @@
         <v>200071</v>
       </c>
       <c r="B74" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C74" t="s">
         <v>831</v>
       </c>
       <c r="D74" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E74" t="s">
         <v>835</v>
       </c>
-      <c r="F74" s="1">
-        <v>101033</v>
+      <c r="F74" s="1" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -24149,19 +24164,19 @@
         <v>200072</v>
       </c>
       <c r="B75" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C75" t="s">
         <v>831</v>
       </c>
       <c r="D75" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E75" t="s">
         <v>836</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -24169,7 +24184,7 @@
         <v>200073</v>
       </c>
       <c r="B76" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C76" t="s">
         <v>831</v>
@@ -24186,7 +24201,7 @@
         <v>200074</v>
       </c>
       <c r="B77" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C77" t="s">
         <v>831</v>
@@ -24203,7 +24218,7 @@
         <v>200075</v>
       </c>
       <c r="B78" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C78" t="s">
         <v>831</v>
@@ -24214,8 +24229,8 @@
       <c r="E78" t="s">
         <v>835</v>
       </c>
-      <c r="F78" s="1">
-        <v>101033</v>
+      <c r="F78" s="1" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -24223,7 +24238,7 @@
         <v>200076</v>
       </c>
       <c r="B79" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C79" t="s">
         <v>831</v>
@@ -24243,7 +24258,7 @@
         <v>200077</v>
       </c>
       <c r="B80" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C80" t="s">
         <v>831</v>
@@ -24260,7 +24275,7 @@
         <v>200078</v>
       </c>
       <c r="B81" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C81" t="s">
         <v>831</v>
@@ -24277,7 +24292,7 @@
         <v>200079</v>
       </c>
       <c r="B82" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C82" t="s">
         <v>831</v>
@@ -24297,7 +24312,7 @@
         <v>200080</v>
       </c>
       <c r="B83" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C83" t="s">
         <v>831</v>
@@ -24307,6 +24322,9 @@
       </c>
       <c r="E83" t="s">
         <v>836</v>
+      </c>
+      <c r="F83" s="1">
+        <v>101019</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -24314,7 +24332,7 @@
         <v>200081</v>
       </c>
       <c r="B84" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C84" t="s">
         <v>842</v>
@@ -24331,7 +24349,7 @@
         <v>200082</v>
       </c>
       <c r="B85" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C85" t="s">
         <v>842</v>
@@ -24348,7 +24366,7 @@
         <v>200083</v>
       </c>
       <c r="B86" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C86" t="s">
         <v>842</v>
@@ -24368,7 +24386,7 @@
         <v>200084</v>
       </c>
       <c r="B87" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C87" t="s">
         <v>842</v>
@@ -24388,13 +24406,13 @@
         <v>200085</v>
       </c>
       <c r="B88" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C88" t="s">
         <v>842</v>
       </c>
       <c r="D88" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E88" t="s">
         <v>833</v>
@@ -24405,13 +24423,13 @@
         <v>200086</v>
       </c>
       <c r="B89" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C89" t="s">
         <v>842</v>
       </c>
       <c r="D89" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E89" t="s">
         <v>834</v>
@@ -24422,13 +24440,13 @@
         <v>200087</v>
       </c>
       <c r="B90" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C90" t="s">
         <v>842</v>
       </c>
       <c r="D90" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E90" t="s">
         <v>835</v>
@@ -24442,13 +24460,13 @@
         <v>200088</v>
       </c>
       <c r="B91" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C91" t="s">
         <v>842</v>
       </c>
       <c r="D91" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E91" t="s">
         <v>836</v>
@@ -24462,7 +24480,7 @@
         <v>200089</v>
       </c>
       <c r="B92" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C92" t="s">
         <v>842</v>
@@ -24479,7 +24497,7 @@
         <v>200090</v>
       </c>
       <c r="B93" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C93" t="s">
         <v>842</v>
@@ -24499,7 +24517,7 @@
         <v>200091</v>
       </c>
       <c r="B94" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C94" t="s">
         <v>842</v>
@@ -24511,7 +24529,7 @@
         <v>835</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -24519,7 +24537,7 @@
         <v>200092</v>
       </c>
       <c r="B95" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C95" t="s">
         <v>842</v>
@@ -24539,7 +24557,7 @@
         <v>200093</v>
       </c>
       <c r="B96" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C96" t="s">
         <v>842</v>
@@ -24556,7 +24574,7 @@
         <v>200094</v>
       </c>
       <c r="B97" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C97" t="s">
         <v>842</v>
@@ -24576,7 +24594,7 @@
         <v>200095</v>
       </c>
       <c r="B98" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C98" t="s">
         <v>842</v>
@@ -24588,7 +24606,7 @@
         <v>835</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -24596,7 +24614,7 @@
         <v>200096</v>
       </c>
       <c r="B99" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C99" t="s">
         <v>842</v>
@@ -24616,7 +24634,7 @@
         <v>200097</v>
       </c>
       <c r="B100" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C100" t="s">
         <v>831</v>
@@ -24633,7 +24651,7 @@
         <v>200098</v>
       </c>
       <c r="B101" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C101" t="s">
         <v>831</v>
@@ -24653,7 +24671,7 @@
         <v>200099</v>
       </c>
       <c r="B102" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C102" t="s">
         <v>831</v>
@@ -24670,7 +24688,7 @@
         <v>200100</v>
       </c>
       <c r="B103" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C103" t="s">
         <v>831</v>
@@ -24681,8 +24699,8 @@
       <c r="E103" t="s">
         <v>836</v>
       </c>
-      <c r="F103" s="1">
-        <v>101020</v>
+      <c r="F103" s="1" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -24690,13 +24708,13 @@
         <v>200101</v>
       </c>
       <c r="B104" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C104" t="s">
         <v>831</v>
       </c>
       <c r="D104" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E104" t="s">
         <v>833</v>
@@ -24707,19 +24725,19 @@
         <v>200102</v>
       </c>
       <c r="B105" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C105" t="s">
         <v>831</v>
       </c>
       <c r="D105" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E105" t="s">
         <v>834</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -24727,13 +24745,13 @@
         <v>200103</v>
       </c>
       <c r="B106" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C106" t="s">
         <v>831</v>
       </c>
       <c r="D106" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E106" t="s">
         <v>835</v>
@@ -24744,19 +24762,19 @@
         <v>200104</v>
       </c>
       <c r="B107" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C107" t="s">
         <v>831</v>
       </c>
       <c r="D107" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E107" t="s">
         <v>836</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -24764,7 +24782,7 @@
         <v>200105</v>
       </c>
       <c r="B108" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C108" t="s">
         <v>831</v>
@@ -24781,7 +24799,7 @@
         <v>200106</v>
       </c>
       <c r="B109" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C109" t="s">
         <v>831</v>
@@ -24801,7 +24819,7 @@
         <v>200107</v>
       </c>
       <c r="B110" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C110" t="s">
         <v>831</v>
@@ -24821,7 +24839,7 @@
         <v>200108</v>
       </c>
       <c r="B111" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C111" t="s">
         <v>831</v>
@@ -24841,7 +24859,7 @@
         <v>200109</v>
       </c>
       <c r="B112" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C112" t="s">
         <v>831</v>
@@ -24858,7 +24876,7 @@
         <v>200110</v>
       </c>
       <c r="B113" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C113" t="s">
         <v>831</v>
@@ -24878,7 +24896,7 @@
         <v>200111</v>
       </c>
       <c r="B114" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C114" t="s">
         <v>831</v>
@@ -24898,7 +24916,7 @@
         <v>200112</v>
       </c>
       <c r="B115" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C115" t="s">
         <v>831</v>
@@ -24908,6 +24926,9 @@
       </c>
       <c r="E115" t="s">
         <v>836</v>
+      </c>
+      <c r="F115" s="1">
+        <v>101019</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -24915,7 +24936,7 @@
         <v>200113</v>
       </c>
       <c r="B116" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C116" t="s">
         <v>842</v>
@@ -24932,7 +24953,7 @@
         <v>200114</v>
       </c>
       <c r="B117" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C117" t="s">
         <v>842</v>
@@ -24944,7 +24965,7 @@
         <v>834</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -24952,7 +24973,7 @@
         <v>200115</v>
       </c>
       <c r="B118" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C118" t="s">
         <v>842</v>
@@ -24972,7 +24993,7 @@
         <v>200116</v>
       </c>
       <c r="B119" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C119" t="s">
         <v>842</v>
@@ -24992,13 +25013,13 @@
         <v>200117</v>
       </c>
       <c r="B120" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C120" t="s">
         <v>842</v>
       </c>
       <c r="D120" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E120" t="s">
         <v>833</v>
@@ -25009,19 +25030,19 @@
         <v>200118</v>
       </c>
       <c r="B121" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C121" t="s">
         <v>842</v>
       </c>
       <c r="D121" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E121" t="s">
         <v>834</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -25029,13 +25050,13 @@
         <v>200119</v>
       </c>
       <c r="B122" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C122" t="s">
         <v>842</v>
       </c>
       <c r="D122" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E122" t="s">
         <v>835</v>
@@ -25046,13 +25067,13 @@
         <v>200120</v>
       </c>
       <c r="B123" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C123" t="s">
         <v>842</v>
       </c>
       <c r="D123" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E123" t="s">
         <v>836</v>
@@ -25066,7 +25087,7 @@
         <v>200121</v>
       </c>
       <c r="B124" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C124" t="s">
         <v>842</v>
@@ -25083,7 +25104,7 @@
         <v>200122</v>
       </c>
       <c r="B125" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C125" t="s">
         <v>842</v>
@@ -25103,7 +25124,7 @@
         <v>200123</v>
       </c>
       <c r="B126" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C126" t="s">
         <v>842</v>
@@ -25115,7 +25136,7 @@
         <v>835</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -25123,7 +25144,7 @@
         <v>200124</v>
       </c>
       <c r="B127" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C127" t="s">
         <v>842</v>
@@ -25143,7 +25164,7 @@
         <v>200125</v>
       </c>
       <c r="B128" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C128" t="s">
         <v>842</v>
@@ -25160,7 +25181,7 @@
         <v>200126</v>
       </c>
       <c r="B129" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C129" t="s">
         <v>842</v>
@@ -25180,7 +25201,7 @@
         <v>200127</v>
       </c>
       <c r="B130" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C130" t="s">
         <v>842</v>
@@ -25200,7 +25221,7 @@
         <v>200128</v>
       </c>
       <c r="B131" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C131" t="s">
         <v>842</v>
@@ -25220,7 +25241,7 @@
         <v>200129</v>
       </c>
       <c r="B132" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C132" t="s">
         <v>831</v>
@@ -25232,7 +25253,7 @@
         <v>833</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -25240,7 +25261,7 @@
         <v>200130</v>
       </c>
       <c r="B133" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C133" t="s">
         <v>831</v>
@@ -25257,7 +25278,7 @@
         <v>200131</v>
       </c>
       <c r="B134" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C134" t="s">
         <v>831</v>
@@ -25274,7 +25295,7 @@
         <v>200132</v>
       </c>
       <c r="B135" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C135" t="s">
         <v>831</v>
@@ -25285,8 +25306,8 @@
       <c r="E135" t="s">
         <v>836</v>
       </c>
-      <c r="F135" s="1">
-        <v>101020</v>
+      <c r="F135" s="1" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -25294,19 +25315,19 @@
         <v>200133</v>
       </c>
       <c r="B136" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C136" t="s">
         <v>831</v>
       </c>
       <c r="D136" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E136" t="s">
         <v>833</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -25314,13 +25335,13 @@
         <v>200134</v>
       </c>
       <c r="B137" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C137" t="s">
         <v>831</v>
       </c>
       <c r="D137" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E137" t="s">
         <v>834</v>
@@ -25331,13 +25352,13 @@
         <v>200135</v>
       </c>
       <c r="B138" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C138" t="s">
         <v>831</v>
       </c>
       <c r="D138" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E138" t="s">
         <v>835</v>
@@ -25348,19 +25369,19 @@
         <v>200136</v>
       </c>
       <c r="B139" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C139" t="s">
         <v>831</v>
       </c>
       <c r="D139" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E139" t="s">
         <v>836</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -25368,7 +25389,7 @@
         <v>200137</v>
       </c>
       <c r="B140" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C140" t="s">
         <v>831</v>
@@ -25388,7 +25409,7 @@
         <v>200138</v>
       </c>
       <c r="B141" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C141" t="s">
         <v>831</v>
@@ -25405,7 +25426,7 @@
         <v>200139</v>
       </c>
       <c r="B142" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C142" t="s">
         <v>831</v>
@@ -25422,7 +25443,7 @@
         <v>200140</v>
       </c>
       <c r="B143" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C143" t="s">
         <v>831</v>
@@ -25442,7 +25463,7 @@
         <v>200141</v>
       </c>
       <c r="B144" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C144" t="s">
         <v>831</v>
@@ -25454,7 +25475,7 @@
         <v>833</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -25462,7 +25483,7 @@
         <v>200142</v>
       </c>
       <c r="B145" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C145" t="s">
         <v>831</v>
@@ -25479,7 +25500,7 @@
         <v>200143</v>
       </c>
       <c r="B146" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C146" t="s">
         <v>831</v>
@@ -25496,7 +25517,7 @@
         <v>200144</v>
       </c>
       <c r="B147" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C147" t="s">
         <v>831</v>
@@ -25506,6 +25527,9 @@
       </c>
       <c r="E147" t="s">
         <v>836</v>
+      </c>
+      <c r="F147" s="1">
+        <v>101019</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -25513,7 +25537,7 @@
         <v>200145</v>
       </c>
       <c r="B148" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C148" t="s">
         <v>842</v>
@@ -25530,7 +25554,7 @@
         <v>200146</v>
       </c>
       <c r="B149" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C149" t="s">
         <v>842</v>
@@ -25547,7 +25571,7 @@
         <v>200147</v>
       </c>
       <c r="B150" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C150" t="s">
         <v>842</v>
@@ -25564,7 +25588,7 @@
         <v>200148</v>
       </c>
       <c r="B151" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C151" t="s">
         <v>842</v>
@@ -25576,7 +25600,7 @@
         <v>836</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -25584,13 +25608,13 @@
         <v>200149</v>
       </c>
       <c r="B152" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C152" t="s">
         <v>842</v>
       </c>
       <c r="D152" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E152" t="s">
         <v>833</v>
@@ -25601,13 +25625,13 @@
         <v>200150</v>
       </c>
       <c r="B153" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C153" t="s">
         <v>842</v>
       </c>
       <c r="D153" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E153" t="s">
         <v>834</v>
@@ -25621,13 +25645,13 @@
         <v>200151</v>
       </c>
       <c r="B154" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C154" t="s">
         <v>842</v>
       </c>
       <c r="D154" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E154" t="s">
         <v>835</v>
@@ -25638,19 +25662,19 @@
         <v>200152</v>
       </c>
       <c r="B155" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C155" t="s">
         <v>842</v>
       </c>
       <c r="D155" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E155" t="s">
         <v>836</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -25658,7 +25682,7 @@
         <v>200153</v>
       </c>
       <c r="B156" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C156" t="s">
         <v>842</v>
@@ -25675,7 +25699,7 @@
         <v>200154</v>
       </c>
       <c r="B157" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C157" t="s">
         <v>842</v>
@@ -25695,7 +25719,7 @@
         <v>200155</v>
       </c>
       <c r="B158" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C158" t="s">
         <v>842</v>
@@ -25715,7 +25739,7 @@
         <v>200156</v>
       </c>
       <c r="B159" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C159" t="s">
         <v>842</v>
@@ -25727,7 +25751,7 @@
         <v>836</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -25735,7 +25759,7 @@
         <v>200157</v>
       </c>
       <c r="B160" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C160" t="s">
         <v>842</v>
@@ -25752,7 +25776,7 @@
         <v>200158</v>
       </c>
       <c r="B161" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C161" t="s">
         <v>842</v>
@@ -25769,7 +25793,7 @@
         <v>200159</v>
       </c>
       <c r="B162" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C162" t="s">
         <v>842</v>
@@ -25789,7 +25813,7 @@
         <v>200160</v>
       </c>
       <c r="B163" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C163" t="s">
         <v>842</v>
@@ -25829,13 +25853,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>669</v>
@@ -25863,22 +25887,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -25886,7 +25910,7 @@
         <v>601001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C4" s="9">
         <v>110100</v>
@@ -27046,7 +27070,7 @@
         <v>601059</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C62" s="9">
         <v>110158</v>
@@ -27086,7 +27110,7 @@
         <v>601061</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C64" s="9">
         <v>110160</v>
@@ -27412,7 +27436,7 @@
         <v>110172</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E80" s="9">
         <v>1007</v>
@@ -27432,7 +27456,7 @@
         <v>110174</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E81" s="9">
         <v>1007</v>
@@ -27452,7 +27476,7 @@
         <v>110176</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E82" s="9">
         <v>1007</v>
@@ -27472,7 +27496,7 @@
         <v>110177</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E83" s="9">
         <v>1007</v>
@@ -27492,7 +27516,7 @@
         <v>110178</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E84" s="9">
         <v>1007</v>
@@ -27512,7 +27536,7 @@
         <v>110179</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E85" s="9">
         <v>1007</v>
@@ -27532,7 +27556,7 @@
         <v>110180</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E86" s="9">
         <v>1007</v>
@@ -27552,7 +27576,7 @@
         <v>110181</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="E87" s="9">
         <v>1007</v>
@@ -27572,7 +27596,7 @@
         <v>110182</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="E88" s="9">
         <v>1007</v>
@@ -27592,7 +27616,7 @@
         <v>110183</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="E89" s="9">
         <v>1007</v>
@@ -27612,7 +27636,7 @@
         <v>110501</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E90" s="9">
         <v>1008</v>
@@ -27632,7 +27656,7 @@
         <v>110502</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E91" s="9">
         <v>1008</v>
@@ -27652,7 +27676,7 @@
         <v>110503</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E92" s="9">
         <v>1008</v>
@@ -27672,7 +27696,7 @@
         <v>110504</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E93" s="9">
         <v>1008</v>
@@ -27692,7 +27716,7 @@
         <v>110505</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="E94" s="9">
         <v>1008</v>
@@ -27706,13 +27730,13 @@
         <v>603006</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C95" s="9">
         <v>110506</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E95" s="9">
         <v>1008</v>
@@ -27732,7 +27756,7 @@
         <v>110507</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E96" s="9">
         <v>1008</v>
@@ -27752,7 +27776,7 @@
         <v>110508</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E97" s="9">
         <v>1008</v>
@@ -27772,7 +27796,7 @@
         <v>110509</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="E98" s="9">
         <v>1008</v>
@@ -27792,7 +27816,7 @@
         <v>110510</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E99" s="9">
         <v>1008</v>
@@ -27812,7 +27836,7 @@
         <v>110511</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="E100" s="9">
         <v>1008</v>
@@ -27832,7 +27856,7 @@
         <v>110512</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E101" s="9">
         <v>1008</v>
@@ -27852,7 +27876,7 @@
         <v>110513</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E102" s="9">
         <v>1008</v>
@@ -27872,7 +27896,7 @@
         <v>110514</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E103" s="9">
         <v>1008</v>
@@ -27892,7 +27916,7 @@
         <v>110515</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E104" s="9">
         <v>1008</v>
@@ -27912,7 +27936,7 @@
         <v>110516</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="E105" s="9">
         <v>1008</v>
@@ -27932,7 +27956,7 @@
         <v>110517</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="E106" s="9">
         <v>1008</v>
@@ -27952,7 +27976,7 @@
         <v>110518</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E107" s="9">
         <v>1008</v>
@@ -27972,7 +27996,7 @@
         <v>110519</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="E108" s="9">
         <v>1008</v>
@@ -27992,7 +28016,7 @@
         <v>110520</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="E109" s="1">
         <v>1008</v>
@@ -28012,7 +28036,7 @@
         <v>110521</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E110" s="1">
         <v>1008</v>
@@ -28032,7 +28056,7 @@
         <v>110522</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="E111" s="1">
         <v>1008</v>
@@ -28052,7 +28076,7 @@
         <v>110523</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E112" s="1">
         <v>1008</v>
@@ -28072,7 +28096,7 @@
         <v>110524</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="E113" s="1">
         <v>1008</v>
@@ -28086,13 +28110,13 @@
         <v>603025</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C114" s="1">
         <v>110525</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="E114" s="1">
         <v>1008</v>
@@ -28112,7 +28136,7 @@
         <v>110526</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="E115" s="1">
         <v>1008</v>
@@ -28132,7 +28156,7 @@
         <v>110527</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E116" s="1">
         <v>1008</v>
@@ -28152,7 +28176,7 @@
         <v>110528</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E117" s="1">
         <v>1008</v>
@@ -28172,7 +28196,7 @@
         <v>110529</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="E118" s="1">
         <v>1008</v>
@@ -28192,7 +28216,7 @@
         <v>110530</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E119" s="1">
         <v>1008</v>
@@ -28212,7 +28236,7 @@
         <v>110531</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="E120" s="1">
         <v>1008</v>
@@ -28232,7 +28256,7 @@
         <v>110532</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E121" s="1">
         <v>1008</v>
@@ -28252,7 +28276,7 @@
         <v>110533</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="E122" s="1">
         <v>1008</v>
@@ -28272,7 +28296,7 @@
         <v>110534</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="E123" s="1">
         <v>1008</v>
@@ -28292,7 +28316,7 @@
         <v>110535</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E124" s="1">
         <v>1008</v>
@@ -28312,7 +28336,7 @@
         <v>110536</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E125" s="1">
         <v>1008</v>
@@ -28332,7 +28356,7 @@
         <v>110537</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="E126" s="1">
         <v>1008</v>
@@ -28352,7 +28376,7 @@
         <v>110538</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="E127" s="1">
         <v>1008</v>
@@ -28372,7 +28396,7 @@
         <v>110539</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E128" s="1">
         <v>1008</v>
@@ -28392,7 +28416,7 @@
         <v>110540</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="E129" s="1">
         <v>1008</v>
@@ -28412,7 +28436,7 @@
         <v>110541</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E130" s="1">
         <v>1008</v>
@@ -28432,7 +28456,7 @@
         <v>110542</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="E131" s="1">
         <v>1008</v>
@@ -28452,7 +28476,7 @@
         <v>110543</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="E132" s="1">
         <v>1008</v>
@@ -28472,7 +28496,7 @@
         <v>110544</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E133" s="1">
         <v>1008</v>
@@ -28492,7 +28516,7 @@
         <v>110545</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="E134" s="1">
         <v>1008</v>
@@ -28512,7 +28536,7 @@
         <v>110546</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="E135" s="1">
         <v>1008</v>
@@ -28532,7 +28556,7 @@
         <v>110547</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E136" s="1">
         <v>1008</v>
@@ -28552,7 +28576,7 @@
         <v>110548</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E137" s="1">
         <v>1008</v>
@@ -28584,7 +28608,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -28595,18 +28619,18 @@
         <v>8</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="10" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -28614,10 +28638,10 @@
         <v>1001</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -28625,10 +28649,10 @@
         <v>1002</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -28636,10 +28660,10 @@
         <v>1003</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -28647,10 +28671,10 @@
         <v>1004</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -28658,10 +28682,10 @@
         <v>1005</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -28669,10 +28693,10 @@
         <v>1006</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -28680,10 +28704,10 @@
         <v>1007</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -28691,7 +28715,7 @@
         <v>1008</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>470</v>
@@ -28718,25 +28742,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
@@ -28759,7 +28783,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>8</v>
@@ -28776,34 +28800,34 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -28811,31 +28835,31 @@
         <v>800001</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="F4" s="10">
         <v>30</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="H4" s="10">
         <v>900001</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -28843,31 +28867,31 @@
         <v>800002</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F5" s="10">
         <v>10</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="H5" s="10">
         <v>900002</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -28875,31 +28899,31 @@
         <v>800003</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F6" s="10">
         <v>40</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="H6" s="10">
         <v>900003</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -28907,31 +28931,31 @@
         <v>800004</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F7" s="10">
         <v>20</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="H7" s="10">
         <v>900004</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -28939,31 +28963,31 @@
         <v>800005</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F8" s="10">
         <v>40</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="H8" s="10">
         <v>900005</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -28971,31 +28995,31 @@
         <v>800006</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="F9" s="10">
         <v>20</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="H9" s="10">
         <v>900007</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -29003,31 +29027,31 @@
         <v>800007</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="F10" s="10">
         <v>35</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="H10" s="10">
         <v>900006</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -29035,31 +29059,31 @@
         <v>800008</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="F11" s="10">
         <v>35</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="H11" s="10">
         <v>900008</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -29067,31 +29091,31 @@
         <v>800009</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="F12" s="10">
         <v>25</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="H12" s="10">
         <v>900009</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -29099,31 +29123,31 @@
         <v>800010</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="F13" s="10">
         <v>30</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="H13" s="10">
         <v>900010</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>
@@ -29163,58 +29187,58 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1">
@@ -29240,10 +29264,10 @@
         <v>7</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>8</v>
@@ -29281,64 +29305,64 @@
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1">
@@ -29346,7 +29370,7 @@
         <v>900001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C4" s="8">
         <v>800001</v>
@@ -29355,10 +29379,10 @@
         <v>103003</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
@@ -29367,40 +29391,40 @@
         <v>0</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1">
@@ -29408,7 +29432,7 @@
         <v>900002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C5" s="8">
         <v>800002</v>
@@ -29417,10 +29441,10 @@
         <v>103007</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="G5" s="8">
         <v>800001</v>
@@ -29429,40 +29453,40 @@
         <v>10</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1">
@@ -29470,7 +29494,7 @@
         <v>900003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C6" s="8">
         <v>800003</v>
@@ -29479,10 +29503,10 @@
         <v>103002</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -29491,40 +29515,40 @@
         <v>0</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15" customHeight="1">
@@ -29532,7 +29556,7 @@
         <v>900004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C7" s="8">
         <v>800004</v>
@@ -29541,10 +29565,10 @@
         <v>103001</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="G7" s="8">
         <v>800003</v>
@@ -29553,40 +29577,40 @@
         <v>20</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15" customHeight="1">
@@ -29594,7 +29618,7 @@
         <v>900005</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C8" s="8">
         <v>800005</v>
@@ -29603,10 +29627,10 @@
         <v>103006</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="G8" s="8">
         <v>800002</v>
@@ -29615,40 +29639,40 @@
         <v>10</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1">
@@ -29656,7 +29680,7 @@
         <v>900006</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C9" s="8">
         <v>800006</v>
@@ -29665,10 +29689,10 @@
         <v>103004</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="G9" s="8">
         <v>800005</v>
@@ -29677,40 +29701,40 @@
         <v>20</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1">
@@ -29718,7 +29742,7 @@
         <v>900007</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="C10" s="8">
         <v>800007</v>
@@ -29727,10 +29751,10 @@
         <v>103009</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="G10" s="8">
         <v>800005</v>
@@ -29739,40 +29763,40 @@
         <v>30</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1">
@@ -29780,7 +29804,7 @@
         <v>900008</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C11" s="8">
         <v>800008</v>
@@ -29789,10 +29813,10 @@
         <v>103005</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="G11" s="8">
         <v>800007</v>
@@ -29801,40 +29825,40 @@
         <v>10</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1">
@@ -29842,7 +29866,7 @@
         <v>900009</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C12" s="8">
         <v>800009</v>
@@ -29851,10 +29875,10 @@
         <v>103010</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="G12" s="8">
         <v>800008</v>
@@ -29863,40 +29887,40 @@
         <v>10</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1">
@@ -29904,7 +29928,7 @@
         <v>900010</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C13" s="8">
         <v>800010</v>
@@ -29913,10 +29937,10 @@
         <v>103008</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="G13" s="8">
         <v>800001</v>
@@ -29925,40 +29949,40 @@
         <v>20</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
   </sheetData>
@@ -29987,16 +30011,16 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="E1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F1" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="G1" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -30010,13 +30034,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="E2" t="s">
         <v>821</v>
       </c>
       <c r="F2" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -30024,13 +30048,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D3" t="s">
         <v>825</v>
@@ -30042,7 +30066,7 @@
         <v>827</v>
       </c>
       <c r="G3" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -30062,10 +30086,10 @@
         <v>842</v>
       </c>
       <c r="F4" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="G4" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -30079,16 +30103,16 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E5" t="s">
         <v>842</v>
       </c>
       <c r="F5" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="G5" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -30108,10 +30132,10 @@
         <v>842</v>
       </c>
       <c r="F6" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="G6" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -30131,10 +30155,10 @@
         <v>842</v>
       </c>
       <c r="F7" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="G7" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -30148,16 +30172,16 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="E8" t="s">
         <v>842</v>
       </c>
       <c r="F8" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="G8" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -30177,10 +30201,10 @@
         <v>842</v>
       </c>
       <c r="F9" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="G9" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -30194,16 +30218,16 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E10" t="s">
         <v>842</v>
       </c>
       <c r="F10" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="G10" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -30217,16 +30241,16 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E11" t="s">
         <v>842</v>
       </c>
       <c r="F11" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="G11" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -30240,16 +30264,16 @@
         <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E12" t="s">
         <v>842</v>
       </c>
       <c r="F12" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G12" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -30272,7 +30296,7 @@
         <v>839</v>
       </c>
       <c r="G13" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -30292,10 +30316,10 @@
         <v>842</v>
       </c>
       <c r="F14" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G14" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -30309,7 +30333,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E15" t="s">
         <v>842</v>
@@ -30318,7 +30342,7 @@
         <v>832</v>
       </c>
       <c r="G15" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -30332,16 +30356,16 @@
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="E16" t="s">
         <v>842</v>
       </c>
       <c r="F16" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G16" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -30355,16 +30379,16 @@
         <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E17" t="s">
         <v>842</v>
       </c>
       <c r="F17" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G17" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -30378,7 +30402,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="E18" t="s">
         <v>842</v>
@@ -30387,7 +30411,7 @@
         <v>839</v>
       </c>
       <c r="G18" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -30401,16 +30425,16 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E19" t="s">
         <v>842</v>
       </c>
       <c r="F19" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G19" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -30433,7 +30457,7 @@
         <v>839</v>
       </c>
       <c r="G20" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -30447,16 +30471,16 @@
         <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="E21" t="s">
         <v>842</v>
       </c>
       <c r="F21" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="G21" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -30470,7 +30494,7 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="E22" t="s">
         <v>831</v>
@@ -30479,7 +30503,7 @@
         <v>1233</v>
       </c>
       <c r="G22" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -30493,16 +30517,16 @@
         <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="E23" t="s">
         <v>831</v>
       </c>
       <c r="F23" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="G23" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -30522,10 +30546,10 @@
         <v>831</v>
       </c>
       <c r="F24" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G24" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -30545,10 +30569,10 @@
         <v>831</v>
       </c>
       <c r="F25" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="G25" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -30568,10 +30592,10 @@
         <v>831</v>
       </c>
       <c r="F26" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="G26" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -30585,16 +30609,16 @@
         <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E27" t="s">
         <v>831</v>
       </c>
       <c r="F27" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="G27" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -30608,16 +30632,16 @@
         <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E28" t="s">
         <v>831</v>
       </c>
       <c r="F28" t="s">
-        <v>1261</v>
+        <v>1233</v>
       </c>
       <c r="G28" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -30631,16 +30655,16 @@
         <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E29" t="s">
         <v>831</v>
       </c>
       <c r="F29" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G29" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -30654,16 +30678,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E30" t="s">
         <v>831</v>
       </c>
       <c r="F30" t="s">
-        <v>832</v>
+        <v>1233</v>
       </c>
       <c r="G30" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -30677,16 +30701,16 @@
         <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E31" t="s">
         <v>831</v>
       </c>
       <c r="F31" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G31" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -30700,16 +30724,16 @@
         <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="E32" t="s">
         <v>831</v>
       </c>
       <c r="F32" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G32" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -30732,7 +30756,7 @@
         <v>839</v>
       </c>
       <c r="G33" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -30755,7 +30779,7 @@
         <v>839</v>
       </c>
       <c r="G34" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -30778,7 +30802,7 @@
         <v>841</v>
       </c>
       <c r="G35" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -30792,16 +30816,16 @@
         <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E36" t="s">
         <v>831</v>
       </c>
       <c r="F36" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="G36" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -30815,16 +30839,16 @@
         <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E37" t="s">
         <v>831</v>
       </c>
       <c r="F37" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="G37" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -30838,16 +30862,16 @@
         <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E38" t="s">
         <v>831</v>
       </c>
       <c r="F38" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="G38" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -30861,16 +30885,16 @@
         <v>93</v>
       </c>
       <c r="D39" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="E39" t="s">
         <v>842</v>
       </c>
       <c r="F39" t="s">
-        <v>1277</v>
+        <v>1233</v>
       </c>
       <c r="G39" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -30884,16 +30908,16 @@
         <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="E40" t="s">
         <v>842</v>
       </c>
       <c r="F40" t="s">
-        <v>1277</v>
+        <v>1233</v>
       </c>
       <c r="G40" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -30907,16 +30931,16 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="E41" t="s">
         <v>842</v>
       </c>
       <c r="F41" t="s">
-        <v>1277</v>
+        <v>1233</v>
       </c>
       <c r="G41" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
   </sheetData>
@@ -30940,13 +30964,13 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E1" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="F1" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -30971,22 +30995,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D3" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E3" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="F3" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -31003,10 +31027,10 @@
         <v>800004</v>
       </c>
       <c r="E4" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="F4" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -31023,10 +31047,10 @@
         <v>800003</v>
       </c>
       <c r="E5" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="F5" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -31043,10 +31067,10 @@
         <v>800001</v>
       </c>
       <c r="E6" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="F6" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -31063,10 +31087,10 @@
         <v>800006</v>
       </c>
       <c r="E7" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F7" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -31083,10 +31107,10 @@
         <v>800008</v>
       </c>
       <c r="E8" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="F8" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -31103,10 +31127,10 @@
         <v>800005</v>
       </c>
       <c r="E9" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="F9" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -31123,10 +31147,10 @@
         <v>800002</v>
       </c>
       <c r="E10" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F10" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -31143,10 +31167,10 @@
         <v>800010</v>
       </c>
       <c r="E11" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="F11" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -31163,10 +31187,10 @@
         <v>800007</v>
       </c>
       <c r="E12" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F12" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -31183,10 +31207,10 @@
         <v>800009</v>
       </c>
       <c r="E13" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="F13" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
     </row>
   </sheetData>

--- a/Excel2JSON(win-x64)/excel_files/Data.xlsx
+++ b/Excel2JSON(win-x64)/excel_files/Data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28919"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8851F10D-FA62-449A-99C6-49BED73FBD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D524A9-FCA7-4504-A27A-7F49D0183C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foods" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5263" uniqueCount="1419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5264" uniqueCount="1418">
   <si>
     <t>key</t>
   </si>
@@ -2722,7 +2722,7 @@
     <t>고구마 조림</t>
   </si>
   <si>
-    <t>110119, 110177</t>
+    <t>110120, 110177</t>
   </si>
   <si>
     <t>110184, 110180, 110409</t>
@@ -3289,7 +3289,7 @@
     <t>죽 요리 제출</t>
   </si>
   <si>
-    <t>굴, 육수, 미역</t>
+    <t>육수, 미역, 굴을 한 번 찐 후에 사용</t>
   </si>
   <si>
     <t>아픈 아이를 위한 따뜻한 한 그릇…</t>
@@ -3301,8 +3301,10 @@
 오늘만큼은 아이가 속 편히 먹을 수 있는 든든한 보양식을 부탁드립니다.
 혹시 가능하시다면, 굴과 육수로 만든 미역국,
 정성껏 끓여주실 수 있을까요?
-참고로, 육수 같은 조합 재료는 도감에서 확인하실 수 있어요.
-미역국이 아니어도, 그와 비슷한 전복이나 게를 사용한 따뜻하고 부드러운 죽 요리라면 괜찮아요.
+참고로, 육수 같은 조합 재료는 요리 도감에서 확인하실 수 있어요.
+아, 굴은 한 번 찐 후에 사용하는 게 더 부드럽고 위에도 좋다더라고요.
+혹시 조리할 때 참고해주실 수 있을까요?
+물론, 미역국이 아니어도 전복이나 게를 사용한 따뜻하고 부드러운 죽 요리라면 괜찮아요.
 뜨끈하고 정성 가득한 그 한 그릇이, 아이에게 큰 힘이 될 거예요.</t>
   </si>
   <si>
@@ -3358,7 +3360,7 @@
     <t>고급 재료 사용 요리 제출</t>
   </si>
   <si>
-    <t>전복, 간장, '칼'로 손질</t>
+    <t>전복, 간장, '칼'로 손질, 그 다음에 한번 더 '칼'로 회를 떠야 한다</t>
   </si>
   <si>
     <t xml:space="preserve"> 내 입은 아무 음식이나 안 받아</t>
@@ -3374,7 +3376,7 @@
 물론, 간장에 콕 찍어 먹는 회 요리여야겠지.
 기본이 안 되어 있으면 바로 실격이니까!
 그리고 말인데, 회를 만들 땐 재료를 먼저 '칼'로 손질하고
-그다음에 '칼'로 회를 떠야 한다는 건, 당연히 알고 있겠지?
+그 다음에 한번 더 '칼'로 회를 떠야 한다는 건, 당연히 알고 있겠지?
 그런 기본도 안 된 요리는 고급이랍시고 올리지도 마!
 뭐, 회 요리가 아니더라도 그 정도 격에 어울리는,
 조선 인삼을 활용한 고급 요리라면…
@@ -3397,12 +3399,12 @@
 솔직히 말해, 기대는 안 했거든.
 그런데 뭐랄까…
 입 안에서 감칠맛이 제법 괜찮게 감돌더군.
-김장할 때 담가둔 묵은지가 하나 있는데,
+저번 시장에서 고급 참기름 한병을 사왔는데,
 원래 아무나 안 주는데 말이야…
 특별히, 너한텐 줘도 괜찮을 것 같군.</t>
   </si>
   <si>
-    <t>내가 이런 걸 먹을 사람으로 보여?</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>허…
@@ -3665,8 +3667,8 @@
     <t>크~ 이게 바로 밥도둑이지 뭐냐!
 고기 냄새가 코를 때리는 그 순간,
 나, 벌써 두 그릇째 퍼먹고 있었다니까!
-너한테 기름 한 병 줄게!
-이거, 내가 아끼던 좋은 거야~
+기분 좋아졌으니까 이거 버터! 너한테 줄께.
+어떤 장사꾼에게 받은건데 말이야. 너한테 주면 더 잘 사용될거 같단 말이지!
 다음엔 더 화끈한 고기 요리 기대할게! 으하하!</t>
   </si>
   <si>
@@ -3735,8 +3737,8 @@
   <si>
     <t>이야~ 제대로 정신이 번쩍 들었어!
 너, 꽤 하는구만?
-기분 좋아졌으니까 이 참기름 한 병 줄게!
-나도 아껴둔 건데… 너한텐 줘도 괜찮을 것 같아~
+너한테 기름 한 병 줄게!
+이거, 내가 아끼던 좋은 거야~
 다음엔 더 재미있는 맛 만들어줘!</t>
   </si>
   <si>
@@ -3932,13 +3934,13 @@
     <t xml:space="preserve"> 절제 속 깊이</t>
   </si>
   <si>
-    <t>넘치지 않았고,
+    <t xml:space="preserve">넘치지 않았고,
 부족하지도 않았소.
 그 요리에는 조선의 정신,
 즉 절제된 정성과 깊은 풍미가 깃들어 있었소.
 그대의 솜씨에 경의를 표하며,
-선대께서 빚어두신 참기름 한 병을 내어드리리다.
-부디, 이 또한 다음 요리에 품위 있게 사용해 주시길 바라오.</t>
+집안 대대로 내려오는 김치를 드리겠소.
+부디, 이 또한 다음 요리에 품위 있게 사용해 주시길 바라오. </t>
   </si>
   <si>
     <t>조선의 맛과는 거리가 있군요</t>
@@ -4286,9 +4288,6 @@
     <t>두툼한 두부에 양념이 쏙쏙!
 밥 위에 척 올리면 한 그릇 뚝딱.
 보들보들하면서도 든든한 단백질 공급원.</t>
-  </si>
-  <si>
-    <t>110120, 110177</t>
   </si>
   <si>
     <t>삶은 고구마, 조림간장</t>
@@ -15983,13 +15982,13 @@
         <v>491</v>
       </c>
       <c r="D9" t="s">
+        <v>893</v>
+      </c>
+      <c r="E9" t="s">
         <v>1332</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>1333</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -16006,10 +16005,10 @@
         <v>894</v>
       </c>
       <c r="E10" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F10" t="s">
         <v>1335</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -16026,10 +16025,10 @@
         <v>895</v>
       </c>
       <c r="E11" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F11" t="s">
         <v>1337</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -16046,10 +16045,10 @@
         <v>896</v>
       </c>
       <c r="E12" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F12" t="s">
         <v>1339</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -16066,10 +16065,10 @@
         <v>897</v>
       </c>
       <c r="E13" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F13" t="s">
         <v>1341</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -16086,10 +16085,10 @@
         <v>898</v>
       </c>
       <c r="E14" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F14" t="s">
         <v>1343</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -16106,10 +16105,10 @@
         <v>899</v>
       </c>
       <c r="E15" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F15" t="s">
         <v>1345</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -16126,10 +16125,10 @@
         <v>900</v>
       </c>
       <c r="E16" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F16" t="s">
         <v>1347</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -16146,10 +16145,10 @@
         <v>901</v>
       </c>
       <c r="E17" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F17" t="s">
         <v>1349</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -16166,10 +16165,10 @@
         <v>902</v>
       </c>
       <c r="E18" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F18" t="s">
         <v>1351</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -16186,10 +16185,10 @@
         <v>903</v>
       </c>
       <c r="E19" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F19" t="s">
         <v>1353</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -16206,10 +16205,10 @@
         <v>904</v>
       </c>
       <c r="E20" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F20" t="s">
         <v>1355</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -16226,10 +16225,10 @@
         <v>905</v>
       </c>
       <c r="E21" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F21" t="s">
         <v>1357</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -16246,10 +16245,10 @@
         <v>906</v>
       </c>
       <c r="E22" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F22" t="s">
         <v>1359</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -16266,10 +16265,10 @@
         <v>907</v>
       </c>
       <c r="E23" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F23" t="s">
         <v>1361</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -16286,10 +16285,10 @@
         <v>908</v>
       </c>
       <c r="E24" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F24" t="s">
         <v>1363</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -16306,10 +16305,10 @@
         <v>909</v>
       </c>
       <c r="E25" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F25" t="s">
         <v>1365</v>
-      </c>
-      <c r="F25" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -16326,10 +16325,10 @@
         <v>910</v>
       </c>
       <c r="E26" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F26" t="s">
         <v>1367</v>
-      </c>
-      <c r="F26" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -16346,10 +16345,10 @@
         <v>911</v>
       </c>
       <c r="E27" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F27" t="s">
         <v>1369</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -16366,10 +16365,10 @@
         <v>913</v>
       </c>
       <c r="E28" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F28" t="s">
         <v>1371</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -16386,10 +16385,10 @@
         <v>914</v>
       </c>
       <c r="E29" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F29" t="s">
         <v>1373</v>
-      </c>
-      <c r="F29" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -16406,10 +16405,10 @@
         <v>915</v>
       </c>
       <c r="E30" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F30" t="s">
         <v>1375</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -16426,10 +16425,10 @@
         <v>916</v>
       </c>
       <c r="E31" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F31" t="s">
         <v>1377</v>
-      </c>
-      <c r="F31" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -16446,10 +16445,10 @@
         <v>917</v>
       </c>
       <c r="E32" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F32" t="s">
         <v>1379</v>
-      </c>
-      <c r="F32" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -16466,10 +16465,10 @@
         <v>918</v>
       </c>
       <c r="E33" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F33" t="s">
         <v>1381</v>
-      </c>
-      <c r="F33" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -16486,10 +16485,10 @@
         <v>919</v>
       </c>
       <c r="E34" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F34" t="s">
         <v>1383</v>
-      </c>
-      <c r="F34" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -16506,10 +16505,10 @@
         <v>920</v>
       </c>
       <c r="E35" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F35" t="s">
         <v>1385</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -16526,10 +16525,10 @@
         <v>921</v>
       </c>
       <c r="E36" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F36" t="s">
         <v>1387</v>
-      </c>
-      <c r="F36" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -16546,10 +16545,10 @@
         <v>922</v>
       </c>
       <c r="E37" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F37" t="s">
         <v>1389</v>
-      </c>
-      <c r="F37" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -16566,10 +16565,10 @@
         <v>923</v>
       </c>
       <c r="E38" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F38" t="s">
         <v>1391</v>
-      </c>
-      <c r="F38" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -16586,10 +16585,10 @@
         <v>924</v>
       </c>
       <c r="E39" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F39" t="s">
         <v>1393</v>
-      </c>
-      <c r="F39" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -16606,10 +16605,10 @@
         <v>925</v>
       </c>
       <c r="E40" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F40" t="s">
         <v>1395</v>
-      </c>
-      <c r="F40" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -16626,10 +16625,10 @@
         <v>926</v>
       </c>
       <c r="E41" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F41" t="s">
         <v>1397</v>
-      </c>
-      <c r="F41" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -16646,10 +16645,10 @@
         <v>927</v>
       </c>
       <c r="E42" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F42" t="s">
         <v>1399</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -16666,10 +16665,10 @@
         <v>928</v>
       </c>
       <c r="E43" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F43" t="s">
         <v>1401</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -16686,10 +16685,10 @@
         <v>929</v>
       </c>
       <c r="E44" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F44" t="s">
         <v>1403</v>
-      </c>
-      <c r="F44" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -16706,10 +16705,10 @@
         <v>930</v>
       </c>
       <c r="E45" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F45" t="s">
         <v>1405</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -16726,10 +16725,10 @@
         <v>931</v>
       </c>
       <c r="E46" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F46" t="s">
         <v>1407</v>
-      </c>
-      <c r="F46" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -16746,10 +16745,10 @@
         <v>932</v>
       </c>
       <c r="E47" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F47" t="s">
         <v>1409</v>
-      </c>
-      <c r="F47" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -16766,10 +16765,10 @@
         <v>933</v>
       </c>
       <c r="E48" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F48" t="s">
         <v>1411</v>
-      </c>
-      <c r="F48" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -16786,10 +16785,10 @@
         <v>934</v>
       </c>
       <c r="E49" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F49" t="s">
         <v>1413</v>
-      </c>
-      <c r="F49" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -16806,10 +16805,10 @@
         <v>935</v>
       </c>
       <c r="E50" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F50" t="s">
         <v>1415</v>
-      </c>
-      <c r="F50" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -16826,10 +16825,10 @@
         <v>936</v>
       </c>
       <c r="E51" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F51" t="s">
         <v>1417</v>
-      </c>
-      <c r="F51" t="s">
-        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -26059,7 +26058,7 @@
         <v>110006</v>
       </c>
       <c r="E11" s="9">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>101</v>
@@ -26079,7 +26078,7 @@
         <v>110107</v>
       </c>
       <c r="E12" s="9">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>101</v>
@@ -29168,7 +29167,7 @@
     <col min="6" max="6" width="20.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.375" style="1" bestFit="1" customWidth="1"/>
@@ -29438,7 +29437,7 @@
         <v>800002</v>
       </c>
       <c r="D5" s="8">
-        <v>103007</v>
+        <v>103009</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>1095</v>
@@ -29452,7 +29451,7 @@
       <c r="H5" s="8">
         <v>10</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="12" t="s">
         <v>1097</v>
       </c>
       <c r="J5" s="11" t="s">
@@ -29686,7 +29685,7 @@
         <v>800006</v>
       </c>
       <c r="D9" s="8">
-        <v>103004</v>
+        <v>103007</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>1153</v>
@@ -29748,7 +29747,7 @@
         <v>800007</v>
       </c>
       <c r="D10" s="8">
-        <v>103009</v>
+        <v>103004</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>1168</v>
@@ -29992,7 +29991,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0316AC22-6E76-4466-9040-E33C4C116F68}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="23.625" bestFit="1" customWidth="1"/>
@@ -30000,7 +29999,7 @@
     <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -30023,7 +30022,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -30046,7 +30045,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>1231</v>
       </c>
@@ -30069,7 +30068,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>110001</v>
       </c>
@@ -30092,7 +30091,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>110002</v>
       </c>
@@ -30115,7 +30114,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>110003</v>
       </c>
@@ -30138,7 +30137,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>110004</v>
       </c>
@@ -30161,7 +30160,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>110005</v>
       </c>
@@ -30184,7 +30183,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>110006</v>
       </c>
@@ -30207,7 +30206,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>110007</v>
       </c>
@@ -30230,7 +30229,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>110008</v>
       </c>
@@ -30253,7 +30252,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>110009</v>
       </c>
@@ -30275,8 +30274,11 @@
       <c r="G12" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>110010</v>
       </c>
@@ -30299,7 +30301,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>110011</v>
       </c>
@@ -30322,7 +30324,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>110012</v>
       </c>
@@ -30345,7 +30347,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>110013</v>
       </c>
@@ -31084,10 +31086,10 @@
         <v>456</v>
       </c>
       <c r="D7">
-        <v>800006</v>
+        <v>800007</v>
       </c>
       <c r="E7" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="F7" t="s">
         <v>1290</v>
@@ -31144,10 +31146,10 @@
         <v>462</v>
       </c>
       <c r="D10">
-        <v>800002</v>
+        <v>800006</v>
       </c>
       <c r="E10" t="s">
-        <v>981</v>
+        <v>1007</v>
       </c>
       <c r="F10" t="s">
         <v>1293</v>
@@ -31184,10 +31186,10 @@
         <v>466</v>
       </c>
       <c r="D12">
-        <v>800007</v>
+        <v>800002</v>
       </c>
       <c r="E12" t="s">
-        <v>1014</v>
+        <v>981</v>
       </c>
       <c r="F12" t="s">
         <v>1295</v>

--- a/Excel2JSON(win-x64)/excel_files/Data.xlsx
+++ b/Excel2JSON(win-x64)/excel_files/Data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28919"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29010"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D524A9-FCA7-4504-A27A-7F49D0183C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72EB484E-13BC-4EC0-BD28-BFE68424AF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foods" sheetId="1" r:id="rId1"/>
@@ -3289,7 +3289,7 @@
     <t>죽 요리 제출</t>
   </si>
   <si>
-    <t>육수, 미역, 굴을 한 번 찐 후에 사용</t>
+    <t>육수, 미역, 굴은 한 번 찐 후에 사용</t>
   </si>
   <si>
     <t>아픈 아이를 위한 따뜻한 한 그릇…</t>
@@ -25975,7 +25975,7 @@
         <v>110103</v>
       </c>
       <c r="D7" s="9">
-        <v>110103</v>
+        <v>110002</v>
       </c>
       <c r="E7" s="9">
         <v>1002</v>
@@ -26015,7 +26015,7 @@
         <v>110105</v>
       </c>
       <c r="D9" s="9">
-        <v>110104</v>
+        <v>110003</v>
       </c>
       <c r="E9" s="9">
         <v>1003</v>
@@ -30954,6 +30954,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF6C8F2-C7EC-46A4-B9CB-9409088395FD}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
